--- a/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/06,26/26,06,26 ПОКОМ ЗПФ/Копия дв 250626 лгрсч пок зпф от Воронкова.xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/06,26/26,06,26 ПОКОМ ЗПФ/Копия дв 250626 лгрсч пок зпф от Воронкова.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\06,26\26,06,26 ПОКОМ ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3206E2F6-411F-4D9C-8F60-DD88771DEBC5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50EA40E3-9571-40F3-BE0B-060B35135E68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,15 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AK$72</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -579,7 +571,7 @@
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="0.00_ ;[Red]\-0.00\ "/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -640,6 +632,22 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="204"/>
     </font>
@@ -749,7 +757,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -787,8 +795,15 @@
     </xf>
     <xf numFmtId="164" fontId="1" fillId="7" borderId="3" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="7" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -1109,7 +1124,9 @@
     <col min="16" max="16" width="6" customWidth="1"/>
     <col min="17" max="17" width="7" customWidth="1"/>
     <col min="18" max="18" width="7" style="33" customWidth="1"/>
-    <col min="19" max="21" width="7" customWidth="1"/>
+    <col min="19" max="19" width="7" customWidth="1"/>
+    <col min="20" max="20" width="7" style="41" customWidth="1"/>
+    <col min="21" max="21" width="7" customWidth="1"/>
     <col min="22" max="22" width="15" customWidth="1"/>
     <col min="23" max="24" width="5" customWidth="1"/>
     <col min="25" max="29" width="6" customWidth="1"/>
@@ -1144,7 +1161,7 @@
       <c r="S1" s="34">
         <v>0.81</v>
       </c>
-      <c r="T1" s="1"/>
+      <c r="T1" s="35"/>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
       <c r="W1" s="1"/>
@@ -1198,7 +1215,7 @@
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
-      <c r="T2" s="1"/>
+      <c r="T2" s="35"/>
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
       <c r="W2" s="1"/>
@@ -1384,7 +1401,7 @@
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
-      <c r="T4" s="1"/>
+      <c r="T4" s="35"/>
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
       <c r="W4" s="1"/>
@@ -1482,7 +1499,7 @@
         <f t="shared" si="0"/>
         <v>21810.794000000005</v>
       </c>
-      <c r="T5" s="4">
+      <c r="T5" s="36">
         <f t="shared" si="0"/>
         <v>21937.200000000001</v>
       </c>
@@ -1534,7 +1551,10 @@
         <v>30.37539682539683</v>
       </c>
       <c r="AL5" s="1"/>
-      <c r="AM5" s="1"/>
+      <c r="AM5" s="4">
+        <f>SUM(AM6:AM500)</f>
+        <v>1802.9300000000005</v>
+      </c>
       <c r="AN5" s="1"/>
       <c r="AO5" s="1"/>
       <c r="AP5" s="1"/>
@@ -1595,7 +1615,7 @@
       <c r="Q6" s="16"/>
       <c r="R6" s="16"/>
       <c r="S6" s="16"/>
-      <c r="T6" s="16"/>
+      <c r="T6" s="37"/>
       <c r="U6" s="16"/>
       <c r="V6" s="14"/>
       <c r="W6" s="14">
@@ -1691,7 +1711,7 @@
       <c r="Q7" s="16"/>
       <c r="R7" s="16"/>
       <c r="S7" s="16"/>
-      <c r="T7" s="16"/>
+      <c r="T7" s="37"/>
       <c r="U7" s="16"/>
       <c r="V7" s="14"/>
       <c r="W7" s="14">
@@ -1787,7 +1807,7 @@
       <c r="Q8" s="16"/>
       <c r="R8" s="16"/>
       <c r="S8" s="16"/>
-      <c r="T8" s="16"/>
+      <c r="T8" s="37"/>
       <c r="U8" s="16"/>
       <c r="V8" s="14"/>
       <c r="W8" s="14">
@@ -1888,7 +1908,7 @@
         <f>R9*$S$1</f>
         <v>81.81</v>
       </c>
-      <c r="T9" s="5">
+      <c r="T9" s="38">
         <f t="shared" ref="T9:T44" si="5">AF9*AG9</f>
         <v>0</v>
       </c>
@@ -1944,7 +1964,10 @@
         <v>0</v>
       </c>
       <c r="AL9" s="1"/>
-      <c r="AM9" s="1"/>
+      <c r="AM9" s="1">
+        <f>P9*G9</f>
+        <v>1.1440000000000001</v>
+      </c>
       <c r="AN9" s="1"/>
       <c r="AO9" s="1"/>
       <c r="AP9" s="1"/>
@@ -2012,7 +2035,7 @@
         <f t="shared" ref="S10:S11" si="10">14*P10-F10</f>
         <v>157.59999999999997</v>
       </c>
-      <c r="T10" s="5">
+      <c r="T10" s="38">
         <f t="shared" si="5"/>
         <v>168</v>
       </c>
@@ -2070,7 +2093,10 @@
         <v>0.2</v>
       </c>
       <c r="AL10" s="1"/>
-      <c r="AM10" s="1"/>
+      <c r="AM10" s="1">
+        <f t="shared" ref="AM10:AM68" si="11">P10*G10</f>
+        <v>6.72</v>
+      </c>
       <c r="AN10" s="1"/>
       <c r="AO10" s="1"/>
       <c r="AP10" s="1"/>
@@ -2138,7 +2164,7 @@
         <f t="shared" si="10"/>
         <v>92</v>
       </c>
-      <c r="T11" s="5">
+      <c r="T11" s="38">
         <f t="shared" si="5"/>
         <v>84</v>
       </c>
@@ -2194,7 +2220,10 @@
         <v>0.1</v>
       </c>
       <c r="AL11" s="1"/>
-      <c r="AM11" s="1"/>
+      <c r="AM11" s="1">
+        <f t="shared" si="11"/>
+        <v>33.32</v>
+      </c>
       <c r="AN11" s="1"/>
       <c r="AO11" s="1"/>
       <c r="AP11" s="1"/>
@@ -2262,7 +2291,7 @@
         <f>R12*$S$1</f>
         <v>611.22600000000011</v>
       </c>
-      <c r="T12" s="5">
+      <c r="T12" s="38">
         <f t="shared" si="5"/>
         <v>672</v>
       </c>
@@ -2318,7 +2347,10 @@
         <v>0.8</v>
       </c>
       <c r="AL12" s="1"/>
-      <c r="AM12" s="1"/>
+      <c r="AM12" s="1">
+        <f t="shared" si="11"/>
+        <v>20.928000000000001</v>
+      </c>
       <c r="AN12" s="1"/>
       <c r="AO12" s="1"/>
       <c r="AP12" s="1"/>
@@ -2383,10 +2415,10 @@
         <v>1691</v>
       </c>
       <c r="S13" s="5">
-        <f t="shared" ref="S13:S15" si="11">R13*$S$1</f>
+        <f t="shared" ref="S13:S15" si="12">R13*$S$1</f>
         <v>1369.71</v>
       </c>
-      <c r="T13" s="5">
+      <c r="T13" s="38">
         <f t="shared" si="5"/>
         <v>1344</v>
       </c>
@@ -2442,7 +2474,10 @@
         <v>1.6</v>
       </c>
       <c r="AL13" s="1"/>
-      <c r="AM13" s="1"/>
+      <c r="AM13" s="1">
+        <f t="shared" si="11"/>
+        <v>44.879999999999995</v>
+      </c>
       <c r="AN13" s="1"/>
       <c r="AO13" s="1"/>
       <c r="AP13" s="1"/>
@@ -2507,10 +2542,10 @@
         <v>850.59999999999991</v>
       </c>
       <c r="S14" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>688.98599999999999</v>
       </c>
-      <c r="T14" s="5">
+      <c r="T14" s="38">
         <f t="shared" si="5"/>
         <v>672</v>
       </c>
@@ -2566,7 +2601,10 @@
         <v>0.8</v>
       </c>
       <c r="AL14" s="1"/>
-      <c r="AM14" s="1"/>
+      <c r="AM14" s="1">
+        <f t="shared" si="11"/>
+        <v>22.991999999999997</v>
+      </c>
       <c r="AN14" s="1"/>
       <c r="AO14" s="1"/>
       <c r="AP14" s="1"/>
@@ -2633,10 +2671,10 @@
         <v>1671.6000000000004</v>
       </c>
       <c r="S15" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1353.9960000000003</v>
       </c>
-      <c r="T15" s="5">
+      <c r="T15" s="38">
         <f t="shared" si="5"/>
         <v>1344</v>
       </c>
@@ -2692,7 +2730,10 @@
         <v>1.6</v>
       </c>
       <c r="AL15" s="1"/>
-      <c r="AM15" s="1"/>
+      <c r="AM15" s="1">
+        <f t="shared" si="11"/>
+        <v>58.512</v>
+      </c>
       <c r="AN15" s="1"/>
       <c r="AO15" s="1"/>
       <c r="AP15" s="1"/>
@@ -2753,7 +2794,7 @@
       <c r="Q16" s="5"/>
       <c r="R16" s="5"/>
       <c r="S16" s="5"/>
-      <c r="T16" s="5">
+      <c r="T16" s="38">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -2811,7 +2852,10 @@
         <v>0</v>
       </c>
       <c r="AL16" s="1"/>
-      <c r="AM16" s="1"/>
+      <c r="AM16" s="1">
+        <f t="shared" si="11"/>
+        <v>15.071999999999999</v>
+      </c>
       <c r="AN16" s="1"/>
       <c r="AO16" s="1"/>
       <c r="AP16" s="1"/>
@@ -2876,10 +2920,10 @@
         <v>638</v>
       </c>
       <c r="S17" s="5">
-        <f t="shared" ref="S17:S18" si="12">R17*$S$1</f>
+        <f t="shared" ref="S17:S18" si="13">R17*$S$1</f>
         <v>516.78000000000009</v>
       </c>
-      <c r="T17" s="5">
+      <c r="T17" s="38">
         <f t="shared" si="5"/>
         <v>672</v>
       </c>
@@ -2937,7 +2981,10 @@
         <v>0.22222222222222221</v>
       </c>
       <c r="AL17" s="1"/>
-      <c r="AM17" s="1"/>
+      <c r="AM17" s="1">
+        <f t="shared" si="11"/>
+        <v>6.5699999999999994</v>
+      </c>
       <c r="AN17" s="1"/>
       <c r="AO17" s="1"/>
       <c r="AP17" s="1"/>
@@ -3002,10 +3049,10 @@
         <v>709</v>
       </c>
       <c r="S18" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>574.29000000000008</v>
       </c>
-      <c r="T18" s="5">
+      <c r="T18" s="38">
         <f t="shared" si="5"/>
         <v>560</v>
       </c>
@@ -3063,7 +3110,10 @@
         <v>0.8</v>
       </c>
       <c r="AL18" s="1"/>
-      <c r="AM18" s="1"/>
+      <c r="AM18" s="1">
+        <f t="shared" si="11"/>
+        <v>37.44</v>
+      </c>
       <c r="AN18" s="1"/>
       <c r="AO18" s="1"/>
       <c r="AP18" s="1"/>
@@ -3122,7 +3172,7 @@
       <c r="Q19" s="16"/>
       <c r="R19" s="16"/>
       <c r="S19" s="16"/>
-      <c r="T19" s="16"/>
+      <c r="T19" s="37"/>
       <c r="U19" s="16"/>
       <c r="V19" s="14"/>
       <c r="W19" s="14">
@@ -3157,7 +3207,10 @@
       <c r="AJ19" s="14"/>
       <c r="AK19" s="17"/>
       <c r="AL19" s="1"/>
-      <c r="AM19" s="1"/>
+      <c r="AM19" s="1">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="AN19" s="1"/>
       <c r="AO19" s="1"/>
       <c r="AP19" s="1"/>
@@ -3220,7 +3273,7 @@
       <c r="Q20" s="5"/>
       <c r="R20" s="5"/>
       <c r="S20" s="5"/>
-      <c r="T20" s="5">
+      <c r="T20" s="38">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -3253,18 +3306,18 @@
         <v>61</v>
       </c>
       <c r="AE20" s="1">
-        <f t="shared" ref="AE20:AE25" si="13">G20*S20</f>
+        <f t="shared" ref="AE20:AE25" si="14">G20*S20</f>
         <v>0</v>
       </c>
       <c r="AF20" s="10">
         <v>12</v>
       </c>
       <c r="AG20" s="1">
-        <f t="shared" ref="AG20:AG25" si="14">MROUND(S20, AF20*AI20)/AF20</f>
+        <f t="shared" ref="AG20:AG25" si="15">MROUND(S20, AF20*AI20)/AF20</f>
         <v>0</v>
       </c>
       <c r="AH20" s="1">
-        <f t="shared" ref="AH20:AH25" si="15">AG20*AF20*G20</f>
+        <f t="shared" ref="AH20:AH25" si="16">AG20*AF20*G20</f>
         <v>0</v>
       </c>
       <c r="AI20" s="1">
@@ -3274,11 +3327,14 @@
         <v>70</v>
       </c>
       <c r="AK20" s="10">
-        <f t="shared" ref="AK20:AK25" si="16">AG20/AJ20</f>
+        <f t="shared" ref="AK20:AK25" si="17">AG20/AJ20</f>
         <v>0</v>
       </c>
       <c r="AL20" s="1"/>
-      <c r="AM20" s="1"/>
+      <c r="AM20" s="1">
+        <f t="shared" si="11"/>
+        <v>7.68</v>
+      </c>
       <c r="AN20" s="1"/>
       <c r="AO20" s="1"/>
       <c r="AP20" s="1"/>
@@ -3343,10 +3399,10 @@
         <v>157</v>
       </c>
       <c r="S21" s="5">
-        <f t="shared" ref="S21:S24" si="17">14*P21-F21</f>
+        <f t="shared" ref="S21:S24" si="18">14*P21-F21</f>
         <v>157</v>
       </c>
-      <c r="T21" s="5">
+      <c r="T21" s="38">
         <f t="shared" si="5"/>
         <v>168</v>
       </c>
@@ -3377,18 +3433,18 @@
       </c>
       <c r="AD21" s="1"/>
       <c r="AE21" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>31.400000000000002</v>
       </c>
       <c r="AF21" s="10">
         <v>12</v>
       </c>
       <c r="AG21" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>14</v>
       </c>
       <c r="AH21" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>33.6</v>
       </c>
       <c r="AI21" s="1">
@@ -3398,11 +3454,14 @@
         <v>70</v>
       </c>
       <c r="AK21" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.2</v>
       </c>
       <c r="AL21" s="1"/>
-      <c r="AM21" s="1"/>
+      <c r="AM21" s="1">
+        <f t="shared" si="11"/>
+        <v>16.600000000000001</v>
+      </c>
       <c r="AN21" s="1"/>
       <c r="AO21" s="1"/>
       <c r="AP21" s="1"/>
@@ -3465,10 +3524,10 @@
         <v>196</v>
       </c>
       <c r="S22" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>196</v>
       </c>
-      <c r="T22" s="5">
+      <c r="T22" s="38">
         <f t="shared" si="5"/>
         <v>180</v>
       </c>
@@ -3499,18 +3558,18 @@
       </c>
       <c r="AD22" s="1"/>
       <c r="AE22" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>196</v>
       </c>
       <c r="AF22" s="10">
         <v>5</v>
       </c>
       <c r="AG22" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>36</v>
       </c>
       <c r="AH22" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>180</v>
       </c>
       <c r="AI22" s="1">
@@ -3520,11 +3579,14 @@
         <v>84</v>
       </c>
       <c r="AK22" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.42857142857142855</v>
       </c>
       <c r="AL22" s="1"/>
-      <c r="AM22" s="1"/>
+      <c r="AM22" s="1">
+        <f t="shared" si="11"/>
+        <v>24</v>
+      </c>
       <c r="AN22" s="1"/>
       <c r="AO22" s="1"/>
       <c r="AP22" s="1"/>
@@ -3589,10 +3651,10 @@
         <v>190.09999999999997</v>
       </c>
       <c r="S23" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>190.09999999999997</v>
       </c>
-      <c r="T23" s="5">
+      <c r="T23" s="38">
         <f t="shared" si="5"/>
         <v>198</v>
       </c>
@@ -3623,18 +3685,18 @@
       </c>
       <c r="AD23" s="1"/>
       <c r="AE23" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>190.09999999999997</v>
       </c>
       <c r="AF23" s="10">
         <v>5.5</v>
       </c>
       <c r="AG23" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>36</v>
       </c>
       <c r="AH23" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>198</v>
       </c>
       <c r="AI23" s="1">
@@ -3644,11 +3706,14 @@
         <v>84</v>
       </c>
       <c r="AK23" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.42857142857142855</v>
       </c>
       <c r="AL23" s="1"/>
-      <c r="AM23" s="1"/>
+      <c r="AM23" s="1">
+        <f t="shared" si="11"/>
+        <v>32.9</v>
+      </c>
       <c r="AN23" s="1"/>
       <c r="AO23" s="1"/>
       <c r="AP23" s="1"/>
@@ -3713,10 +3778,10 @@
         <v>331.19999999999993</v>
       </c>
       <c r="S24" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>331.19999999999993</v>
       </c>
-      <c r="T24" s="5">
+      <c r="T24" s="38">
         <f t="shared" si="5"/>
         <v>336</v>
       </c>
@@ -3747,18 +3812,18 @@
       </c>
       <c r="AD24" s="1"/>
       <c r="AE24" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>331.19999999999993</v>
       </c>
       <c r="AF24" s="10">
         <v>3</v>
       </c>
       <c r="AG24" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>112</v>
       </c>
       <c r="AH24" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>336</v>
       </c>
       <c r="AI24" s="1">
@@ -3768,11 +3833,14 @@
         <v>126</v>
       </c>
       <c r="AK24" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.88888888888888884</v>
       </c>
       <c r="AL24" s="1"/>
-      <c r="AM24" s="1"/>
+      <c r="AM24" s="1">
+        <f t="shared" si="11"/>
+        <v>40.799999999999997</v>
+      </c>
       <c r="AN24" s="1"/>
       <c r="AO24" s="1"/>
       <c r="AP24" s="1"/>
@@ -3840,7 +3908,7 @@
         <f>R25*$S$1</f>
         <v>453.43799999999999</v>
       </c>
-      <c r="T25" s="5">
+      <c r="T25" s="38">
         <f t="shared" si="5"/>
         <v>420</v>
       </c>
@@ -3873,18 +3941,18 @@
         <v>49</v>
       </c>
       <c r="AE25" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>113.3595</v>
       </c>
       <c r="AF25" s="10">
         <v>6</v>
       </c>
       <c r="AG25" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>70</v>
       </c>
       <c r="AH25" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>105</v>
       </c>
       <c r="AI25" s="1">
@@ -3894,11 +3962,14 @@
         <v>140</v>
       </c>
       <c r="AK25" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.5</v>
       </c>
       <c r="AL25" s="1"/>
-      <c r="AM25" s="1"/>
+      <c r="AM25" s="1">
+        <f t="shared" si="11"/>
+        <v>16.45</v>
+      </c>
       <c r="AN25" s="1"/>
       <c r="AO25" s="1"/>
       <c r="AP25" s="1"/>
@@ -3953,7 +4024,7 @@
       <c r="Q26" s="16"/>
       <c r="R26" s="16"/>
       <c r="S26" s="16"/>
-      <c r="T26" s="16"/>
+      <c r="T26" s="37"/>
       <c r="U26" s="16"/>
       <c r="V26" s="14"/>
       <c r="W26" s="14" t="e">
@@ -3988,7 +4059,10 @@
       <c r="AJ26" s="14"/>
       <c r="AK26" s="17"/>
       <c r="AL26" s="1"/>
-      <c r="AM26" s="1"/>
+      <c r="AM26" s="1">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="AN26" s="1"/>
       <c r="AO26" s="1"/>
       <c r="AP26" s="1"/>
@@ -4049,7 +4123,7 @@
       <c r="Q27" s="5"/>
       <c r="R27" s="5"/>
       <c r="S27" s="5"/>
-      <c r="T27" s="5">
+      <c r="T27" s="38">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -4107,7 +4181,10 @@
         <v>0</v>
       </c>
       <c r="AL27" s="1"/>
-      <c r="AM27" s="1"/>
+      <c r="AM27" s="1">
+        <f t="shared" si="11"/>
+        <v>12.85</v>
+      </c>
       <c r="AN27" s="1"/>
       <c r="AO27" s="1"/>
       <c r="AP27" s="1"/>
@@ -4175,7 +4252,7 @@
         <f>R28*$S$1</f>
         <v>611.06399999999996</v>
       </c>
-      <c r="T28" s="5">
+      <c r="T28" s="38">
         <f t="shared" si="5"/>
         <v>576</v>
       </c>
@@ -4231,7 +4308,10 @@
         <v>1.1428571428571428</v>
       </c>
       <c r="AL28" s="1"/>
-      <c r="AM28" s="1"/>
+      <c r="AM28" s="1">
+        <f t="shared" si="11"/>
+        <v>100.6</v>
+      </c>
       <c r="AN28" s="1"/>
       <c r="AO28" s="1"/>
       <c r="AP28" s="1"/>
@@ -4292,7 +4372,7 @@
       <c r="Q29" s="5"/>
       <c r="R29" s="5"/>
       <c r="S29" s="5"/>
-      <c r="T29" s="5">
+      <c r="T29" s="38">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -4348,7 +4428,10 @@
         <v>0</v>
       </c>
       <c r="AL29" s="1"/>
-      <c r="AM29" s="1"/>
+      <c r="AM29" s="1">
+        <f t="shared" si="11"/>
+        <v>9.9819999999999993</v>
+      </c>
       <c r="AN29" s="1"/>
       <c r="AO29" s="1"/>
       <c r="AP29" s="1"/>
@@ -4413,10 +4496,10 @@
         <v>675.2</v>
       </c>
       <c r="S30" s="5">
-        <f t="shared" ref="S30:S31" si="18">R30*$S$1</f>
+        <f t="shared" ref="S30:S31" si="19">R30*$S$1</f>
         <v>546.91200000000003</v>
       </c>
-      <c r="T30" s="5">
+      <c r="T30" s="38">
         <f t="shared" si="5"/>
         <v>504</v>
       </c>
@@ -4474,7 +4557,10 @@
         <v>0.6</v>
       </c>
       <c r="AL30" s="1"/>
-      <c r="AM30" s="1"/>
+      <c r="AM30" s="1">
+        <f t="shared" si="11"/>
+        <v>27.95</v>
+      </c>
       <c r="AN30" s="1"/>
       <c r="AO30" s="1"/>
       <c r="AP30" s="1"/>
@@ -4539,10 +4625,10 @@
         <v>999.59999999999991</v>
       </c>
       <c r="S31" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>809.67599999999993</v>
       </c>
-      <c r="T31" s="5">
+      <c r="T31" s="38">
         <f t="shared" si="5"/>
         <v>840</v>
       </c>
@@ -4598,7 +4684,10 @@
         <v>1</v>
       </c>
       <c r="AL31" s="1"/>
-      <c r="AM31" s="1"/>
+      <c r="AM31" s="1">
+        <f t="shared" si="11"/>
+        <v>30.2</v>
+      </c>
       <c r="AN31" s="1"/>
       <c r="AO31" s="1"/>
       <c r="AP31" s="1"/>
@@ -4653,7 +4742,7 @@
       <c r="Q32" s="16"/>
       <c r="R32" s="16"/>
       <c r="S32" s="16"/>
-      <c r="T32" s="16"/>
+      <c r="T32" s="37"/>
       <c r="U32" s="16"/>
       <c r="V32" s="14"/>
       <c r="W32" s="14" t="e">
@@ -4688,7 +4777,10 @@
       <c r="AJ32" s="14"/>
       <c r="AK32" s="17"/>
       <c r="AL32" s="1"/>
-      <c r="AM32" s="1"/>
+      <c r="AM32" s="1">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="AN32" s="1"/>
       <c r="AO32" s="1"/>
       <c r="AP32" s="1"/>
@@ -4749,7 +4841,7 @@
       <c r="Q33" s="5"/>
       <c r="R33" s="5"/>
       <c r="S33" s="5"/>
-      <c r="T33" s="5">
+      <c r="T33" s="38">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -4780,18 +4872,18 @@
       </c>
       <c r="AD33" s="1"/>
       <c r="AE33" s="1">
-        <f t="shared" ref="AE33:AE44" si="19">G33*S33</f>
+        <f t="shared" ref="AE33:AE44" si="20">G33*S33</f>
         <v>0</v>
       </c>
       <c r="AF33" s="10">
         <v>12</v>
       </c>
       <c r="AG33" s="1">
-        <f t="shared" ref="AG33:AG44" si="20">MROUND(S33, AF33*AI33)/AF33</f>
+        <f t="shared" ref="AG33:AG44" si="21">MROUND(S33, AF33*AI33)/AF33</f>
         <v>0</v>
       </c>
       <c r="AH33" s="1">
-        <f t="shared" ref="AH33:AH44" si="21">AG33*AF33*G33</f>
+        <f t="shared" ref="AH33:AH44" si="22">AG33*AF33*G33</f>
         <v>0</v>
       </c>
       <c r="AI33" s="1">
@@ -4801,11 +4893,14 @@
         <v>70</v>
       </c>
       <c r="AK33" s="10">
-        <f t="shared" ref="AK33:AK44" si="22">AG33/AJ33</f>
+        <f t="shared" ref="AK33:AK44" si="23">AG33/AJ33</f>
         <v>0</v>
       </c>
       <c r="AL33" s="1"/>
-      <c r="AM33" s="1"/>
+      <c r="AM33" s="1">
+        <f t="shared" si="11"/>
+        <v>7.6</v>
+      </c>
       <c r="AN33" s="1"/>
       <c r="AO33" s="1"/>
       <c r="AP33" s="1"/>
@@ -4873,7 +4968,7 @@
         <f>9*P34-F34</f>
         <v>117.60000000000001</v>
       </c>
-      <c r="T34" s="5">
+      <c r="T34" s="38">
         <f t="shared" si="5"/>
         <v>168</v>
       </c>
@@ -4906,18 +5001,18 @@
         <v>49</v>
       </c>
       <c r="AE34" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>29.400000000000002</v>
       </c>
       <c r="AF34" s="10">
         <v>12</v>
       </c>
       <c r="AG34" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>14</v>
       </c>
       <c r="AH34" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>42</v>
       </c>
       <c r="AI34" s="1">
@@ -4927,11 +5022,14 @@
         <v>70</v>
       </c>
       <c r="AK34" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.2</v>
       </c>
       <c r="AL34" s="1"/>
-      <c r="AM34" s="1"/>
+      <c r="AM34" s="1">
+        <f t="shared" si="11"/>
+        <v>3.1</v>
+      </c>
       <c r="AN34" s="1"/>
       <c r="AO34" s="1"/>
       <c r="AP34" s="1"/>
@@ -4996,10 +5094,10 @@
         <v>170.40000000000003</v>
       </c>
       <c r="S35" s="5">
-        <f t="shared" ref="S35:S44" si="23">14*P35-F35</f>
+        <f t="shared" ref="S35:S44" si="24">14*P35-F35</f>
         <v>170.40000000000003</v>
       </c>
-      <c r="T35" s="5">
+      <c r="T35" s="38">
         <f t="shared" si="5"/>
         <v>192</v>
       </c>
@@ -5030,18 +5128,18 @@
       </c>
       <c r="AD35" s="1"/>
       <c r="AE35" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>119.28000000000002</v>
       </c>
       <c r="AF35" s="10">
         <v>8</v>
       </c>
       <c r="AG35" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>24</v>
       </c>
       <c r="AH35" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>134.39999999999998</v>
       </c>
       <c r="AI35" s="1">
@@ -5051,11 +5149,14 @@
         <v>84</v>
       </c>
       <c r="AK35" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.2857142857142857</v>
       </c>
       <c r="AL35" s="1"/>
-      <c r="AM35" s="1"/>
+      <c r="AM35" s="1">
+        <f t="shared" si="11"/>
+        <v>20.72</v>
+      </c>
       <c r="AN35" s="1"/>
       <c r="AO35" s="1"/>
       <c r="AP35" s="1"/>
@@ -5120,10 +5221,10 @@
         <v>184.59999999999997</v>
       </c>
       <c r="S36" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>184.59999999999997</v>
       </c>
-      <c r="T36" s="5">
+      <c r="T36" s="38">
         <f t="shared" si="5"/>
         <v>192</v>
       </c>
@@ -5154,18 +5255,18 @@
       </c>
       <c r="AD36" s="1"/>
       <c r="AE36" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>129.21999999999997</v>
       </c>
       <c r="AF36" s="10">
         <v>8</v>
       </c>
       <c r="AG36" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>24</v>
       </c>
       <c r="AH36" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>134.39999999999998</v>
       </c>
       <c r="AI36" s="1">
@@ -5175,11 +5276,14 @@
         <v>84</v>
       </c>
       <c r="AK36" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.2857142857142857</v>
       </c>
       <c r="AL36" s="1"/>
-      <c r="AM36" s="1"/>
+      <c r="AM36" s="1">
+        <f t="shared" si="11"/>
+        <v>19.179999999999996</v>
+      </c>
       <c r="AN36" s="1"/>
       <c r="AO36" s="1"/>
       <c r="AP36" s="1"/>
@@ -5244,10 +5348,10 @@
         <v>262.8</v>
       </c>
       <c r="S37" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>262.8</v>
       </c>
-      <c r="T37" s="5">
+      <c r="T37" s="38">
         <f t="shared" si="5"/>
         <v>288</v>
       </c>
@@ -5278,18 +5382,18 @@
       </c>
       <c r="AD37" s="1"/>
       <c r="AE37" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>183.96</v>
       </c>
       <c r="AF37" s="10">
         <v>8</v>
       </c>
       <c r="AG37" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>36</v>
       </c>
       <c r="AH37" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>201.6</v>
       </c>
       <c r="AI37" s="1">
@@ -5299,11 +5403,14 @@
         <v>84</v>
       </c>
       <c r="AK37" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.42857142857142855</v>
       </c>
       <c r="AL37" s="1"/>
-      <c r="AM37" s="1"/>
+      <c r="AM37" s="1">
+        <f t="shared" si="11"/>
+        <v>20.439999999999998</v>
+      </c>
       <c r="AN37" s="1"/>
       <c r="AO37" s="1"/>
       <c r="AP37" s="1"/>
@@ -5351,7 +5458,7 @@
         <v>142</v>
       </c>
       <c r="L38" s="1">
-        <f t="shared" ref="L38:L69" si="24">E38-K38</f>
+        <f t="shared" ref="L38:L69" si="25">E38-K38</f>
         <v>-25</v>
       </c>
       <c r="M38" s="1"/>
@@ -5364,7 +5471,7 @@
       <c r="Q38" s="5"/>
       <c r="R38" s="5"/>
       <c r="S38" s="5"/>
-      <c r="T38" s="5">
+      <c r="T38" s="38">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -5395,20 +5502,20 @@
       </c>
       <c r="AD38" s="1"/>
       <c r="AE38" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AF38" s="10">
         <v>10</v>
       </c>
       <c r="AG38" s="1">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AH38" s="1">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
+      <c r="AH38" s="1">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
       <c r="AI38" s="1">
         <v>12</v>
       </c>
@@ -5416,11 +5523,14 @@
         <v>84</v>
       </c>
       <c r="AK38" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AL38" s="1"/>
-      <c r="AM38" s="1"/>
+      <c r="AM38" s="1">
+        <f t="shared" si="11"/>
+        <v>16.38</v>
+      </c>
       <c r="AN38" s="1"/>
       <c r="AO38" s="1"/>
       <c r="AP38" s="1"/>
@@ -5468,7 +5578,7 @@
         <v>112</v>
       </c>
       <c r="L39" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-14</v>
       </c>
       <c r="M39" s="1"/>
@@ -5485,10 +5595,10 @@
         <v>153.40000000000003</v>
       </c>
       <c r="S39" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>153.40000000000003</v>
       </c>
-      <c r="T39" s="5">
+      <c r="T39" s="38">
         <f t="shared" si="5"/>
         <v>120</v>
       </c>
@@ -5519,18 +5629,18 @@
       </c>
       <c r="AD39" s="1"/>
       <c r="AE39" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>107.38000000000002</v>
       </c>
       <c r="AF39" s="10">
         <v>10</v>
       </c>
       <c r="AG39" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>12</v>
       </c>
       <c r="AH39" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>84</v>
       </c>
       <c r="AI39" s="1">
@@ -5540,11 +5650,14 @@
         <v>84</v>
       </c>
       <c r="AK39" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.14285714285714285</v>
       </c>
       <c r="AL39" s="1"/>
-      <c r="AM39" s="1"/>
+      <c r="AM39" s="1">
+        <f t="shared" si="11"/>
+        <v>13.72</v>
+      </c>
       <c r="AN39" s="1"/>
       <c r="AO39" s="1"/>
       <c r="AP39" s="1"/>
@@ -5592,7 +5705,7 @@
         <v>217</v>
       </c>
       <c r="L40" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-4</v>
       </c>
       <c r="M40" s="1"/>
@@ -5612,7 +5725,7 @@
         <f>13*P40-F40</f>
         <v>385.80000000000007</v>
       </c>
-      <c r="T40" s="5">
+      <c r="T40" s="38">
         <f t="shared" si="5"/>
         <v>360</v>
       </c>
@@ -5645,18 +5758,18 @@
         <v>49</v>
       </c>
       <c r="AE40" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>270.06</v>
       </c>
       <c r="AF40" s="10">
         <v>10</v>
       </c>
       <c r="AG40" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>36</v>
       </c>
       <c r="AH40" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>251.99999999999997</v>
       </c>
       <c r="AI40" s="1">
@@ -5666,11 +5779,14 @@
         <v>84</v>
       </c>
       <c r="AK40" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.42857142857142855</v>
       </c>
       <c r="AL40" s="1"/>
-      <c r="AM40" s="1"/>
+      <c r="AM40" s="1">
+        <f t="shared" si="11"/>
+        <v>29.82</v>
+      </c>
       <c r="AN40" s="1"/>
       <c r="AO40" s="1"/>
       <c r="AP40" s="1"/>
@@ -5718,7 +5834,7 @@
         <v>104</v>
       </c>
       <c r="L41" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-10</v>
       </c>
       <c r="M41" s="1"/>
@@ -5735,10 +5851,10 @@
         <v>131.19999999999999</v>
       </c>
       <c r="S41" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>131.19999999999999</v>
       </c>
-      <c r="T41" s="5">
+      <c r="T41" s="38">
         <f t="shared" si="5"/>
         <v>120</v>
       </c>
@@ -5769,18 +5885,18 @@
       </c>
       <c r="AD41" s="1"/>
       <c r="AE41" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>91.839999999999989</v>
       </c>
       <c r="AF41" s="10">
         <v>10</v>
       </c>
       <c r="AG41" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>12</v>
       </c>
       <c r="AH41" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>84</v>
       </c>
       <c r="AI41" s="1">
@@ -5790,11 +5906,14 @@
         <v>84</v>
       </c>
       <c r="AK41" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.14285714285714285</v>
       </c>
       <c r="AL41" s="1"/>
-      <c r="AM41" s="1"/>
+      <c r="AM41" s="1">
+        <f t="shared" si="11"/>
+        <v>13.16</v>
+      </c>
       <c r="AN41" s="1"/>
       <c r="AO41" s="1"/>
       <c r="AP41" s="1"/>
@@ -5842,7 +5961,7 @@
         <v>385</v>
       </c>
       <c r="L42" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-25</v>
       </c>
       <c r="M42" s="1"/>
@@ -5859,10 +5978,10 @@
         <v>348</v>
       </c>
       <c r="S42" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>348</v>
       </c>
-      <c r="T42" s="5">
+      <c r="T42" s="38">
         <f t="shared" si="5"/>
         <v>360</v>
       </c>
@@ -5895,18 +6014,18 @@
         <v>49</v>
       </c>
       <c r="AE42" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>348</v>
       </c>
       <c r="AF42" s="10">
         <v>5</v>
       </c>
       <c r="AG42" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>72</v>
       </c>
       <c r="AH42" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>360</v>
       </c>
       <c r="AI42" s="1">
@@ -5916,11 +6035,14 @@
         <v>144</v>
       </c>
       <c r="AK42" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.5</v>
       </c>
       <c r="AL42" s="1"/>
-      <c r="AM42" s="1"/>
+      <c r="AM42" s="1">
+        <f t="shared" si="11"/>
+        <v>72</v>
+      </c>
       <c r="AN42" s="1"/>
       <c r="AO42" s="1"/>
       <c r="AP42" s="1"/>
@@ -5966,7 +6088,7 @@
         <v>306</v>
       </c>
       <c r="L43" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>3</v>
       </c>
       <c r="M43" s="1"/>
@@ -5986,7 +6108,7 @@
         <f>R43*$S$1</f>
         <v>469.31400000000002</v>
       </c>
-      <c r="T43" s="5">
+      <c r="T43" s="38">
         <f t="shared" si="5"/>
         <v>384</v>
       </c>
@@ -6017,18 +6139,18 @@
       </c>
       <c r="AD43" s="1"/>
       <c r="AE43" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>187.72560000000001</v>
       </c>
       <c r="AF43" s="10">
         <v>16</v>
       </c>
       <c r="AG43" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>24</v>
       </c>
       <c r="AH43" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>153.60000000000002</v>
       </c>
       <c r="AI43" s="1">
@@ -6038,11 +6160,14 @@
         <v>84</v>
       </c>
       <c r="AK43" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.2857142857142857</v>
       </c>
       <c r="AL43" s="1"/>
-      <c r="AM43" s="1"/>
+      <c r="AM43" s="1">
+        <f t="shared" si="11"/>
+        <v>24.72</v>
+      </c>
       <c r="AN43" s="1"/>
       <c r="AO43" s="1"/>
       <c r="AP43" s="1"/>
@@ -6090,7 +6215,7 @@
         <v>338</v>
       </c>
       <c r="L44" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-11</v>
       </c>
       <c r="M44" s="1"/>
@@ -6107,10 +6232,10 @@
         <v>464.60000000000014</v>
       </c>
       <c r="S44" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>464.60000000000014</v>
       </c>
-      <c r="T44" s="5">
+      <c r="T44" s="38">
         <f t="shared" si="5"/>
         <v>480</v>
       </c>
@@ -6143,18 +6268,18 @@
         <v>49</v>
       </c>
       <c r="AE44" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>325.22000000000008</v>
       </c>
       <c r="AF44" s="10">
         <v>10</v>
       </c>
       <c r="AG44" s="1">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>48</v>
       </c>
       <c r="AH44" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>336</v>
       </c>
       <c r="AI44" s="1">
@@ -6164,11 +6289,14 @@
         <v>84</v>
       </c>
       <c r="AK44" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.5714285714285714</v>
       </c>
       <c r="AL44" s="1"/>
-      <c r="AM44" s="1"/>
+      <c r="AM44" s="1">
+        <f t="shared" si="11"/>
+        <v>45.78</v>
+      </c>
       <c r="AN44" s="1"/>
       <c r="AO44" s="1"/>
       <c r="AP44" s="1"/>
@@ -6210,7 +6338,7 @@
       </c>
       <c r="K45" s="14"/>
       <c r="L45" s="14">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
       <c r="M45" s="14"/>
@@ -6223,7 +6351,7 @@
       <c r="Q45" s="16"/>
       <c r="R45" s="16"/>
       <c r="S45" s="16"/>
-      <c r="T45" s="16"/>
+      <c r="T45" s="37"/>
       <c r="U45" s="16"/>
       <c r="V45" s="14"/>
       <c r="W45" s="14">
@@ -6248,7 +6376,10 @@
       <c r="AJ45" s="14"/>
       <c r="AK45" s="17"/>
       <c r="AL45" s="1"/>
-      <c r="AM45" s="1"/>
+      <c r="AM45" s="1">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="AN45" s="1"/>
       <c r="AO45" s="1"/>
       <c r="AP45" s="1"/>
@@ -6298,7 +6429,7 @@
         <v>181</v>
       </c>
       <c r="L46" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-12</v>
       </c>
       <c r="M46" s="1"/>
@@ -6315,11 +6446,11 @@
         <v>201.19999999999993</v>
       </c>
       <c r="S46" s="5">
-        <f t="shared" ref="S46:S59" si="25">14*P46-F46</f>
+        <f t="shared" ref="S46:S59" si="26">14*P46-F46</f>
         <v>201.19999999999993</v>
       </c>
-      <c r="T46" s="5">
-        <f t="shared" ref="T46:T68" si="26">AF46*AG46</f>
+      <c r="T46" s="38">
+        <f t="shared" ref="T46:T68" si="27">AF46*AG46</f>
         <v>192</v>
       </c>
       <c r="U46" s="5"/>
@@ -6349,18 +6480,18 @@
       </c>
       <c r="AD46" s="1"/>
       <c r="AE46" s="1">
-        <f t="shared" ref="AE46:AE68" si="27">G46*S46</f>
+        <f t="shared" ref="AE46:AE68" si="28">G46*S46</f>
         <v>80.479999999999976</v>
       </c>
       <c r="AF46" s="10">
         <v>16</v>
       </c>
       <c r="AG46" s="1">
-        <f t="shared" ref="AG46:AG68" si="28">MROUND(S46, AF46*AI46)/AF46</f>
+        <f t="shared" ref="AG46:AG68" si="29">MROUND(S46, AF46*AI46)/AF46</f>
         <v>12</v>
       </c>
       <c r="AH46" s="1">
-        <f t="shared" ref="AH46:AH68" si="29">AG46*AF46*G46</f>
+        <f t="shared" ref="AH46:AH68" si="30">AG46*AF46*G46</f>
         <v>76.800000000000011</v>
       </c>
       <c r="AI46" s="1">
@@ -6370,11 +6501,14 @@
         <v>84</v>
       </c>
       <c r="AK46" s="10">
-        <f t="shared" ref="AK46:AK68" si="30">AG46/AJ46</f>
+        <f t="shared" ref="AK46:AK68" si="31">AG46/AJ46</f>
         <v>0.14285714285714285</v>
       </c>
       <c r="AL46" s="1"/>
-      <c r="AM46" s="1"/>
+      <c r="AM46" s="1">
+        <f t="shared" si="11"/>
+        <v>13.52</v>
+      </c>
       <c r="AN46" s="1"/>
       <c r="AO46" s="1"/>
       <c r="AP46" s="1"/>
@@ -6424,7 +6558,7 @@
         <v>409</v>
       </c>
       <c r="L47" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>78</v>
       </c>
       <c r="M47" s="1"/>
@@ -6444,8 +6578,8 @@
         <f>R47*$S$1</f>
         <v>425.73600000000016</v>
       </c>
-      <c r="T47" s="5">
-        <f t="shared" si="26"/>
+      <c r="T47" s="38">
+        <f t="shared" si="27"/>
         <v>480</v>
       </c>
       <c r="U47" s="5"/>
@@ -6475,18 +6609,18 @@
       </c>
       <c r="AD47" s="1"/>
       <c r="AE47" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>298.01520000000011</v>
       </c>
       <c r="AF47" s="10">
         <v>10</v>
       </c>
       <c r="AG47" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>48</v>
       </c>
       <c r="AH47" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>336</v>
       </c>
       <c r="AI47" s="1">
@@ -6496,11 +6630,14 @@
         <v>84</v>
       </c>
       <c r="AK47" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.5714285714285714</v>
       </c>
       <c r="AL47" s="1"/>
-      <c r="AM47" s="1"/>
+      <c r="AM47" s="1">
+        <f t="shared" si="11"/>
+        <v>68.179999999999993</v>
+      </c>
       <c r="AN47" s="1"/>
       <c r="AO47" s="1"/>
       <c r="AP47" s="1"/>
@@ -6548,7 +6685,7 @@
         <v>153</v>
       </c>
       <c r="L48" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-2</v>
       </c>
       <c r="M48" s="1"/>
@@ -6568,8 +6705,8 @@
         <f>11*P48-F48</f>
         <v>274.2</v>
       </c>
-      <c r="T48" s="5">
-        <f t="shared" si="26"/>
+      <c r="T48" s="38">
+        <f t="shared" si="27"/>
         <v>240</v>
       </c>
       <c r="U48" s="5"/>
@@ -6599,18 +6736,18 @@
       </c>
       <c r="AD48" s="1"/>
       <c r="AE48" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>191.93999999999997</v>
       </c>
       <c r="AF48" s="10">
         <v>10</v>
       </c>
       <c r="AG48" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>24</v>
       </c>
       <c r="AH48" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>168</v>
       </c>
       <c r="AI48" s="1">
@@ -6620,11 +6757,14 @@
         <v>84</v>
       </c>
       <c r="AK48" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.2857142857142857</v>
       </c>
       <c r="AL48" s="1"/>
-      <c r="AM48" s="1"/>
+      <c r="AM48" s="1">
+        <f t="shared" si="11"/>
+        <v>21.139999999999997</v>
+      </c>
       <c r="AN48" s="1"/>
       <c r="AO48" s="1"/>
       <c r="AP48" s="1"/>
@@ -6672,7 +6812,7 @@
         <v>673</v>
       </c>
       <c r="L49" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-204</v>
       </c>
       <c r="M49" s="1"/>
@@ -6689,11 +6829,11 @@
         <v>337.20000000000005</v>
       </c>
       <c r="S49" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>337.20000000000005</v>
       </c>
-      <c r="T49" s="5">
-        <f t="shared" si="26"/>
+      <c r="T49" s="38">
+        <f t="shared" si="27"/>
         <v>360</v>
       </c>
       <c r="U49" s="5"/>
@@ -6723,18 +6863,18 @@
       </c>
       <c r="AD49" s="1"/>
       <c r="AE49" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>337.20000000000005</v>
       </c>
       <c r="AF49" s="10">
         <v>5</v>
       </c>
       <c r="AG49" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>72</v>
       </c>
       <c r="AH49" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>360</v>
       </c>
       <c r="AI49" s="1">
@@ -6744,11 +6884,14 @@
         <v>84</v>
       </c>
       <c r="AK49" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.8571428571428571</v>
       </c>
       <c r="AL49" s="1"/>
-      <c r="AM49" s="1"/>
+      <c r="AM49" s="1">
+        <f t="shared" si="11"/>
+        <v>93.8</v>
+      </c>
       <c r="AN49" s="1"/>
       <c r="AO49" s="1"/>
       <c r="AP49" s="1"/>
@@ -6796,7 +6939,7 @@
         <v>224</v>
       </c>
       <c r="L50" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-23</v>
       </c>
       <c r="M50" s="1"/>
@@ -6813,11 +6956,11 @@
         <v>321.80000000000007</v>
       </c>
       <c r="S50" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>321.80000000000007</v>
       </c>
-      <c r="T50" s="5">
-        <f t="shared" si="26"/>
+      <c r="T50" s="38">
+        <f t="shared" si="27"/>
         <v>288</v>
       </c>
       <c r="U50" s="5"/>
@@ -6849,18 +6992,18 @@
         <v>49</v>
       </c>
       <c r="AE50" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>289.62000000000006</v>
       </c>
       <c r="AF50" s="10">
         <v>8</v>
       </c>
       <c r="AG50" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>36</v>
       </c>
       <c r="AH50" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>259.2</v>
       </c>
       <c r="AI50" s="1">
@@ -6870,11 +7013,14 @@
         <v>84</v>
       </c>
       <c r="AK50" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.42857142857142855</v>
       </c>
       <c r="AL50" s="1"/>
-      <c r="AM50" s="1"/>
+      <c r="AM50" s="1">
+        <f t="shared" si="11"/>
+        <v>36.180000000000007</v>
+      </c>
       <c r="AN50" s="1"/>
       <c r="AO50" s="1"/>
       <c r="AP50" s="1"/>
@@ -6922,7 +7068,7 @@
         <v>106</v>
       </c>
       <c r="L51" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-33</v>
       </c>
       <c r="M51" s="1"/>
@@ -6942,8 +7088,8 @@
         <f>16*P51-F51</f>
         <v>69.599999999999994</v>
       </c>
-      <c r="T51" s="5">
-        <f t="shared" si="26"/>
+      <c r="T51" s="38">
+        <f t="shared" si="27"/>
         <v>96</v>
       </c>
       <c r="U51" s="5"/>
@@ -6975,18 +7121,18 @@
         <v>49</v>
       </c>
       <c r="AE51" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>62.639999999999993</v>
       </c>
       <c r="AF51" s="10">
         <v>8</v>
       </c>
       <c r="AG51" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>12</v>
       </c>
       <c r="AH51" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>86.4</v>
       </c>
       <c r="AI51" s="1">
@@ -6996,11 +7142,14 @@
         <v>84</v>
       </c>
       <c r="AK51" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.14285714285714285</v>
       </c>
       <c r="AL51" s="1"/>
-      <c r="AM51" s="1"/>
+      <c r="AM51" s="1">
+        <f t="shared" si="11"/>
+        <v>13.14</v>
+      </c>
       <c r="AN51" s="1"/>
       <c r="AO51" s="1"/>
       <c r="AP51" s="1"/>
@@ -7048,7 +7197,7 @@
         <v>360</v>
       </c>
       <c r="L52" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-15</v>
       </c>
       <c r="M52" s="1"/>
@@ -7065,11 +7214,11 @@
         <v>426</v>
       </c>
       <c r="S52" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>426</v>
       </c>
-      <c r="T52" s="5">
-        <f t="shared" si="26"/>
+      <c r="T52" s="38">
+        <f t="shared" si="27"/>
         <v>420</v>
       </c>
       <c r="U52" s="5"/>
@@ -7099,18 +7248,18 @@
       </c>
       <c r="AD52" s="1"/>
       <c r="AE52" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>426</v>
       </c>
       <c r="AF52" s="10">
         <v>5</v>
       </c>
       <c r="AG52" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>84</v>
       </c>
       <c r="AH52" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>420</v>
       </c>
       <c r="AI52" s="1">
@@ -7120,11 +7269,14 @@
         <v>144</v>
       </c>
       <c r="AK52" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.58333333333333337</v>
       </c>
       <c r="AL52" s="1"/>
-      <c r="AM52" s="1"/>
+      <c r="AM52" s="1">
+        <f t="shared" si="11"/>
+        <v>69</v>
+      </c>
       <c r="AN52" s="1"/>
       <c r="AO52" s="1"/>
       <c r="AP52" s="1"/>
@@ -7172,7 +7324,7 @@
         <v>470.4</v>
       </c>
       <c r="L53" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>3.1000000000000227</v>
       </c>
       <c r="M53" s="1"/>
@@ -7192,8 +7344,8 @@
         <f>R53*$S$1</f>
         <v>718.47</v>
       </c>
-      <c r="T53" s="5">
-        <f t="shared" si="26"/>
+      <c r="T53" s="38">
+        <f t="shared" si="27"/>
         <v>725.2</v>
       </c>
       <c r="U53" s="5"/>
@@ -7223,18 +7375,18 @@
       </c>
       <c r="AD53" s="1"/>
       <c r="AE53" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>718.47</v>
       </c>
       <c r="AF53" s="10">
         <v>3.7</v>
       </c>
       <c r="AG53" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>196</v>
       </c>
       <c r="AH53" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>725.2</v>
       </c>
       <c r="AI53" s="1">
@@ -7244,11 +7396,14 @@
         <v>126</v>
       </c>
       <c r="AK53" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>1.5555555555555556</v>
       </c>
       <c r="AL53" s="1"/>
-      <c r="AM53" s="1"/>
+      <c r="AM53" s="1">
+        <f t="shared" si="11"/>
+        <v>94.7</v>
+      </c>
       <c r="AN53" s="1"/>
       <c r="AO53" s="1"/>
       <c r="AP53" s="1"/>
@@ -7296,7 +7451,7 @@
         <v>249</v>
       </c>
       <c r="L54" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-10</v>
       </c>
       <c r="M54" s="1"/>
@@ -7309,8 +7464,8 @@
       <c r="Q54" s="5"/>
       <c r="R54" s="5"/>
       <c r="S54" s="5"/>
-      <c r="T54" s="5">
-        <f t="shared" si="26"/>
+      <c r="T54" s="38">
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="U54" s="5"/>
@@ -7342,20 +7497,20 @@
         <v>135</v>
       </c>
       <c r="AE54" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AF54" s="10">
         <v>30</v>
       </c>
       <c r="AG54" s="1">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="AH54" s="1">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
+      <c r="AH54" s="1">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
       <c r="AI54" s="1">
         <v>14</v>
       </c>
@@ -7363,11 +7518,14 @@
         <v>126</v>
       </c>
       <c r="AK54" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AL54" s="1"/>
-      <c r="AM54" s="1"/>
+      <c r="AM54" s="1">
+        <f t="shared" si="11"/>
+        <v>4.3019999999999996</v>
+      </c>
       <c r="AN54" s="1"/>
       <c r="AO54" s="1"/>
       <c r="AP54" s="1"/>
@@ -7415,7 +7573,7 @@
         <v>183</v>
       </c>
       <c r="L55" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-20</v>
       </c>
       <c r="M55" s="1"/>
@@ -7435,8 +7593,8 @@
         <f>11*P55-F55</f>
         <v>306.60000000000002</v>
       </c>
-      <c r="T55" s="5">
-        <f t="shared" si="26"/>
+      <c r="T55" s="38">
+        <f t="shared" si="27"/>
         <v>336</v>
       </c>
       <c r="U55" s="5"/>
@@ -7466,18 +7624,18 @@
       </c>
       <c r="AD55" s="1"/>
       <c r="AE55" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>70.518000000000015</v>
       </c>
       <c r="AF55" s="10">
         <v>6</v>
       </c>
       <c r="AG55" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>56</v>
       </c>
       <c r="AH55" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>77.28</v>
       </c>
       <c r="AI55" s="1">
@@ -7487,11 +7645,14 @@
         <v>140</v>
       </c>
       <c r="AK55" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.4</v>
       </c>
       <c r="AL55" s="1"/>
-      <c r="AM55" s="1"/>
+      <c r="AM55" s="1">
+        <f t="shared" si="11"/>
+        <v>7.4980000000000002</v>
+      </c>
       <c r="AN55" s="1"/>
       <c r="AO55" s="1"/>
       <c r="AP55" s="1"/>
@@ -7539,7 +7700,7 @@
         <v>699</v>
       </c>
       <c r="L56" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>6</v>
       </c>
       <c r="M56" s="1"/>
@@ -7559,8 +7720,8 @@
         <f>R56*$S$1</f>
         <v>520.02</v>
       </c>
-      <c r="T56" s="5">
-        <f t="shared" si="26"/>
+      <c r="T56" s="38">
+        <f t="shared" si="27"/>
         <v>504</v>
       </c>
       <c r="U56" s="5"/>
@@ -7592,18 +7753,18 @@
         <v>49</v>
       </c>
       <c r="AE56" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>130.005</v>
       </c>
       <c r="AF56" s="10">
         <v>12</v>
       </c>
       <c r="AG56" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>42</v>
       </c>
       <c r="AH56" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>126</v>
       </c>
       <c r="AI56" s="1">
@@ -7613,11 +7774,14 @@
         <v>70</v>
       </c>
       <c r="AK56" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.6</v>
       </c>
       <c r="AL56" s="1"/>
-      <c r="AM56" s="1"/>
+      <c r="AM56" s="1">
+        <f t="shared" si="11"/>
+        <v>35.25</v>
+      </c>
       <c r="AN56" s="1"/>
       <c r="AO56" s="1"/>
       <c r="AP56" s="1"/>
@@ -7665,7 +7829,7 @@
         <v>359</v>
       </c>
       <c r="L57" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-6</v>
       </c>
       <c r="M57" s="1"/>
@@ -7682,11 +7846,11 @@
         <v>122.39999999999986</v>
       </c>
       <c r="S57" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>122.39999999999986</v>
       </c>
-      <c r="T57" s="5">
-        <f t="shared" si="26"/>
+      <c r="T57" s="38">
+        <f t="shared" si="27"/>
         <v>168</v>
       </c>
       <c r="U57" s="5"/>
@@ -7716,18 +7880,18 @@
       </c>
       <c r="AD57" s="1"/>
       <c r="AE57" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>30.599999999999966</v>
       </c>
       <c r="AF57" s="10">
         <v>12</v>
       </c>
       <c r="AG57" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>14</v>
       </c>
       <c r="AH57" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>42</v>
       </c>
       <c r="AI57" s="1">
@@ -7737,11 +7901,14 @@
         <v>70</v>
       </c>
       <c r="AK57" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.2</v>
       </c>
       <c r="AL57" s="1"/>
-      <c r="AM57" s="1"/>
+      <c r="AM57" s="1">
+        <f t="shared" si="11"/>
+        <v>17.649999999999999</v>
+      </c>
       <c r="AN57" s="1"/>
       <c r="AO57" s="1"/>
       <c r="AP57" s="1"/>
@@ -7785,7 +7952,7 @@
         <v>36</v>
       </c>
       <c r="L58" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="M58" s="1"/>
@@ -7798,8 +7965,8 @@
       <c r="Q58" s="5"/>
       <c r="R58" s="5"/>
       <c r="S58" s="5"/>
-      <c r="T58" s="5">
-        <f t="shared" si="26"/>
+      <c r="T58" s="38">
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="U58" s="5"/>
@@ -7829,20 +7996,20 @@
       </c>
       <c r="AD58" s="1"/>
       <c r="AE58" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AF58" s="10">
         <v>6</v>
       </c>
       <c r="AG58" s="1">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="AH58" s="1">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
+      <c r="AH58" s="1">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
       <c r="AI58" s="1">
         <v>14</v>
       </c>
@@ -7850,11 +8017,14 @@
         <v>140</v>
       </c>
       <c r="AK58" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AL58" s="1"/>
-      <c r="AM58" s="1"/>
+      <c r="AM58" s="1">
+        <f t="shared" si="11"/>
+        <v>1.296</v>
+      </c>
       <c r="AN58" s="1"/>
       <c r="AO58" s="1"/>
       <c r="AP58" s="1"/>
@@ -7898,7 +8068,7 @@
         <v>48</v>
       </c>
       <c r="L59" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="M59" s="1"/>
@@ -7915,11 +8085,11 @@
         <v>67.400000000000006</v>
       </c>
       <c r="S59" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>67.400000000000006</v>
       </c>
-      <c r="T59" s="5">
-        <f t="shared" si="26"/>
+      <c r="T59" s="38">
+        <f t="shared" si="27"/>
         <v>84</v>
       </c>
       <c r="U59" s="5"/>
@@ -7949,18 +8119,18 @@
       </c>
       <c r="AD59" s="1"/>
       <c r="AE59" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>12.132000000000001</v>
       </c>
       <c r="AF59" s="10">
         <v>6</v>
       </c>
       <c r="AG59" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>14</v>
       </c>
       <c r="AH59" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>15.12</v>
       </c>
       <c r="AI59" s="1">
@@ -7970,11 +8140,14 @@
         <v>140</v>
       </c>
       <c r="AK59" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.1</v>
       </c>
       <c r="AL59" s="1"/>
-      <c r="AM59" s="1"/>
+      <c r="AM59" s="1">
+        <f t="shared" si="11"/>
+        <v>1.728</v>
+      </c>
       <c r="AN59" s="1"/>
       <c r="AO59" s="1"/>
       <c r="AP59" s="1"/>
@@ -8010,7 +8183,7 @@
       <c r="J60" s="1"/>
       <c r="K60" s="1"/>
       <c r="L60" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="M60" s="1"/>
@@ -8030,8 +8203,8 @@
         <f>6*14</f>
         <v>84</v>
       </c>
-      <c r="T60" s="5">
-        <f t="shared" si="26"/>
+      <c r="T60" s="38">
+        <f t="shared" si="27"/>
         <v>84</v>
       </c>
       <c r="U60" s="32">
@@ -8063,18 +8236,18 @@
       </c>
       <c r="AD60" s="1"/>
       <c r="AE60" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>15.12</v>
       </c>
       <c r="AF60" s="10">
         <v>6</v>
       </c>
       <c r="AG60" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>14</v>
       </c>
       <c r="AH60" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>15.12</v>
       </c>
       <c r="AI60" s="1">
@@ -8084,11 +8257,14 @@
         <v>140</v>
       </c>
       <c r="AK60" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.1</v>
       </c>
       <c r="AL60" s="1"/>
-      <c r="AM60" s="1"/>
+      <c r="AM60" s="1">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="AN60" s="1"/>
       <c r="AO60" s="1"/>
       <c r="AP60" s="1"/>
@@ -8136,7 +8312,7 @@
         <v>634</v>
       </c>
       <c r="L61" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>5</v>
       </c>
       <c r="M61" s="1"/>
@@ -8156,8 +8332,8 @@
         <f>R61*$S$1</f>
         <v>749.41200000000003</v>
       </c>
-      <c r="T61" s="5">
-        <f t="shared" si="26"/>
+      <c r="T61" s="38">
+        <f t="shared" si="27"/>
         <v>672</v>
       </c>
       <c r="U61" s="5"/>
@@ -8189,18 +8365,18 @@
         <v>49</v>
       </c>
       <c r="AE61" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>224.8236</v>
       </c>
       <c r="AF61" s="10">
         <v>12</v>
       </c>
       <c r="AG61" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>56</v>
       </c>
       <c r="AH61" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>201.6</v>
       </c>
       <c r="AI61" s="1">
@@ -8210,11 +8386,14 @@
         <v>70</v>
       </c>
       <c r="AK61" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.8</v>
       </c>
       <c r="AL61" s="1"/>
-      <c r="AM61" s="1"/>
+      <c r="AM61" s="1">
+        <f t="shared" si="11"/>
+        <v>38.339999999999996</v>
+      </c>
       <c r="AN61" s="1"/>
       <c r="AO61" s="1"/>
       <c r="AP61" s="1"/>
@@ -8262,7 +8441,7 @@
         <v>419</v>
       </c>
       <c r="L62" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>2</v>
       </c>
       <c r="M62" s="1"/>
@@ -8275,8 +8454,8 @@
       <c r="Q62" s="5"/>
       <c r="R62" s="5"/>
       <c r="S62" s="5"/>
-      <c r="T62" s="5">
-        <f t="shared" si="26"/>
+      <c r="T62" s="38">
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="U62" s="5"/>
@@ -8308,20 +8487,20 @@
         <v>49</v>
       </c>
       <c r="AE62" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AF62" s="10">
         <v>12</v>
       </c>
       <c r="AG62" s="1">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="AH62" s="1">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
+      <c r="AH62" s="1">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
       <c r="AI62" s="1">
         <v>14</v>
       </c>
@@ -8329,11 +8508,14 @@
         <v>70</v>
       </c>
       <c r="AK62" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AL62" s="1"/>
-      <c r="AM62" s="1"/>
+      <c r="AM62" s="1">
+        <f t="shared" si="11"/>
+        <v>25.26</v>
+      </c>
       <c r="AN62" s="1"/>
       <c r="AO62" s="1"/>
       <c r="AP62" s="1"/>
@@ -8381,7 +8563,7 @@
         <v>127</v>
       </c>
       <c r="L63" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>2</v>
       </c>
       <c r="M63" s="1"/>
@@ -8394,8 +8576,8 @@
       <c r="Q63" s="5"/>
       <c r="R63" s="5"/>
       <c r="S63" s="5"/>
-      <c r="T63" s="5">
-        <f t="shared" si="26"/>
+      <c r="T63" s="38">
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="U63" s="5"/>
@@ -8427,20 +8609,20 @@
         <v>49</v>
       </c>
       <c r="AE63" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AF63" s="10">
         <v>14</v>
       </c>
       <c r="AG63" s="1">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="AH63" s="1">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
+      <c r="AH63" s="1">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
       <c r="AI63" s="1">
         <v>14</v>
       </c>
@@ -8448,11 +8630,14 @@
         <v>70</v>
       </c>
       <c r="AK63" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AL63" s="1"/>
-      <c r="AM63" s="1"/>
+      <c r="AM63" s="1">
+        <f t="shared" si="11"/>
+        <v>7.74</v>
+      </c>
       <c r="AN63" s="1"/>
       <c r="AO63" s="1"/>
       <c r="AP63" s="1"/>
@@ -8500,7 +8685,7 @@
         <v>1900</v>
       </c>
       <c r="L64" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-27</v>
       </c>
       <c r="M64" s="1"/>
@@ -8517,11 +8702,11 @@
         <v>3018</v>
       </c>
       <c r="S64" s="5">
-        <f t="shared" ref="S64:S66" si="31">R64*$S$1</f>
+        <f t="shared" ref="S64:S66" si="32">R64*$S$1</f>
         <v>2444.5800000000004</v>
       </c>
-      <c r="T64" s="5">
-        <f t="shared" si="26"/>
+      <c r="T64" s="38">
+        <f t="shared" si="27"/>
         <v>2520</v>
       </c>
       <c r="U64" s="5"/>
@@ -8553,18 +8738,18 @@
         <v>49</v>
       </c>
       <c r="AE64" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>611.1450000000001</v>
       </c>
       <c r="AF64" s="10">
         <v>12</v>
       </c>
       <c r="AG64" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>210</v>
       </c>
       <c r="AH64" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>630</v>
       </c>
       <c r="AI64" s="1">
@@ -8574,11 +8759,14 @@
         <v>70</v>
       </c>
       <c r="AK64" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>3</v>
       </c>
       <c r="AL64" s="1"/>
-      <c r="AM64" s="1"/>
+      <c r="AM64" s="1">
+        <f t="shared" si="11"/>
+        <v>93.65</v>
+      </c>
       <c r="AN64" s="1"/>
       <c r="AO64" s="1"/>
       <c r="AP64" s="1"/>
@@ -8628,7 +8816,7 @@
         <v>1677</v>
       </c>
       <c r="L65" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>83</v>
       </c>
       <c r="M65" s="1"/>
@@ -8645,11 +8833,11 @@
         <v>1622</v>
       </c>
       <c r="S65" s="5">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>1313.8200000000002</v>
       </c>
-      <c r="T65" s="5">
-        <f t="shared" si="26"/>
+      <c r="T65" s="38">
+        <f t="shared" si="27"/>
         <v>1344</v>
       </c>
       <c r="U65" s="5"/>
@@ -8681,18 +8869,18 @@
         <v>49</v>
       </c>
       <c r="AE65" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>328.45500000000004</v>
       </c>
       <c r="AF65" s="10">
         <v>12</v>
       </c>
       <c r="AG65" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>112</v>
       </c>
       <c r="AH65" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>336</v>
       </c>
       <c r="AI65" s="1">
@@ -8702,11 +8890,14 @@
         <v>70</v>
       </c>
       <c r="AK65" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>1.6</v>
       </c>
       <c r="AL65" s="1"/>
-      <c r="AM65" s="1"/>
+      <c r="AM65" s="1">
+        <f t="shared" si="11"/>
+        <v>88</v>
+      </c>
       <c r="AN65" s="1"/>
       <c r="AO65" s="1"/>
       <c r="AP65" s="1"/>
@@ -8754,7 +8945,7 @@
         <v>336</v>
       </c>
       <c r="L66" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-5</v>
       </c>
       <c r="M66" s="1"/>
@@ -8771,11 +8962,11 @@
         <v>614.40000000000009</v>
       </c>
       <c r="S66" s="5">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>497.6640000000001</v>
       </c>
-      <c r="T66" s="5">
-        <f t="shared" si="26"/>
+      <c r="T66" s="38">
+        <f t="shared" si="27"/>
         <v>504</v>
       </c>
       <c r="U66" s="5"/>
@@ -8805,18 +8996,18 @@
       </c>
       <c r="AD66" s="1"/>
       <c r="AE66" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>114.46272000000003</v>
       </c>
       <c r="AF66" s="10">
         <v>6</v>
       </c>
       <c r="AG66" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>84</v>
       </c>
       <c r="AH66" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>115.92</v>
       </c>
       <c r="AI66" s="1">
@@ -8826,11 +9017,14 @@
         <v>140</v>
       </c>
       <c r="AK66" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.6</v>
       </c>
       <c r="AL66" s="1"/>
-      <c r="AM66" s="1"/>
+      <c r="AM66" s="1">
+        <f t="shared" si="11"/>
+        <v>15.226000000000001</v>
+      </c>
       <c r="AN66" s="1"/>
       <c r="AO66" s="1"/>
       <c r="AP66" s="1"/>
@@ -8878,7 +9072,7 @@
         <v>198.2</v>
       </c>
       <c r="L67" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>12.400000000000006</v>
       </c>
       <c r="M67" s="1"/>
@@ -8898,8 +9092,8 @@
         <f>11*P67-F67</f>
         <v>377.72</v>
       </c>
-      <c r="T67" s="5">
-        <f t="shared" si="26"/>
+      <c r="T67" s="38">
+        <f t="shared" si="27"/>
         <v>378</v>
       </c>
       <c r="U67" s="5"/>
@@ -8929,18 +9123,18 @@
       </c>
       <c r="AD67" s="1"/>
       <c r="AE67" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>377.72</v>
       </c>
       <c r="AF67" s="10">
         <v>2.7</v>
       </c>
       <c r="AG67" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>140</v>
       </c>
       <c r="AH67" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>378</v>
       </c>
       <c r="AI67" s="1">
@@ -8950,11 +9144,14 @@
         <v>126</v>
       </c>
       <c r="AK67" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>1.1111111111111112</v>
       </c>
       <c r="AL67" s="1"/>
-      <c r="AM67" s="1"/>
+      <c r="AM67" s="1">
+        <f t="shared" si="11"/>
+        <v>42.12</v>
+      </c>
       <c r="AN67" s="1"/>
       <c r="AO67" s="1"/>
       <c r="AP67" s="1"/>
@@ -9004,7 +9201,7 @@
         <v>840</v>
       </c>
       <c r="L68" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-35</v>
       </c>
       <c r="M68" s="1"/>
@@ -9024,8 +9221,8 @@
         <f>R68*$S$1</f>
         <v>1123.47</v>
       </c>
-      <c r="T68" s="5">
-        <f t="shared" si="26"/>
+      <c r="T68" s="38">
+        <f t="shared" si="27"/>
         <v>1140</v>
       </c>
       <c r="U68" s="5"/>
@@ -9055,18 +9252,18 @@
       </c>
       <c r="AD68" s="1"/>
       <c r="AE68" s="1">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>1123.47</v>
       </c>
       <c r="AF68" s="10">
         <v>5</v>
       </c>
       <c r="AG68" s="1">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>228</v>
       </c>
       <c r="AH68" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1140</v>
       </c>
       <c r="AI68" s="1">
@@ -9076,11 +9273,14 @@
         <v>84</v>
       </c>
       <c r="AK68" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>2.7142857142857144</v>
       </c>
       <c r="AL68" s="1"/>
-      <c r="AM68" s="1"/>
+      <c r="AM68" s="1">
+        <f t="shared" si="11"/>
+        <v>161</v>
+      </c>
       <c r="AN68" s="1"/>
       <c r="AO68" s="1"/>
       <c r="AP68" s="1"/>
@@ -9128,7 +9328,7 @@
         <v>5</v>
       </c>
       <c r="L69" s="14">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="M69" s="14"/>
@@ -9141,7 +9341,7 @@
       <c r="Q69" s="25"/>
       <c r="R69" s="25"/>
       <c r="S69" s="25"/>
-      <c r="T69" s="25"/>
+      <c r="T69" s="39"/>
       <c r="U69" s="25"/>
       <c r="V69" s="14"/>
       <c r="W69" s="14">
@@ -9217,7 +9417,7 @@
       <c r="Q70" s="28"/>
       <c r="R70" s="28"/>
       <c r="S70" s="28"/>
-      <c r="T70" s="28"/>
+      <c r="T70" s="40"/>
       <c r="U70" s="31">
         <v>100</v>
       </c>
@@ -9283,7 +9483,7 @@
       <c r="Q71" s="28"/>
       <c r="R71" s="28"/>
       <c r="S71" s="28"/>
-      <c r="T71" s="28"/>
+      <c r="T71" s="40"/>
       <c r="U71" s="31">
         <v>100</v>
       </c>
@@ -9355,7 +9555,7 @@
       <c r="Q72" s="28"/>
       <c r="R72" s="28"/>
       <c r="S72" s="28"/>
-      <c r="T72" s="28"/>
+      <c r="T72" s="40"/>
       <c r="U72" s="31">
         <v>100</v>
       </c>
@@ -9421,7 +9621,7 @@
       <c r="Q73" s="1"/>
       <c r="R73" s="1"/>
       <c r="S73" s="1"/>
-      <c r="T73" s="1"/>
+      <c r="T73" s="35"/>
       <c r="U73" s="1"/>
       <c r="V73" s="1"/>
       <c r="W73" s="1"/>
@@ -9475,7 +9675,7 @@
       <c r="Q74" s="1"/>
       <c r="R74" s="1"/>
       <c r="S74" s="1"/>
-      <c r="T74" s="1"/>
+      <c r="T74" s="35"/>
       <c r="U74" s="1"/>
       <c r="V74" s="1"/>
       <c r="W74" s="1"/>
@@ -9529,7 +9729,7 @@
       <c r="Q75" s="1"/>
       <c r="R75" s="1"/>
       <c r="S75" s="1"/>
-      <c r="T75" s="1"/>
+      <c r="T75" s="35"/>
       <c r="U75" s="1"/>
       <c r="V75" s="1"/>
       <c r="W75" s="1"/>
@@ -9583,7 +9783,7 @@
       <c r="Q76" s="1"/>
       <c r="R76" s="1"/>
       <c r="S76" s="1"/>
-      <c r="T76" s="1"/>
+      <c r="T76" s="35"/>
       <c r="U76" s="1"/>
       <c r="V76" s="1"/>
       <c r="W76" s="1"/>
@@ -9637,7 +9837,7 @@
       <c r="Q77" s="1"/>
       <c r="R77" s="1"/>
       <c r="S77" s="1"/>
-      <c r="T77" s="1"/>
+      <c r="T77" s="35"/>
       <c r="U77" s="1"/>
       <c r="V77" s="1"/>
       <c r="W77" s="1"/>
@@ -9691,7 +9891,7 @@
       <c r="Q78" s="1"/>
       <c r="R78" s="1"/>
       <c r="S78" s="1"/>
-      <c r="T78" s="1"/>
+      <c r="T78" s="35"/>
       <c r="U78" s="1"/>
       <c r="V78" s="1"/>
       <c r="W78" s="1"/>
@@ -9745,7 +9945,7 @@
       <c r="Q79" s="1"/>
       <c r="R79" s="1"/>
       <c r="S79" s="1"/>
-      <c r="T79" s="1"/>
+      <c r="T79" s="35"/>
       <c r="U79" s="1"/>
       <c r="V79" s="1"/>
       <c r="W79" s="1"/>
@@ -9799,7 +9999,7 @@
       <c r="Q80" s="1"/>
       <c r="R80" s="1"/>
       <c r="S80" s="1"/>
-      <c r="T80" s="1"/>
+      <c r="T80" s="35"/>
       <c r="U80" s="1"/>
       <c r="V80" s="1"/>
       <c r="W80" s="1"/>
@@ -9853,7 +10053,7 @@
       <c r="Q81" s="1"/>
       <c r="R81" s="1"/>
       <c r="S81" s="1"/>
-      <c r="T81" s="1"/>
+      <c r="T81" s="35"/>
       <c r="U81" s="1"/>
       <c r="V81" s="1"/>
       <c r="W81" s="1"/>
@@ -9907,7 +10107,7 @@
       <c r="Q82" s="1"/>
       <c r="R82" s="1"/>
       <c r="S82" s="1"/>
-      <c r="T82" s="1"/>
+      <c r="T82" s="35"/>
       <c r="U82" s="1"/>
       <c r="V82" s="1"/>
       <c r="W82" s="1"/>
@@ -9961,7 +10161,7 @@
       <c r="Q83" s="1"/>
       <c r="R83" s="1"/>
       <c r="S83" s="1"/>
-      <c r="T83" s="1"/>
+      <c r="T83" s="35"/>
       <c r="U83" s="1"/>
       <c r="V83" s="1"/>
       <c r="W83" s="1"/>
@@ -10015,7 +10215,7 @@
       <c r="Q84" s="1"/>
       <c r="R84" s="1"/>
       <c r="S84" s="1"/>
-      <c r="T84" s="1"/>
+      <c r="T84" s="35"/>
       <c r="U84" s="1"/>
       <c r="V84" s="1"/>
       <c r="W84" s="1"/>
@@ -10069,7 +10269,7 @@
       <c r="Q85" s="1"/>
       <c r="R85" s="1"/>
       <c r="S85" s="1"/>
-      <c r="T85" s="1"/>
+      <c r="T85" s="35"/>
       <c r="U85" s="1"/>
       <c r="V85" s="1"/>
       <c r="W85" s="1"/>
@@ -10123,7 +10323,7 @@
       <c r="Q86" s="1"/>
       <c r="R86" s="1"/>
       <c r="S86" s="1"/>
-      <c r="T86" s="1"/>
+      <c r="T86" s="35"/>
       <c r="U86" s="1"/>
       <c r="V86" s="1"/>
       <c r="W86" s="1"/>
@@ -10177,7 +10377,7 @@
       <c r="Q87" s="1"/>
       <c r="R87" s="1"/>
       <c r="S87" s="1"/>
-      <c r="T87" s="1"/>
+      <c r="T87" s="35"/>
       <c r="U87" s="1"/>
       <c r="V87" s="1"/>
       <c r="W87" s="1"/>
@@ -10231,7 +10431,7 @@
       <c r="Q88" s="1"/>
       <c r="R88" s="1"/>
       <c r="S88" s="1"/>
-      <c r="T88" s="1"/>
+      <c r="T88" s="35"/>
       <c r="U88" s="1"/>
       <c r="V88" s="1"/>
       <c r="W88" s="1"/>
@@ -10285,7 +10485,7 @@
       <c r="Q89" s="1"/>
       <c r="R89" s="1"/>
       <c r="S89" s="1"/>
-      <c r="T89" s="1"/>
+      <c r="T89" s="35"/>
       <c r="U89" s="1"/>
       <c r="V89" s="1"/>
       <c r="W89" s="1"/>
@@ -10339,7 +10539,7 @@
       <c r="Q90" s="1"/>
       <c r="R90" s="1"/>
       <c r="S90" s="1"/>
-      <c r="T90" s="1"/>
+      <c r="T90" s="35"/>
       <c r="U90" s="1"/>
       <c r="V90" s="1"/>
       <c r="W90" s="1"/>
@@ -10393,7 +10593,7 @@
       <c r="Q91" s="1"/>
       <c r="R91" s="1"/>
       <c r="S91" s="1"/>
-      <c r="T91" s="1"/>
+      <c r="T91" s="35"/>
       <c r="U91" s="1"/>
       <c r="V91" s="1"/>
       <c r="W91" s="1"/>
@@ -10447,7 +10647,7 @@
       <c r="Q92" s="1"/>
       <c r="R92" s="1"/>
       <c r="S92" s="1"/>
-      <c r="T92" s="1"/>
+      <c r="T92" s="35"/>
       <c r="U92" s="1"/>
       <c r="V92" s="1"/>
       <c r="W92" s="1"/>
@@ -10501,7 +10701,7 @@
       <c r="Q93" s="1"/>
       <c r="R93" s="1"/>
       <c r="S93" s="1"/>
-      <c r="T93" s="1"/>
+      <c r="T93" s="35"/>
       <c r="U93" s="1"/>
       <c r="V93" s="1"/>
       <c r="W93" s="1"/>
@@ -10555,7 +10755,7 @@
       <c r="Q94" s="1"/>
       <c r="R94" s="1"/>
       <c r="S94" s="1"/>
-      <c r="T94" s="1"/>
+      <c r="T94" s="35"/>
       <c r="U94" s="1"/>
       <c r="V94" s="1"/>
       <c r="W94" s="1"/>
@@ -10609,7 +10809,7 @@
       <c r="Q95" s="1"/>
       <c r="R95" s="1"/>
       <c r="S95" s="1"/>
-      <c r="T95" s="1"/>
+      <c r="T95" s="35"/>
       <c r="U95" s="1"/>
       <c r="V95" s="1"/>
       <c r="W95" s="1"/>
@@ -10663,7 +10863,7 @@
       <c r="Q96" s="1"/>
       <c r="R96" s="1"/>
       <c r="S96" s="1"/>
-      <c r="T96" s="1"/>
+      <c r="T96" s="35"/>
       <c r="U96" s="1"/>
       <c r="V96" s="1"/>
       <c r="W96" s="1"/>
@@ -10717,7 +10917,7 @@
       <c r="Q97" s="1"/>
       <c r="R97" s="1"/>
       <c r="S97" s="1"/>
-      <c r="T97" s="1"/>
+      <c r="T97" s="35"/>
       <c r="U97" s="1"/>
       <c r="V97" s="1"/>
       <c r="W97" s="1"/>
@@ -10771,7 +10971,7 @@
       <c r="Q98" s="1"/>
       <c r="R98" s="1"/>
       <c r="S98" s="1"/>
-      <c r="T98" s="1"/>
+      <c r="T98" s="35"/>
       <c r="U98" s="1"/>
       <c r="V98" s="1"/>
       <c r="W98" s="1"/>
@@ -10825,7 +11025,7 @@
       <c r="Q99" s="1"/>
       <c r="R99" s="1"/>
       <c r="S99" s="1"/>
-      <c r="T99" s="1"/>
+      <c r="T99" s="35"/>
       <c r="U99" s="1"/>
       <c r="V99" s="1"/>
       <c r="W99" s="1"/>
@@ -10879,7 +11079,7 @@
       <c r="Q100" s="1"/>
       <c r="R100" s="1"/>
       <c r="S100" s="1"/>
-      <c r="T100" s="1"/>
+      <c r="T100" s="35"/>
       <c r="U100" s="1"/>
       <c r="V100" s="1"/>
       <c r="W100" s="1"/>
@@ -10933,7 +11133,7 @@
       <c r="Q101" s="1"/>
       <c r="R101" s="1"/>
       <c r="S101" s="1"/>
-      <c r="T101" s="1"/>
+      <c r="T101" s="35"/>
       <c r="U101" s="1"/>
       <c r="V101" s="1"/>
       <c r="W101" s="1"/>
@@ -10987,7 +11187,7 @@
       <c r="Q102" s="1"/>
       <c r="R102" s="1"/>
       <c r="S102" s="1"/>
-      <c r="T102" s="1"/>
+      <c r="T102" s="35"/>
       <c r="U102" s="1"/>
       <c r="V102" s="1"/>
       <c r="W102" s="1"/>
@@ -11041,7 +11241,7 @@
       <c r="Q103" s="1"/>
       <c r="R103" s="1"/>
       <c r="S103" s="1"/>
-      <c r="T103" s="1"/>
+      <c r="T103" s="35"/>
       <c r="U103" s="1"/>
       <c r="V103" s="1"/>
       <c r="W103" s="1"/>
@@ -11095,7 +11295,7 @@
       <c r="Q104" s="1"/>
       <c r="R104" s="1"/>
       <c r="S104" s="1"/>
-      <c r="T104" s="1"/>
+      <c r="T104" s="35"/>
       <c r="U104" s="1"/>
       <c r="V104" s="1"/>
       <c r="W104" s="1"/>
@@ -11149,7 +11349,7 @@
       <c r="Q105" s="1"/>
       <c r="R105" s="1"/>
       <c r="S105" s="1"/>
-      <c r="T105" s="1"/>
+      <c r="T105" s="35"/>
       <c r="U105" s="1"/>
       <c r="V105" s="1"/>
       <c r="W105" s="1"/>
@@ -11203,7 +11403,7 @@
       <c r="Q106" s="1"/>
       <c r="R106" s="1"/>
       <c r="S106" s="1"/>
-      <c r="T106" s="1"/>
+      <c r="T106" s="35"/>
       <c r="U106" s="1"/>
       <c r="V106" s="1"/>
       <c r="W106" s="1"/>
@@ -11257,7 +11457,7 @@
       <c r="Q107" s="1"/>
       <c r="R107" s="1"/>
       <c r="S107" s="1"/>
-      <c r="T107" s="1"/>
+      <c r="T107" s="35"/>
       <c r="U107" s="1"/>
       <c r="V107" s="1"/>
       <c r="W107" s="1"/>
@@ -11311,7 +11511,7 @@
       <c r="Q108" s="1"/>
       <c r="R108" s="1"/>
       <c r="S108" s="1"/>
-      <c r="T108" s="1"/>
+      <c r="T108" s="35"/>
       <c r="U108" s="1"/>
       <c r="V108" s="1"/>
       <c r="W108" s="1"/>
@@ -11365,7 +11565,7 @@
       <c r="Q109" s="1"/>
       <c r="R109" s="1"/>
       <c r="S109" s="1"/>
-      <c r="T109" s="1"/>
+      <c r="T109" s="35"/>
       <c r="U109" s="1"/>
       <c r="V109" s="1"/>
       <c r="W109" s="1"/>
@@ -11419,7 +11619,7 @@
       <c r="Q110" s="1"/>
       <c r="R110" s="1"/>
       <c r="S110" s="1"/>
-      <c r="T110" s="1"/>
+      <c r="T110" s="35"/>
       <c r="U110" s="1"/>
       <c r="V110" s="1"/>
       <c r="W110" s="1"/>
@@ -11473,7 +11673,7 @@
       <c r="Q111" s="1"/>
       <c r="R111" s="1"/>
       <c r="S111" s="1"/>
-      <c r="T111" s="1"/>
+      <c r="T111" s="35"/>
       <c r="U111" s="1"/>
       <c r="V111" s="1"/>
       <c r="W111" s="1"/>
@@ -11527,7 +11727,7 @@
       <c r="Q112" s="1"/>
       <c r="R112" s="1"/>
       <c r="S112" s="1"/>
-      <c r="T112" s="1"/>
+      <c r="T112" s="35"/>
       <c r="U112" s="1"/>
       <c r="V112" s="1"/>
       <c r="W112" s="1"/>
@@ -11581,7 +11781,7 @@
       <c r="Q113" s="1"/>
       <c r="R113" s="1"/>
       <c r="S113" s="1"/>
-      <c r="T113" s="1"/>
+      <c r="T113" s="35"/>
       <c r="U113" s="1"/>
       <c r="V113" s="1"/>
       <c r="W113" s="1"/>
@@ -11635,7 +11835,7 @@
       <c r="Q114" s="1"/>
       <c r="R114" s="1"/>
       <c r="S114" s="1"/>
-      <c r="T114" s="1"/>
+      <c r="T114" s="35"/>
       <c r="U114" s="1"/>
       <c r="V114" s="1"/>
       <c r="W114" s="1"/>
@@ -11689,7 +11889,7 @@
       <c r="Q115" s="1"/>
       <c r="R115" s="1"/>
       <c r="S115" s="1"/>
-      <c r="T115" s="1"/>
+      <c r="T115" s="35"/>
       <c r="U115" s="1"/>
       <c r="V115" s="1"/>
       <c r="W115" s="1"/>
@@ -11743,7 +11943,7 @@
       <c r="Q116" s="1"/>
       <c r="R116" s="1"/>
       <c r="S116" s="1"/>
-      <c r="T116" s="1"/>
+      <c r="T116" s="35"/>
       <c r="U116" s="1"/>
       <c r="V116" s="1"/>
       <c r="W116" s="1"/>
@@ -11797,7 +11997,7 @@
       <c r="Q117" s="1"/>
       <c r="R117" s="1"/>
       <c r="S117" s="1"/>
-      <c r="T117" s="1"/>
+      <c r="T117" s="35"/>
       <c r="U117" s="1"/>
       <c r="V117" s="1"/>
       <c r="W117" s="1"/>
@@ -11851,7 +12051,7 @@
       <c r="Q118" s="1"/>
       <c r="R118" s="1"/>
       <c r="S118" s="1"/>
-      <c r="T118" s="1"/>
+      <c r="T118" s="35"/>
       <c r="U118" s="1"/>
       <c r="V118" s="1"/>
       <c r="W118" s="1"/>
@@ -11905,7 +12105,7 @@
       <c r="Q119" s="1"/>
       <c r="R119" s="1"/>
       <c r="S119" s="1"/>
-      <c r="T119" s="1"/>
+      <c r="T119" s="35"/>
       <c r="U119" s="1"/>
       <c r="V119" s="1"/>
       <c r="W119" s="1"/>
@@ -11959,7 +12159,7 @@
       <c r="Q120" s="1"/>
       <c r="R120" s="1"/>
       <c r="S120" s="1"/>
-      <c r="T120" s="1"/>
+      <c r="T120" s="35"/>
       <c r="U120" s="1"/>
       <c r="V120" s="1"/>
       <c r="W120" s="1"/>
@@ -12013,7 +12213,7 @@
       <c r="Q121" s="1"/>
       <c r="R121" s="1"/>
       <c r="S121" s="1"/>
-      <c r="T121" s="1"/>
+      <c r="T121" s="35"/>
       <c r="U121" s="1"/>
       <c r="V121" s="1"/>
       <c r="W121" s="1"/>
@@ -12067,7 +12267,7 @@
       <c r="Q122" s="1"/>
       <c r="R122" s="1"/>
       <c r="S122" s="1"/>
-      <c r="T122" s="1"/>
+      <c r="T122" s="35"/>
       <c r="U122" s="1"/>
       <c r="V122" s="1"/>
       <c r="W122" s="1"/>
@@ -12121,7 +12321,7 @@
       <c r="Q123" s="1"/>
       <c r="R123" s="1"/>
       <c r="S123" s="1"/>
-      <c r="T123" s="1"/>
+      <c r="T123" s="35"/>
       <c r="U123" s="1"/>
       <c r="V123" s="1"/>
       <c r="W123" s="1"/>
@@ -12175,7 +12375,7 @@
       <c r="Q124" s="1"/>
       <c r="R124" s="1"/>
       <c r="S124" s="1"/>
-      <c r="T124" s="1"/>
+      <c r="T124" s="35"/>
       <c r="U124" s="1"/>
       <c r="V124" s="1"/>
       <c r="W124" s="1"/>
@@ -12229,7 +12429,7 @@
       <c r="Q125" s="1"/>
       <c r="R125" s="1"/>
       <c r="S125" s="1"/>
-      <c r="T125" s="1"/>
+      <c r="T125" s="35"/>
       <c r="U125" s="1"/>
       <c r="V125" s="1"/>
       <c r="W125" s="1"/>
@@ -12283,7 +12483,7 @@
       <c r="Q126" s="1"/>
       <c r="R126" s="1"/>
       <c r="S126" s="1"/>
-      <c r="T126" s="1"/>
+      <c r="T126" s="35"/>
       <c r="U126" s="1"/>
       <c r="V126" s="1"/>
       <c r="W126" s="1"/>
@@ -12337,7 +12537,7 @@
       <c r="Q127" s="1"/>
       <c r="R127" s="1"/>
       <c r="S127" s="1"/>
-      <c r="T127" s="1"/>
+      <c r="T127" s="35"/>
       <c r="U127" s="1"/>
       <c r="V127" s="1"/>
       <c r="W127" s="1"/>
@@ -12391,7 +12591,7 @@
       <c r="Q128" s="1"/>
       <c r="R128" s="1"/>
       <c r="S128" s="1"/>
-      <c r="T128" s="1"/>
+      <c r="T128" s="35"/>
       <c r="U128" s="1"/>
       <c r="V128" s="1"/>
       <c r="W128" s="1"/>
@@ -12445,7 +12645,7 @@
       <c r="Q129" s="1"/>
       <c r="R129" s="1"/>
       <c r="S129" s="1"/>
-      <c r="T129" s="1"/>
+      <c r="T129" s="35"/>
       <c r="U129" s="1"/>
       <c r="V129" s="1"/>
       <c r="W129" s="1"/>
@@ -12499,7 +12699,7 @@
       <c r="Q130" s="1"/>
       <c r="R130" s="1"/>
       <c r="S130" s="1"/>
-      <c r="T130" s="1"/>
+      <c r="T130" s="35"/>
       <c r="U130" s="1"/>
       <c r="V130" s="1"/>
       <c r="W130" s="1"/>
@@ -12553,7 +12753,7 @@
       <c r="Q131" s="1"/>
       <c r="R131" s="1"/>
       <c r="S131" s="1"/>
-      <c r="T131" s="1"/>
+      <c r="T131" s="35"/>
       <c r="U131" s="1"/>
       <c r="V131" s="1"/>
       <c r="W131" s="1"/>
@@ -12607,7 +12807,7 @@
       <c r="Q132" s="1"/>
       <c r="R132" s="1"/>
       <c r="S132" s="1"/>
-      <c r="T132" s="1"/>
+      <c r="T132" s="35"/>
       <c r="U132" s="1"/>
       <c r="V132" s="1"/>
       <c r="W132" s="1"/>
@@ -12661,7 +12861,7 @@
       <c r="Q133" s="1"/>
       <c r="R133" s="1"/>
       <c r="S133" s="1"/>
-      <c r="T133" s="1"/>
+      <c r="T133" s="35"/>
       <c r="U133" s="1"/>
       <c r="V133" s="1"/>
       <c r="W133" s="1"/>
@@ -12715,7 +12915,7 @@
       <c r="Q134" s="1"/>
       <c r="R134" s="1"/>
       <c r="S134" s="1"/>
-      <c r="T134" s="1"/>
+      <c r="T134" s="35"/>
       <c r="U134" s="1"/>
       <c r="V134" s="1"/>
       <c r="W134" s="1"/>
@@ -12769,7 +12969,7 @@
       <c r="Q135" s="1"/>
       <c r="R135" s="1"/>
       <c r="S135" s="1"/>
-      <c r="T135" s="1"/>
+      <c r="T135" s="35"/>
       <c r="U135" s="1"/>
       <c r="V135" s="1"/>
       <c r="W135" s="1"/>
@@ -12823,7 +13023,7 @@
       <c r="Q136" s="1"/>
       <c r="R136" s="1"/>
       <c r="S136" s="1"/>
-      <c r="T136" s="1"/>
+      <c r="T136" s="35"/>
       <c r="U136" s="1"/>
       <c r="V136" s="1"/>
       <c r="W136" s="1"/>
@@ -12877,7 +13077,7 @@
       <c r="Q137" s="1"/>
       <c r="R137" s="1"/>
       <c r="S137" s="1"/>
-      <c r="T137" s="1"/>
+      <c r="T137" s="35"/>
       <c r="U137" s="1"/>
       <c r="V137" s="1"/>
       <c r="W137" s="1"/>
@@ -12931,7 +13131,7 @@
       <c r="Q138" s="1"/>
       <c r="R138" s="1"/>
       <c r="S138" s="1"/>
-      <c r="T138" s="1"/>
+      <c r="T138" s="35"/>
       <c r="U138" s="1"/>
       <c r="V138" s="1"/>
       <c r="W138" s="1"/>
@@ -12985,7 +13185,7 @@
       <c r="Q139" s="1"/>
       <c r="R139" s="1"/>
       <c r="S139" s="1"/>
-      <c r="T139" s="1"/>
+      <c r="T139" s="35"/>
       <c r="U139" s="1"/>
       <c r="V139" s="1"/>
       <c r="W139" s="1"/>
@@ -13039,7 +13239,7 @@
       <c r="Q140" s="1"/>
       <c r="R140" s="1"/>
       <c r="S140" s="1"/>
-      <c r="T140" s="1"/>
+      <c r="T140" s="35"/>
       <c r="U140" s="1"/>
       <c r="V140" s="1"/>
       <c r="W140" s="1"/>
@@ -13093,7 +13293,7 @@
       <c r="Q141" s="1"/>
       <c r="R141" s="1"/>
       <c r="S141" s="1"/>
-      <c r="T141" s="1"/>
+      <c r="T141" s="35"/>
       <c r="U141" s="1"/>
       <c r="V141" s="1"/>
       <c r="W141" s="1"/>
@@ -13147,7 +13347,7 @@
       <c r="Q142" s="1"/>
       <c r="R142" s="1"/>
       <c r="S142" s="1"/>
-      <c r="T142" s="1"/>
+      <c r="T142" s="35"/>
       <c r="U142" s="1"/>
       <c r="V142" s="1"/>
       <c r="W142" s="1"/>
@@ -13201,7 +13401,7 @@
       <c r="Q143" s="1"/>
       <c r="R143" s="1"/>
       <c r="S143" s="1"/>
-      <c r="T143" s="1"/>
+      <c r="T143" s="35"/>
       <c r="U143" s="1"/>
       <c r="V143" s="1"/>
       <c r="W143" s="1"/>
@@ -13255,7 +13455,7 @@
       <c r="Q144" s="1"/>
       <c r="R144" s="1"/>
       <c r="S144" s="1"/>
-      <c r="T144" s="1"/>
+      <c r="T144" s="35"/>
       <c r="U144" s="1"/>
       <c r="V144" s="1"/>
       <c r="W144" s="1"/>
@@ -13309,7 +13509,7 @@
       <c r="Q145" s="1"/>
       <c r="R145" s="1"/>
       <c r="S145" s="1"/>
-      <c r="T145" s="1"/>
+      <c r="T145" s="35"/>
       <c r="U145" s="1"/>
       <c r="V145" s="1"/>
       <c r="W145" s="1"/>
@@ -13363,7 +13563,7 @@
       <c r="Q146" s="1"/>
       <c r="R146" s="1"/>
       <c r="S146" s="1"/>
-      <c r="T146" s="1"/>
+      <c r="T146" s="35"/>
       <c r="U146" s="1"/>
       <c r="V146" s="1"/>
       <c r="W146" s="1"/>
@@ -13417,7 +13617,7 @@
       <c r="Q147" s="1"/>
       <c r="R147" s="1"/>
       <c r="S147" s="1"/>
-      <c r="T147" s="1"/>
+      <c r="T147" s="35"/>
       <c r="U147" s="1"/>
       <c r="V147" s="1"/>
       <c r="W147" s="1"/>
@@ -13471,7 +13671,7 @@
       <c r="Q148" s="1"/>
       <c r="R148" s="1"/>
       <c r="S148" s="1"/>
-      <c r="T148" s="1"/>
+      <c r="T148" s="35"/>
       <c r="U148" s="1"/>
       <c r="V148" s="1"/>
       <c r="W148" s="1"/>
@@ -13525,7 +13725,7 @@
       <c r="Q149" s="1"/>
       <c r="R149" s="1"/>
       <c r="S149" s="1"/>
-      <c r="T149" s="1"/>
+      <c r="T149" s="35"/>
       <c r="U149" s="1"/>
       <c r="V149" s="1"/>
       <c r="W149" s="1"/>
@@ -13579,7 +13779,7 @@
       <c r="Q150" s="1"/>
       <c r="R150" s="1"/>
       <c r="S150" s="1"/>
-      <c r="T150" s="1"/>
+      <c r="T150" s="35"/>
       <c r="U150" s="1"/>
       <c r="V150" s="1"/>
       <c r="W150" s="1"/>
@@ -13633,7 +13833,7 @@
       <c r="Q151" s="1"/>
       <c r="R151" s="1"/>
       <c r="S151" s="1"/>
-      <c r="T151" s="1"/>
+      <c r="T151" s="35"/>
       <c r="U151" s="1"/>
       <c r="V151" s="1"/>
       <c r="W151" s="1"/>
@@ -13687,7 +13887,7 @@
       <c r="Q152" s="1"/>
       <c r="R152" s="1"/>
       <c r="S152" s="1"/>
-      <c r="T152" s="1"/>
+      <c r="T152" s="35"/>
       <c r="U152" s="1"/>
       <c r="V152" s="1"/>
       <c r="W152" s="1"/>
@@ -13741,7 +13941,7 @@
       <c r="Q153" s="1"/>
       <c r="R153" s="1"/>
       <c r="S153" s="1"/>
-      <c r="T153" s="1"/>
+      <c r="T153" s="35"/>
       <c r="U153" s="1"/>
       <c r="V153" s="1"/>
       <c r="W153" s="1"/>
@@ -13795,7 +13995,7 @@
       <c r="Q154" s="1"/>
       <c r="R154" s="1"/>
       <c r="S154" s="1"/>
-      <c r="T154" s="1"/>
+      <c r="T154" s="35"/>
       <c r="U154" s="1"/>
       <c r="V154" s="1"/>
       <c r="W154" s="1"/>
@@ -13849,7 +14049,7 @@
       <c r="Q155" s="1"/>
       <c r="R155" s="1"/>
       <c r="S155" s="1"/>
-      <c r="T155" s="1"/>
+      <c r="T155" s="35"/>
       <c r="U155" s="1"/>
       <c r="V155" s="1"/>
       <c r="W155" s="1"/>
@@ -13903,7 +14103,7 @@
       <c r="Q156" s="1"/>
       <c r="R156" s="1"/>
       <c r="S156" s="1"/>
-      <c r="T156" s="1"/>
+      <c r="T156" s="35"/>
       <c r="U156" s="1"/>
       <c r="V156" s="1"/>
       <c r="W156" s="1"/>
@@ -13957,7 +14157,7 @@
       <c r="Q157" s="1"/>
       <c r="R157" s="1"/>
       <c r="S157" s="1"/>
-      <c r="T157" s="1"/>
+      <c r="T157" s="35"/>
       <c r="U157" s="1"/>
       <c r="V157" s="1"/>
       <c r="W157" s="1"/>
@@ -14011,7 +14211,7 @@
       <c r="Q158" s="1"/>
       <c r="R158" s="1"/>
       <c r="S158" s="1"/>
-      <c r="T158" s="1"/>
+      <c r="T158" s="35"/>
       <c r="U158" s="1"/>
       <c r="V158" s="1"/>
       <c r="W158" s="1"/>
@@ -14065,7 +14265,7 @@
       <c r="Q159" s="1"/>
       <c r="R159" s="1"/>
       <c r="S159" s="1"/>
-      <c r="T159" s="1"/>
+      <c r="T159" s="35"/>
       <c r="U159" s="1"/>
       <c r="V159" s="1"/>
       <c r="W159" s="1"/>
@@ -14119,7 +14319,7 @@
       <c r="Q160" s="1"/>
       <c r="R160" s="1"/>
       <c r="S160" s="1"/>
-      <c r="T160" s="1"/>
+      <c r="T160" s="35"/>
       <c r="U160" s="1"/>
       <c r="V160" s="1"/>
       <c r="W160" s="1"/>
@@ -14173,7 +14373,7 @@
       <c r="Q161" s="1"/>
       <c r="R161" s="1"/>
       <c r="S161" s="1"/>
-      <c r="T161" s="1"/>
+      <c r="T161" s="35"/>
       <c r="U161" s="1"/>
       <c r="V161" s="1"/>
       <c r="W161" s="1"/>
@@ -14227,7 +14427,7 @@
       <c r="Q162" s="1"/>
       <c r="R162" s="1"/>
       <c r="S162" s="1"/>
-      <c r="T162" s="1"/>
+      <c r="T162" s="35"/>
       <c r="U162" s="1"/>
       <c r="V162" s="1"/>
       <c r="W162" s="1"/>
@@ -14281,7 +14481,7 @@
       <c r="Q163" s="1"/>
       <c r="R163" s="1"/>
       <c r="S163" s="1"/>
-      <c r="T163" s="1"/>
+      <c r="T163" s="35"/>
       <c r="U163" s="1"/>
       <c r="V163" s="1"/>
       <c r="W163" s="1"/>
@@ -14335,7 +14535,7 @@
       <c r="Q164" s="1"/>
       <c r="R164" s="1"/>
       <c r="S164" s="1"/>
-      <c r="T164" s="1"/>
+      <c r="T164" s="35"/>
       <c r="U164" s="1"/>
       <c r="V164" s="1"/>
       <c r="W164" s="1"/>
@@ -14389,7 +14589,7 @@
       <c r="Q165" s="1"/>
       <c r="R165" s="1"/>
       <c r="S165" s="1"/>
-      <c r="T165" s="1"/>
+      <c r="T165" s="35"/>
       <c r="U165" s="1"/>
       <c r="V165" s="1"/>
       <c r="W165" s="1"/>
@@ -14443,7 +14643,7 @@
       <c r="Q166" s="1"/>
       <c r="R166" s="1"/>
       <c r="S166" s="1"/>
-      <c r="T166" s="1"/>
+      <c r="T166" s="35"/>
       <c r="U166" s="1"/>
       <c r="V166" s="1"/>
       <c r="W166" s="1"/>
@@ -14497,7 +14697,7 @@
       <c r="Q167" s="1"/>
       <c r="R167" s="1"/>
       <c r="S167" s="1"/>
-      <c r="T167" s="1"/>
+      <c r="T167" s="35"/>
       <c r="U167" s="1"/>
       <c r="V167" s="1"/>
       <c r="W167" s="1"/>
@@ -14551,7 +14751,7 @@
       <c r="Q168" s="1"/>
       <c r="R168" s="1"/>
       <c r="S168" s="1"/>
-      <c r="T168" s="1"/>
+      <c r="T168" s="35"/>
       <c r="U168" s="1"/>
       <c r="V168" s="1"/>
       <c r="W168" s="1"/>
@@ -14605,7 +14805,7 @@
       <c r="Q169" s="1"/>
       <c r="R169" s="1"/>
       <c r="S169" s="1"/>
-      <c r="T169" s="1"/>
+      <c r="T169" s="35"/>
       <c r="U169" s="1"/>
       <c r="V169" s="1"/>
       <c r="W169" s="1"/>
@@ -14659,7 +14859,7 @@
       <c r="Q170" s="1"/>
       <c r="R170" s="1"/>
       <c r="S170" s="1"/>
-      <c r="T170" s="1"/>
+      <c r="T170" s="35"/>
       <c r="U170" s="1"/>
       <c r="V170" s="1"/>
       <c r="W170" s="1"/>
@@ -14713,7 +14913,7 @@
       <c r="Q171" s="1"/>
       <c r="R171" s="1"/>
       <c r="S171" s="1"/>
-      <c r="T171" s="1"/>
+      <c r="T171" s="35"/>
       <c r="U171" s="1"/>
       <c r="V171" s="1"/>
       <c r="W171" s="1"/>
@@ -14767,7 +14967,7 @@
       <c r="Q172" s="1"/>
       <c r="R172" s="1"/>
       <c r="S172" s="1"/>
-      <c r="T172" s="1"/>
+      <c r="T172" s="35"/>
       <c r="U172" s="1"/>
       <c r="V172" s="1"/>
       <c r="W172" s="1"/>
@@ -14821,7 +15021,7 @@
       <c r="Q173" s="1"/>
       <c r="R173" s="1"/>
       <c r="S173" s="1"/>
-      <c r="T173" s="1"/>
+      <c r="T173" s="35"/>
       <c r="U173" s="1"/>
       <c r="V173" s="1"/>
       <c r="W173" s="1"/>
@@ -14875,7 +15075,7 @@
       <c r="Q174" s="1"/>
       <c r="R174" s="1"/>
       <c r="S174" s="1"/>
-      <c r="T174" s="1"/>
+      <c r="T174" s="35"/>
       <c r="U174" s="1"/>
       <c r="V174" s="1"/>
       <c r="W174" s="1"/>
@@ -14929,7 +15129,7 @@
       <c r="Q175" s="1"/>
       <c r="R175" s="1"/>
       <c r="S175" s="1"/>
-      <c r="T175" s="1"/>
+      <c r="T175" s="35"/>
       <c r="U175" s="1"/>
       <c r="V175" s="1"/>
       <c r="W175" s="1"/>
@@ -14983,7 +15183,7 @@
       <c r="Q176" s="1"/>
       <c r="R176" s="1"/>
       <c r="S176" s="1"/>
-      <c r="T176" s="1"/>
+      <c r="T176" s="35"/>
       <c r="U176" s="1"/>
       <c r="V176" s="1"/>
       <c r="W176" s="1"/>
@@ -15037,7 +15237,7 @@
       <c r="Q177" s="1"/>
       <c r="R177" s="1"/>
       <c r="S177" s="1"/>
-      <c r="T177" s="1"/>
+      <c r="T177" s="35"/>
       <c r="U177" s="1"/>
       <c r="V177" s="1"/>
       <c r="W177" s="1"/>
@@ -15091,7 +15291,7 @@
       <c r="Q178" s="1"/>
       <c r="R178" s="1"/>
       <c r="S178" s="1"/>
-      <c r="T178" s="1"/>
+      <c r="T178" s="35"/>
       <c r="U178" s="1"/>
       <c r="V178" s="1"/>
       <c r="W178" s="1"/>
@@ -15145,7 +15345,7 @@
       <c r="Q179" s="1"/>
       <c r="R179" s="1"/>
       <c r="S179" s="1"/>
-      <c r="T179" s="1"/>
+      <c r="T179" s="35"/>
       <c r="U179" s="1"/>
       <c r="V179" s="1"/>
       <c r="W179" s="1"/>
@@ -15199,7 +15399,7 @@
       <c r="Q180" s="1"/>
       <c r="R180" s="1"/>
       <c r="S180" s="1"/>
-      <c r="T180" s="1"/>
+      <c r="T180" s="35"/>
       <c r="U180" s="1"/>
       <c r="V180" s="1"/>
       <c r="W180" s="1"/>
@@ -15253,7 +15453,7 @@
       <c r="Q181" s="1"/>
       <c r="R181" s="1"/>
       <c r="S181" s="1"/>
-      <c r="T181" s="1"/>
+      <c r="T181" s="35"/>
       <c r="U181" s="1"/>
       <c r="V181" s="1"/>
       <c r="W181" s="1"/>
@@ -15307,7 +15507,7 @@
       <c r="Q182" s="1"/>
       <c r="R182" s="1"/>
       <c r="S182" s="1"/>
-      <c r="T182" s="1"/>
+      <c r="T182" s="35"/>
       <c r="U182" s="1"/>
       <c r="V182" s="1"/>
       <c r="W182" s="1"/>
@@ -15361,7 +15561,7 @@
       <c r="Q183" s="1"/>
       <c r="R183" s="1"/>
       <c r="S183" s="1"/>
-      <c r="T183" s="1"/>
+      <c r="T183" s="35"/>
       <c r="U183" s="1"/>
       <c r="V183" s="1"/>
       <c r="W183" s="1"/>
@@ -15415,7 +15615,7 @@
       <c r="Q184" s="1"/>
       <c r="R184" s="1"/>
       <c r="S184" s="1"/>
-      <c r="T184" s="1"/>
+      <c r="T184" s="35"/>
       <c r="U184" s="1"/>
       <c r="V184" s="1"/>
       <c r="W184" s="1"/>
@@ -15469,7 +15669,7 @@
       <c r="Q185" s="1"/>
       <c r="R185" s="1"/>
       <c r="S185" s="1"/>
-      <c r="T185" s="1"/>
+      <c r="T185" s="35"/>
       <c r="U185" s="1"/>
       <c r="V185" s="1"/>
       <c r="W185" s="1"/>
@@ -15523,7 +15723,7 @@
       <c r="Q186" s="1"/>
       <c r="R186" s="1"/>
       <c r="S186" s="1"/>
-      <c r="T186" s="1"/>
+      <c r="T186" s="35"/>
       <c r="U186" s="1"/>
       <c r="V186" s="1"/>
       <c r="W186" s="1"/>
@@ -15577,7 +15777,7 @@
       <c r="Q187" s="1"/>
       <c r="R187" s="1"/>
       <c r="S187" s="1"/>
-      <c r="T187" s="1"/>
+      <c r="T187" s="35"/>
       <c r="U187" s="1"/>
       <c r="V187" s="1"/>
       <c r="W187" s="1"/>
@@ -15631,7 +15831,7 @@
       <c r="Q188" s="1"/>
       <c r="R188" s="1"/>
       <c r="S188" s="1"/>
-      <c r="T188" s="1"/>
+      <c r="T188" s="35"/>
       <c r="U188" s="1"/>
       <c r="V188" s="1"/>
       <c r="W188" s="1"/>
@@ -15685,7 +15885,7 @@
       <c r="Q189" s="1"/>
       <c r="R189" s="1"/>
       <c r="S189" s="1"/>
-      <c r="T189" s="1"/>
+      <c r="T189" s="35"/>
       <c r="U189" s="1"/>
       <c r="V189" s="1"/>
       <c r="W189" s="1"/>
@@ -15739,7 +15939,7 @@
       <c r="Q190" s="1"/>
       <c r="R190" s="1"/>
       <c r="S190" s="1"/>
-      <c r="T190" s="1"/>
+      <c r="T190" s="35"/>
       <c r="U190" s="1"/>
       <c r="V190" s="1"/>
       <c r="W190" s="1"/>
@@ -15793,7 +15993,7 @@
       <c r="Q191" s="1"/>
       <c r="R191" s="1"/>
       <c r="S191" s="1"/>
-      <c r="T191" s="1"/>
+      <c r="T191" s="35"/>
       <c r="U191" s="1"/>
       <c r="V191" s="1"/>
       <c r="W191" s="1"/>
@@ -15847,7 +16047,7 @@
       <c r="Q192" s="1"/>
       <c r="R192" s="1"/>
       <c r="S192" s="1"/>
-      <c r="T192" s="1"/>
+      <c r="T192" s="35"/>
       <c r="U192" s="1"/>
       <c r="V192" s="1"/>
       <c r="W192" s="1"/>
@@ -15901,7 +16101,7 @@
       <c r="Q193" s="1"/>
       <c r="R193" s="1"/>
       <c r="S193" s="1"/>
-      <c r="T193" s="1"/>
+      <c r="T193" s="35"/>
       <c r="U193" s="1"/>
       <c r="V193" s="1"/>
       <c r="W193" s="1"/>
@@ -15955,7 +16155,7 @@
       <c r="Q194" s="1"/>
       <c r="R194" s="1"/>
       <c r="S194" s="1"/>
-      <c r="T194" s="1"/>
+      <c r="T194" s="35"/>
       <c r="U194" s="1"/>
       <c r="V194" s="1"/>
       <c r="W194" s="1"/>
@@ -16009,7 +16209,7 @@
       <c r="Q195" s="1"/>
       <c r="R195" s="1"/>
       <c r="S195" s="1"/>
-      <c r="T195" s="1"/>
+      <c r="T195" s="35"/>
       <c r="U195" s="1"/>
       <c r="V195" s="1"/>
       <c r="W195" s="1"/>
@@ -16063,7 +16263,7 @@
       <c r="Q196" s="1"/>
       <c r="R196" s="1"/>
       <c r="S196" s="1"/>
-      <c r="T196" s="1"/>
+      <c r="T196" s="35"/>
       <c r="U196" s="1"/>
       <c r="V196" s="1"/>
       <c r="W196" s="1"/>
@@ -16117,7 +16317,7 @@
       <c r="Q197" s="1"/>
       <c r="R197" s="1"/>
       <c r="S197" s="1"/>
-      <c r="T197" s="1"/>
+      <c r="T197" s="35"/>
       <c r="U197" s="1"/>
       <c r="V197" s="1"/>
       <c r="W197" s="1"/>
@@ -16171,7 +16371,7 @@
       <c r="Q198" s="1"/>
       <c r="R198" s="1"/>
       <c r="S198" s="1"/>
-      <c r="T198" s="1"/>
+      <c r="T198" s="35"/>
       <c r="U198" s="1"/>
       <c r="V198" s="1"/>
       <c r="W198" s="1"/>
@@ -16225,7 +16425,7 @@
       <c r="Q199" s="1"/>
       <c r="R199" s="1"/>
       <c r="S199" s="1"/>
-      <c r="T199" s="1"/>
+      <c r="T199" s="35"/>
       <c r="U199" s="1"/>
       <c r="V199" s="1"/>
       <c r="W199" s="1"/>
@@ -16279,7 +16479,7 @@
       <c r="Q200" s="1"/>
       <c r="R200" s="1"/>
       <c r="S200" s="1"/>
-      <c r="T200" s="1"/>
+      <c r="T200" s="35"/>
       <c r="U200" s="1"/>
       <c r="V200" s="1"/>
       <c r="W200" s="1"/>
@@ -16333,7 +16533,7 @@
       <c r="Q201" s="1"/>
       <c r="R201" s="1"/>
       <c r="S201" s="1"/>
-      <c r="T201" s="1"/>
+      <c r="T201" s="35"/>
       <c r="U201" s="1"/>
       <c r="V201" s="1"/>
       <c r="W201" s="1"/>
@@ -16387,7 +16587,7 @@
       <c r="Q202" s="1"/>
       <c r="R202" s="1"/>
       <c r="S202" s="1"/>
-      <c r="T202" s="1"/>
+      <c r="T202" s="35"/>
       <c r="U202" s="1"/>
       <c r="V202" s="1"/>
       <c r="W202" s="1"/>
@@ -16441,7 +16641,7 @@
       <c r="Q203" s="1"/>
       <c r="R203" s="1"/>
       <c r="S203" s="1"/>
-      <c r="T203" s="1"/>
+      <c r="T203" s="35"/>
       <c r="U203" s="1"/>
       <c r="V203" s="1"/>
       <c r="W203" s="1"/>
@@ -16495,7 +16695,7 @@
       <c r="Q204" s="1"/>
       <c r="R204" s="1"/>
       <c r="S204" s="1"/>
-      <c r="T204" s="1"/>
+      <c r="T204" s="35"/>
       <c r="U204" s="1"/>
       <c r="V204" s="1"/>
       <c r="W204" s="1"/>
@@ -16549,7 +16749,7 @@
       <c r="Q205" s="1"/>
       <c r="R205" s="1"/>
       <c r="S205" s="1"/>
-      <c r="T205" s="1"/>
+      <c r="T205" s="35"/>
       <c r="U205" s="1"/>
       <c r="V205" s="1"/>
       <c r="W205" s="1"/>
@@ -16603,7 +16803,7 @@
       <c r="Q206" s="1"/>
       <c r="R206" s="1"/>
       <c r="S206" s="1"/>
-      <c r="T206" s="1"/>
+      <c r="T206" s="35"/>
       <c r="U206" s="1"/>
       <c r="V206" s="1"/>
       <c r="W206" s="1"/>
@@ -16657,7 +16857,7 @@
       <c r="Q207" s="1"/>
       <c r="R207" s="1"/>
       <c r="S207" s="1"/>
-      <c r="T207" s="1"/>
+      <c r="T207" s="35"/>
       <c r="U207" s="1"/>
       <c r="V207" s="1"/>
       <c r="W207" s="1"/>
@@ -16711,7 +16911,7 @@
       <c r="Q208" s="1"/>
       <c r="R208" s="1"/>
       <c r="S208" s="1"/>
-      <c r="T208" s="1"/>
+      <c r="T208" s="35"/>
       <c r="U208" s="1"/>
       <c r="V208" s="1"/>
       <c r="W208" s="1"/>
@@ -16765,7 +16965,7 @@
       <c r="Q209" s="1"/>
       <c r="R209" s="1"/>
       <c r="S209" s="1"/>
-      <c r="T209" s="1"/>
+      <c r="T209" s="35"/>
       <c r="U209" s="1"/>
       <c r="V209" s="1"/>
       <c r="W209" s="1"/>
@@ -16819,7 +17019,7 @@
       <c r="Q210" s="1"/>
       <c r="R210" s="1"/>
       <c r="S210" s="1"/>
-      <c r="T210" s="1"/>
+      <c r="T210" s="35"/>
       <c r="U210" s="1"/>
       <c r="V210" s="1"/>
       <c r="W210" s="1"/>
@@ -16873,7 +17073,7 @@
       <c r="Q211" s="1"/>
       <c r="R211" s="1"/>
       <c r="S211" s="1"/>
-      <c r="T211" s="1"/>
+      <c r="T211" s="35"/>
       <c r="U211" s="1"/>
       <c r="V211" s="1"/>
       <c r="W211" s="1"/>
@@ -16927,7 +17127,7 @@
       <c r="Q212" s="1"/>
       <c r="R212" s="1"/>
       <c r="S212" s="1"/>
-      <c r="T212" s="1"/>
+      <c r="T212" s="35"/>
       <c r="U212" s="1"/>
       <c r="V212" s="1"/>
       <c r="W212" s="1"/>
@@ -16981,7 +17181,7 @@
       <c r="Q213" s="1"/>
       <c r="R213" s="1"/>
       <c r="S213" s="1"/>
-      <c r="T213" s="1"/>
+      <c r="T213" s="35"/>
       <c r="U213" s="1"/>
       <c r="V213" s="1"/>
       <c r="W213" s="1"/>
@@ -17035,7 +17235,7 @@
       <c r="Q214" s="1"/>
       <c r="R214" s="1"/>
       <c r="S214" s="1"/>
-      <c r="T214" s="1"/>
+      <c r="T214" s="35"/>
       <c r="U214" s="1"/>
       <c r="V214" s="1"/>
       <c r="W214" s="1"/>
@@ -17089,7 +17289,7 @@
       <c r="Q215" s="1"/>
       <c r="R215" s="1"/>
       <c r="S215" s="1"/>
-      <c r="T215" s="1"/>
+      <c r="T215" s="35"/>
       <c r="U215" s="1"/>
       <c r="V215" s="1"/>
       <c r="W215" s="1"/>
@@ -17143,7 +17343,7 @@
       <c r="Q216" s="1"/>
       <c r="R216" s="1"/>
       <c r="S216" s="1"/>
-      <c r="T216" s="1"/>
+      <c r="T216" s="35"/>
       <c r="U216" s="1"/>
       <c r="V216" s="1"/>
       <c r="W216" s="1"/>
@@ -17197,7 +17397,7 @@
       <c r="Q217" s="1"/>
       <c r="R217" s="1"/>
       <c r="S217" s="1"/>
-      <c r="T217" s="1"/>
+      <c r="T217" s="35"/>
       <c r="U217" s="1"/>
       <c r="V217" s="1"/>
       <c r="W217" s="1"/>
@@ -17251,7 +17451,7 @@
       <c r="Q218" s="1"/>
       <c r="R218" s="1"/>
       <c r="S218" s="1"/>
-      <c r="T218" s="1"/>
+      <c r="T218" s="35"/>
       <c r="U218" s="1"/>
       <c r="V218" s="1"/>
       <c r="W218" s="1"/>
@@ -17305,7 +17505,7 @@
       <c r="Q219" s="1"/>
       <c r="R219" s="1"/>
       <c r="S219" s="1"/>
-      <c r="T219" s="1"/>
+      <c r="T219" s="35"/>
       <c r="U219" s="1"/>
       <c r="V219" s="1"/>
       <c r="W219" s="1"/>
@@ -17359,7 +17559,7 @@
       <c r="Q220" s="1"/>
       <c r="R220" s="1"/>
       <c r="S220" s="1"/>
-      <c r="T220" s="1"/>
+      <c r="T220" s="35"/>
       <c r="U220" s="1"/>
       <c r="V220" s="1"/>
       <c r="W220" s="1"/>
@@ -17413,7 +17613,7 @@
       <c r="Q221" s="1"/>
       <c r="R221" s="1"/>
       <c r="S221" s="1"/>
-      <c r="T221" s="1"/>
+      <c r="T221" s="35"/>
       <c r="U221" s="1"/>
       <c r="V221" s="1"/>
       <c r="W221" s="1"/>
@@ -17467,7 +17667,7 @@
       <c r="Q222" s="1"/>
       <c r="R222" s="1"/>
       <c r="S222" s="1"/>
-      <c r="T222" s="1"/>
+      <c r="T222" s="35"/>
       <c r="U222" s="1"/>
       <c r="V222" s="1"/>
       <c r="W222" s="1"/>
@@ -17521,7 +17721,7 @@
       <c r="Q223" s="1"/>
       <c r="R223" s="1"/>
       <c r="S223" s="1"/>
-      <c r="T223" s="1"/>
+      <c r="T223" s="35"/>
       <c r="U223" s="1"/>
       <c r="V223" s="1"/>
       <c r="W223" s="1"/>
@@ -17575,7 +17775,7 @@
       <c r="Q224" s="1"/>
       <c r="R224" s="1"/>
       <c r="S224" s="1"/>
-      <c r="T224" s="1"/>
+      <c r="T224" s="35"/>
       <c r="U224" s="1"/>
       <c r="V224" s="1"/>
       <c r="W224" s="1"/>
@@ -17629,7 +17829,7 @@
       <c r="Q225" s="1"/>
       <c r="R225" s="1"/>
       <c r="S225" s="1"/>
-      <c r="T225" s="1"/>
+      <c r="T225" s="35"/>
       <c r="U225" s="1"/>
       <c r="V225" s="1"/>
       <c r="W225" s="1"/>
@@ -17683,7 +17883,7 @@
       <c r="Q226" s="1"/>
       <c r="R226" s="1"/>
       <c r="S226" s="1"/>
-      <c r="T226" s="1"/>
+      <c r="T226" s="35"/>
       <c r="U226" s="1"/>
       <c r="V226" s="1"/>
       <c r="W226" s="1"/>
@@ -17737,7 +17937,7 @@
       <c r="Q227" s="1"/>
       <c r="R227" s="1"/>
       <c r="S227" s="1"/>
-      <c r="T227" s="1"/>
+      <c r="T227" s="35"/>
       <c r="U227" s="1"/>
       <c r="V227" s="1"/>
       <c r="W227" s="1"/>
@@ -17791,7 +17991,7 @@
       <c r="Q228" s="1"/>
       <c r="R228" s="1"/>
       <c r="S228" s="1"/>
-      <c r="T228" s="1"/>
+      <c r="T228" s="35"/>
       <c r="U228" s="1"/>
       <c r="V228" s="1"/>
       <c r="W228" s="1"/>
@@ -17845,7 +18045,7 @@
       <c r="Q229" s="1"/>
       <c r="R229" s="1"/>
       <c r="S229" s="1"/>
-      <c r="T229" s="1"/>
+      <c r="T229" s="35"/>
       <c r="U229" s="1"/>
       <c r="V229" s="1"/>
       <c r="W229" s="1"/>
@@ -17899,7 +18099,7 @@
       <c r="Q230" s="1"/>
       <c r="R230" s="1"/>
       <c r="S230" s="1"/>
-      <c r="T230" s="1"/>
+      <c r="T230" s="35"/>
       <c r="U230" s="1"/>
       <c r="V230" s="1"/>
       <c r="W230" s="1"/>
@@ -17953,7 +18153,7 @@
       <c r="Q231" s="1"/>
       <c r="R231" s="1"/>
       <c r="S231" s="1"/>
-      <c r="T231" s="1"/>
+      <c r="T231" s="35"/>
       <c r="U231" s="1"/>
       <c r="V231" s="1"/>
       <c r="W231" s="1"/>
@@ -18007,7 +18207,7 @@
       <c r="Q232" s="1"/>
       <c r="R232" s="1"/>
       <c r="S232" s="1"/>
-      <c r="T232" s="1"/>
+      <c r="T232" s="35"/>
       <c r="U232" s="1"/>
       <c r="V232" s="1"/>
       <c r="W232" s="1"/>
@@ -18061,7 +18261,7 @@
       <c r="Q233" s="1"/>
       <c r="R233" s="1"/>
       <c r="S233" s="1"/>
-      <c r="T233" s="1"/>
+      <c r="T233" s="35"/>
       <c r="U233" s="1"/>
       <c r="V233" s="1"/>
       <c r="W233" s="1"/>
@@ -18115,7 +18315,7 @@
       <c r="Q234" s="1"/>
       <c r="R234" s="1"/>
       <c r="S234" s="1"/>
-      <c r="T234" s="1"/>
+      <c r="T234" s="35"/>
       <c r="U234" s="1"/>
       <c r="V234" s="1"/>
       <c r="W234" s="1"/>
@@ -18169,7 +18369,7 @@
       <c r="Q235" s="1"/>
       <c r="R235" s="1"/>
       <c r="S235" s="1"/>
-      <c r="T235" s="1"/>
+      <c r="T235" s="35"/>
       <c r="U235" s="1"/>
       <c r="V235" s="1"/>
       <c r="W235" s="1"/>
@@ -18223,7 +18423,7 @@
       <c r="Q236" s="1"/>
       <c r="R236" s="1"/>
       <c r="S236" s="1"/>
-      <c r="T236" s="1"/>
+      <c r="T236" s="35"/>
       <c r="U236" s="1"/>
       <c r="V236" s="1"/>
       <c r="W236" s="1"/>
@@ -18277,7 +18477,7 @@
       <c r="Q237" s="1"/>
       <c r="R237" s="1"/>
       <c r="S237" s="1"/>
-      <c r="T237" s="1"/>
+      <c r="T237" s="35"/>
       <c r="U237" s="1"/>
       <c r="V237" s="1"/>
       <c r="W237" s="1"/>
@@ -18331,7 +18531,7 @@
       <c r="Q238" s="1"/>
       <c r="R238" s="1"/>
       <c r="S238" s="1"/>
-      <c r="T238" s="1"/>
+      <c r="T238" s="35"/>
       <c r="U238" s="1"/>
       <c r="V238" s="1"/>
       <c r="W238" s="1"/>
@@ -18385,7 +18585,7 @@
       <c r="Q239" s="1"/>
       <c r="R239" s="1"/>
       <c r="S239" s="1"/>
-      <c r="T239" s="1"/>
+      <c r="T239" s="35"/>
       <c r="U239" s="1"/>
       <c r="V239" s="1"/>
       <c r="W239" s="1"/>
@@ -18439,7 +18639,7 @@
       <c r="Q240" s="1"/>
       <c r="R240" s="1"/>
       <c r="S240" s="1"/>
-      <c r="T240" s="1"/>
+      <c r="T240" s="35"/>
       <c r="U240" s="1"/>
       <c r="V240" s="1"/>
       <c r="W240" s="1"/>
@@ -18493,7 +18693,7 @@
       <c r="Q241" s="1"/>
       <c r="R241" s="1"/>
       <c r="S241" s="1"/>
-      <c r="T241" s="1"/>
+      <c r="T241" s="35"/>
       <c r="U241" s="1"/>
       <c r="V241" s="1"/>
       <c r="W241" s="1"/>
@@ -18547,7 +18747,7 @@
       <c r="Q242" s="1"/>
       <c r="R242" s="1"/>
       <c r="S242" s="1"/>
-      <c r="T242" s="1"/>
+      <c r="T242" s="35"/>
       <c r="U242" s="1"/>
       <c r="V242" s="1"/>
       <c r="W242" s="1"/>
@@ -18601,7 +18801,7 @@
       <c r="Q243" s="1"/>
       <c r="R243" s="1"/>
       <c r="S243" s="1"/>
-      <c r="T243" s="1"/>
+      <c r="T243" s="35"/>
       <c r="U243" s="1"/>
       <c r="V243" s="1"/>
       <c r="W243" s="1"/>
@@ -18655,7 +18855,7 @@
       <c r="Q244" s="1"/>
       <c r="R244" s="1"/>
       <c r="S244" s="1"/>
-      <c r="T244" s="1"/>
+      <c r="T244" s="35"/>
       <c r="U244" s="1"/>
       <c r="V244" s="1"/>
       <c r="W244" s="1"/>
@@ -18709,7 +18909,7 @@
       <c r="Q245" s="1"/>
       <c r="R245" s="1"/>
       <c r="S245" s="1"/>
-      <c r="T245" s="1"/>
+      <c r="T245" s="35"/>
       <c r="U245" s="1"/>
       <c r="V245" s="1"/>
       <c r="W245" s="1"/>
@@ -18763,7 +18963,7 @@
       <c r="Q246" s="1"/>
       <c r="R246" s="1"/>
       <c r="S246" s="1"/>
-      <c r="T246" s="1"/>
+      <c r="T246" s="35"/>
       <c r="U246" s="1"/>
       <c r="V246" s="1"/>
       <c r="W246" s="1"/>
@@ -18817,7 +19017,7 @@
       <c r="Q247" s="1"/>
       <c r="R247" s="1"/>
       <c r="S247" s="1"/>
-      <c r="T247" s="1"/>
+      <c r="T247" s="35"/>
       <c r="U247" s="1"/>
       <c r="V247" s="1"/>
       <c r="W247" s="1"/>
@@ -18871,7 +19071,7 @@
       <c r="Q248" s="1"/>
       <c r="R248" s="1"/>
       <c r="S248" s="1"/>
-      <c r="T248" s="1"/>
+      <c r="T248" s="35"/>
       <c r="U248" s="1"/>
       <c r="V248" s="1"/>
       <c r="W248" s="1"/>
@@ -18925,7 +19125,7 @@
       <c r="Q249" s="1"/>
       <c r="R249" s="1"/>
       <c r="S249" s="1"/>
-      <c r="T249" s="1"/>
+      <c r="T249" s="35"/>
       <c r="U249" s="1"/>
       <c r="V249" s="1"/>
       <c r="W249" s="1"/>
@@ -18979,7 +19179,7 @@
       <c r="Q250" s="1"/>
       <c r="R250" s="1"/>
       <c r="S250" s="1"/>
-      <c r="T250" s="1"/>
+      <c r="T250" s="35"/>
       <c r="U250" s="1"/>
       <c r="V250" s="1"/>
       <c r="W250" s="1"/>
@@ -19033,7 +19233,7 @@
       <c r="Q251" s="1"/>
       <c r="R251" s="1"/>
       <c r="S251" s="1"/>
-      <c r="T251" s="1"/>
+      <c r="T251" s="35"/>
       <c r="U251" s="1"/>
       <c r="V251" s="1"/>
       <c r="W251" s="1"/>
@@ -19087,7 +19287,7 @@
       <c r="Q252" s="1"/>
       <c r="R252" s="1"/>
       <c r="S252" s="1"/>
-      <c r="T252" s="1"/>
+      <c r="T252" s="35"/>
       <c r="U252" s="1"/>
       <c r="V252" s="1"/>
       <c r="W252" s="1"/>
@@ -19141,7 +19341,7 @@
       <c r="Q253" s="1"/>
       <c r="R253" s="1"/>
       <c r="S253" s="1"/>
-      <c r="T253" s="1"/>
+      <c r="T253" s="35"/>
       <c r="U253" s="1"/>
       <c r="V253" s="1"/>
       <c r="W253" s="1"/>
@@ -19195,7 +19395,7 @@
       <c r="Q254" s="1"/>
       <c r="R254" s="1"/>
       <c r="S254" s="1"/>
-      <c r="T254" s="1"/>
+      <c r="T254" s="35"/>
       <c r="U254" s="1"/>
       <c r="V254" s="1"/>
       <c r="W254" s="1"/>
@@ -19249,7 +19449,7 @@
       <c r="Q255" s="1"/>
       <c r="R255" s="1"/>
       <c r="S255" s="1"/>
-      <c r="T255" s="1"/>
+      <c r="T255" s="35"/>
       <c r="U255" s="1"/>
       <c r="V255" s="1"/>
       <c r="W255" s="1"/>
@@ -19303,7 +19503,7 @@
       <c r="Q256" s="1"/>
       <c r="R256" s="1"/>
       <c r="S256" s="1"/>
-      <c r="T256" s="1"/>
+      <c r="T256" s="35"/>
       <c r="U256" s="1"/>
       <c r="V256" s="1"/>
       <c r="W256" s="1"/>
@@ -19357,7 +19557,7 @@
       <c r="Q257" s="1"/>
       <c r="R257" s="1"/>
       <c r="S257" s="1"/>
-      <c r="T257" s="1"/>
+      <c r="T257" s="35"/>
       <c r="U257" s="1"/>
       <c r="V257" s="1"/>
       <c r="W257" s="1"/>
@@ -19411,7 +19611,7 @@
       <c r="Q258" s="1"/>
       <c r="R258" s="1"/>
       <c r="S258" s="1"/>
-      <c r="T258" s="1"/>
+      <c r="T258" s="35"/>
       <c r="U258" s="1"/>
       <c r="V258" s="1"/>
       <c r="W258" s="1"/>
@@ -19465,7 +19665,7 @@
       <c r="Q259" s="1"/>
       <c r="R259" s="1"/>
       <c r="S259" s="1"/>
-      <c r="T259" s="1"/>
+      <c r="T259" s="35"/>
       <c r="U259" s="1"/>
       <c r="V259" s="1"/>
       <c r="W259" s="1"/>
@@ -19519,7 +19719,7 @@
       <c r="Q260" s="1"/>
       <c r="R260" s="1"/>
       <c r="S260" s="1"/>
-      <c r="T260" s="1"/>
+      <c r="T260" s="35"/>
       <c r="U260" s="1"/>
       <c r="V260" s="1"/>
       <c r="W260" s="1"/>
@@ -19573,7 +19773,7 @@
       <c r="Q261" s="1"/>
       <c r="R261" s="1"/>
       <c r="S261" s="1"/>
-      <c r="T261" s="1"/>
+      <c r="T261" s="35"/>
       <c r="U261" s="1"/>
       <c r="V261" s="1"/>
       <c r="W261" s="1"/>
@@ -19627,7 +19827,7 @@
       <c r="Q262" s="1"/>
       <c r="R262" s="1"/>
       <c r="S262" s="1"/>
-      <c r="T262" s="1"/>
+      <c r="T262" s="35"/>
       <c r="U262" s="1"/>
       <c r="V262" s="1"/>
       <c r="W262" s="1"/>
@@ -19681,7 +19881,7 @@
       <c r="Q263" s="1"/>
       <c r="R263" s="1"/>
       <c r="S263" s="1"/>
-      <c r="T263" s="1"/>
+      <c r="T263" s="35"/>
       <c r="U263" s="1"/>
       <c r="V263" s="1"/>
       <c r="W263" s="1"/>
@@ -19735,7 +19935,7 @@
       <c r="Q264" s="1"/>
       <c r="R264" s="1"/>
       <c r="S264" s="1"/>
-      <c r="T264" s="1"/>
+      <c r="T264" s="35"/>
       <c r="U264" s="1"/>
       <c r="V264" s="1"/>
       <c r="W264" s="1"/>
@@ -19789,7 +19989,7 @@
       <c r="Q265" s="1"/>
       <c r="R265" s="1"/>
       <c r="S265" s="1"/>
-      <c r="T265" s="1"/>
+      <c r="T265" s="35"/>
       <c r="U265" s="1"/>
       <c r="V265" s="1"/>
       <c r="W265" s="1"/>
@@ -19843,7 +20043,7 @@
       <c r="Q266" s="1"/>
       <c r="R266" s="1"/>
       <c r="S266" s="1"/>
-      <c r="T266" s="1"/>
+      <c r="T266" s="35"/>
       <c r="U266" s="1"/>
       <c r="V266" s="1"/>
       <c r="W266" s="1"/>
@@ -19897,7 +20097,7 @@
       <c r="Q267" s="1"/>
       <c r="R267" s="1"/>
       <c r="S267" s="1"/>
-      <c r="T267" s="1"/>
+      <c r="T267" s="35"/>
       <c r="U267" s="1"/>
       <c r="V267" s="1"/>
       <c r="W267" s="1"/>
@@ -19951,7 +20151,7 @@
       <c r="Q268" s="1"/>
       <c r="R268" s="1"/>
       <c r="S268" s="1"/>
-      <c r="T268" s="1"/>
+      <c r="T268" s="35"/>
       <c r="U268" s="1"/>
       <c r="V268" s="1"/>
       <c r="W268" s="1"/>
@@ -20005,7 +20205,7 @@
       <c r="Q269" s="1"/>
       <c r="R269" s="1"/>
       <c r="S269" s="1"/>
-      <c r="T269" s="1"/>
+      <c r="T269" s="35"/>
       <c r="U269" s="1"/>
       <c r="V269" s="1"/>
       <c r="W269" s="1"/>
@@ -20059,7 +20259,7 @@
       <c r="Q270" s="1"/>
       <c r="R270" s="1"/>
       <c r="S270" s="1"/>
-      <c r="T270" s="1"/>
+      <c r="T270" s="35"/>
       <c r="U270" s="1"/>
       <c r="V270" s="1"/>
       <c r="W270" s="1"/>
@@ -20113,7 +20313,7 @@
       <c r="Q271" s="1"/>
       <c r="R271" s="1"/>
       <c r="S271" s="1"/>
-      <c r="T271" s="1"/>
+      <c r="T271" s="35"/>
       <c r="U271" s="1"/>
       <c r="V271" s="1"/>
       <c r="W271" s="1"/>
@@ -20167,7 +20367,7 @@
       <c r="Q272" s="1"/>
       <c r="R272" s="1"/>
       <c r="S272" s="1"/>
-      <c r="T272" s="1"/>
+      <c r="T272" s="35"/>
       <c r="U272" s="1"/>
       <c r="V272" s="1"/>
       <c r="W272" s="1"/>
@@ -20221,7 +20421,7 @@
       <c r="Q273" s="1"/>
       <c r="R273" s="1"/>
       <c r="S273" s="1"/>
-      <c r="T273" s="1"/>
+      <c r="T273" s="35"/>
       <c r="U273" s="1"/>
       <c r="V273" s="1"/>
       <c r="W273" s="1"/>
@@ -20275,7 +20475,7 @@
       <c r="Q274" s="1"/>
       <c r="R274" s="1"/>
       <c r="S274" s="1"/>
-      <c r="T274" s="1"/>
+      <c r="T274" s="35"/>
       <c r="U274" s="1"/>
       <c r="V274" s="1"/>
       <c r="W274" s="1"/>
@@ -20329,7 +20529,7 @@
       <c r="Q275" s="1"/>
       <c r="R275" s="1"/>
       <c r="S275" s="1"/>
-      <c r="T275" s="1"/>
+      <c r="T275" s="35"/>
       <c r="U275" s="1"/>
       <c r="V275" s="1"/>
       <c r="W275" s="1"/>
@@ -20383,7 +20583,7 @@
       <c r="Q276" s="1"/>
       <c r="R276" s="1"/>
       <c r="S276" s="1"/>
-      <c r="T276" s="1"/>
+      <c r="T276" s="35"/>
       <c r="U276" s="1"/>
       <c r="V276" s="1"/>
       <c r="W276" s="1"/>
@@ -20437,7 +20637,7 @@
       <c r="Q277" s="1"/>
       <c r="R277" s="1"/>
       <c r="S277" s="1"/>
-      <c r="T277" s="1"/>
+      <c r="T277" s="35"/>
       <c r="U277" s="1"/>
       <c r="V277" s="1"/>
       <c r="W277" s="1"/>
@@ -20491,7 +20691,7 @@
       <c r="Q278" s="1"/>
       <c r="R278" s="1"/>
       <c r="S278" s="1"/>
-      <c r="T278" s="1"/>
+      <c r="T278" s="35"/>
       <c r="U278" s="1"/>
       <c r="V278" s="1"/>
       <c r="W278" s="1"/>
@@ -20545,7 +20745,7 @@
       <c r="Q279" s="1"/>
       <c r="R279" s="1"/>
       <c r="S279" s="1"/>
-      <c r="T279" s="1"/>
+      <c r="T279" s="35"/>
       <c r="U279" s="1"/>
       <c r="V279" s="1"/>
       <c r="W279" s="1"/>
@@ -20599,7 +20799,7 @@
       <c r="Q280" s="1"/>
       <c r="R280" s="1"/>
       <c r="S280" s="1"/>
-      <c r="T280" s="1"/>
+      <c r="T280" s="35"/>
       <c r="U280" s="1"/>
       <c r="V280" s="1"/>
       <c r="W280" s="1"/>
@@ -20653,7 +20853,7 @@
       <c r="Q281" s="1"/>
       <c r="R281" s="1"/>
       <c r="S281" s="1"/>
-      <c r="T281" s="1"/>
+      <c r="T281" s="35"/>
       <c r="U281" s="1"/>
       <c r="V281" s="1"/>
       <c r="W281" s="1"/>
@@ -20707,7 +20907,7 @@
       <c r="Q282" s="1"/>
       <c r="R282" s="1"/>
       <c r="S282" s="1"/>
-      <c r="T282" s="1"/>
+      <c r="T282" s="35"/>
       <c r="U282" s="1"/>
       <c r="V282" s="1"/>
       <c r="W282" s="1"/>
@@ -20761,7 +20961,7 @@
       <c r="Q283" s="1"/>
       <c r="R283" s="1"/>
       <c r="S283" s="1"/>
-      <c r="T283" s="1"/>
+      <c r="T283" s="35"/>
       <c r="U283" s="1"/>
       <c r="V283" s="1"/>
       <c r="W283" s="1"/>
@@ -20815,7 +21015,7 @@
       <c r="Q284" s="1"/>
       <c r="R284" s="1"/>
       <c r="S284" s="1"/>
-      <c r="T284" s="1"/>
+      <c r="T284" s="35"/>
       <c r="U284" s="1"/>
       <c r="V284" s="1"/>
       <c r="W284" s="1"/>
@@ -20869,7 +21069,7 @@
       <c r="Q285" s="1"/>
       <c r="R285" s="1"/>
       <c r="S285" s="1"/>
-      <c r="T285" s="1"/>
+      <c r="T285" s="35"/>
       <c r="U285" s="1"/>
       <c r="V285" s="1"/>
       <c r="W285" s="1"/>
@@ -20923,7 +21123,7 @@
       <c r="Q286" s="1"/>
       <c r="R286" s="1"/>
       <c r="S286" s="1"/>
-      <c r="T286" s="1"/>
+      <c r="T286" s="35"/>
       <c r="U286" s="1"/>
       <c r="V286" s="1"/>
       <c r="W286" s="1"/>
@@ -20977,7 +21177,7 @@
       <c r="Q287" s="1"/>
       <c r="R287" s="1"/>
       <c r="S287" s="1"/>
-      <c r="T287" s="1"/>
+      <c r="T287" s="35"/>
       <c r="U287" s="1"/>
       <c r="V287" s="1"/>
       <c r="W287" s="1"/>
@@ -21031,7 +21231,7 @@
       <c r="Q288" s="1"/>
       <c r="R288" s="1"/>
       <c r="S288" s="1"/>
-      <c r="T288" s="1"/>
+      <c r="T288" s="35"/>
       <c r="U288" s="1"/>
       <c r="V288" s="1"/>
       <c r="W288" s="1"/>
@@ -21085,7 +21285,7 @@
       <c r="Q289" s="1"/>
       <c r="R289" s="1"/>
       <c r="S289" s="1"/>
-      <c r="T289" s="1"/>
+      <c r="T289" s="35"/>
       <c r="U289" s="1"/>
       <c r="V289" s="1"/>
       <c r="W289" s="1"/>
@@ -21139,7 +21339,7 @@
       <c r="Q290" s="1"/>
       <c r="R290" s="1"/>
       <c r="S290" s="1"/>
-      <c r="T290" s="1"/>
+      <c r="T290" s="35"/>
       <c r="U290" s="1"/>
       <c r="V290" s="1"/>
       <c r="W290" s="1"/>
@@ -21193,7 +21393,7 @@
       <c r="Q291" s="1"/>
       <c r="R291" s="1"/>
       <c r="S291" s="1"/>
-      <c r="T291" s="1"/>
+      <c r="T291" s="35"/>
       <c r="U291" s="1"/>
       <c r="V291" s="1"/>
       <c r="W291" s="1"/>
@@ -21247,7 +21447,7 @@
       <c r="Q292" s="1"/>
       <c r="R292" s="1"/>
       <c r="S292" s="1"/>
-      <c r="T292" s="1"/>
+      <c r="T292" s="35"/>
       <c r="U292" s="1"/>
       <c r="V292" s="1"/>
       <c r="W292" s="1"/>
@@ -21301,7 +21501,7 @@
       <c r="Q293" s="1"/>
       <c r="R293" s="1"/>
       <c r="S293" s="1"/>
-      <c r="T293" s="1"/>
+      <c r="T293" s="35"/>
       <c r="U293" s="1"/>
       <c r="V293" s="1"/>
       <c r="W293" s="1"/>
@@ -21355,7 +21555,7 @@
       <c r="Q294" s="1"/>
       <c r="R294" s="1"/>
       <c r="S294" s="1"/>
-      <c r="T294" s="1"/>
+      <c r="T294" s="35"/>
       <c r="U294" s="1"/>
       <c r="V294" s="1"/>
       <c r="W294" s="1"/>
@@ -21409,7 +21609,7 @@
       <c r="Q295" s="1"/>
       <c r="R295" s="1"/>
       <c r="S295" s="1"/>
-      <c r="T295" s="1"/>
+      <c r="T295" s="35"/>
       <c r="U295" s="1"/>
       <c r="V295" s="1"/>
       <c r="W295" s="1"/>
@@ -21463,7 +21663,7 @@
       <c r="Q296" s="1"/>
       <c r="R296" s="1"/>
       <c r="S296" s="1"/>
-      <c r="T296" s="1"/>
+      <c r="T296" s="35"/>
       <c r="U296" s="1"/>
       <c r="V296" s="1"/>
       <c r="W296" s="1"/>
@@ -21517,7 +21717,7 @@
       <c r="Q297" s="1"/>
       <c r="R297" s="1"/>
       <c r="S297" s="1"/>
-      <c r="T297" s="1"/>
+      <c r="T297" s="35"/>
       <c r="U297" s="1"/>
       <c r="V297" s="1"/>
       <c r="W297" s="1"/>
@@ -21571,7 +21771,7 @@
       <c r="Q298" s="1"/>
       <c r="R298" s="1"/>
       <c r="S298" s="1"/>
-      <c r="T298" s="1"/>
+      <c r="T298" s="35"/>
       <c r="U298" s="1"/>
       <c r="V298" s="1"/>
       <c r="W298" s="1"/>
@@ -21625,7 +21825,7 @@
       <c r="Q299" s="1"/>
       <c r="R299" s="1"/>
       <c r="S299" s="1"/>
-      <c r="T299" s="1"/>
+      <c r="T299" s="35"/>
       <c r="U299" s="1"/>
       <c r="V299" s="1"/>
       <c r="W299" s="1"/>
@@ -21679,7 +21879,7 @@
       <c r="Q300" s="1"/>
       <c r="R300" s="1"/>
       <c r="S300" s="1"/>
-      <c r="T300" s="1"/>
+      <c r="T300" s="35"/>
       <c r="U300" s="1"/>
       <c r="V300" s="1"/>
       <c r="W300" s="1"/>
@@ -21733,7 +21933,7 @@
       <c r="Q301" s="1"/>
       <c r="R301" s="1"/>
       <c r="S301" s="1"/>
-      <c r="T301" s="1"/>
+      <c r="T301" s="35"/>
       <c r="U301" s="1"/>
       <c r="V301" s="1"/>
       <c r="W301" s="1"/>
@@ -21787,7 +21987,7 @@
       <c r="Q302" s="1"/>
       <c r="R302" s="1"/>
       <c r="S302" s="1"/>
-      <c r="T302" s="1"/>
+      <c r="T302" s="35"/>
       <c r="U302" s="1"/>
       <c r="V302" s="1"/>
       <c r="W302" s="1"/>
@@ -21841,7 +22041,7 @@
       <c r="Q303" s="1"/>
       <c r="R303" s="1"/>
       <c r="S303" s="1"/>
-      <c r="T303" s="1"/>
+      <c r="T303" s="35"/>
       <c r="U303" s="1"/>
       <c r="V303" s="1"/>
       <c r="W303" s="1"/>
@@ -21895,7 +22095,7 @@
       <c r="Q304" s="1"/>
       <c r="R304" s="1"/>
       <c r="S304" s="1"/>
-      <c r="T304" s="1"/>
+      <c r="T304" s="35"/>
       <c r="U304" s="1"/>
       <c r="V304" s="1"/>
       <c r="W304" s="1"/>
@@ -21949,7 +22149,7 @@
       <c r="Q305" s="1"/>
       <c r="R305" s="1"/>
       <c r="S305" s="1"/>
-      <c r="T305" s="1"/>
+      <c r="T305" s="35"/>
       <c r="U305" s="1"/>
       <c r="V305" s="1"/>
       <c r="W305" s="1"/>
@@ -22003,7 +22203,7 @@
       <c r="Q306" s="1"/>
       <c r="R306" s="1"/>
       <c r="S306" s="1"/>
-      <c r="T306" s="1"/>
+      <c r="T306" s="35"/>
       <c r="U306" s="1"/>
       <c r="V306" s="1"/>
       <c r="W306" s="1"/>
@@ -22057,7 +22257,7 @@
       <c r="Q307" s="1"/>
       <c r="R307" s="1"/>
       <c r="S307" s="1"/>
-      <c r="T307" s="1"/>
+      <c r="T307" s="35"/>
       <c r="U307" s="1"/>
       <c r="V307" s="1"/>
       <c r="W307" s="1"/>
@@ -22111,7 +22311,7 @@
       <c r="Q308" s="1"/>
       <c r="R308" s="1"/>
       <c r="S308" s="1"/>
-      <c r="T308" s="1"/>
+      <c r="T308" s="35"/>
       <c r="U308" s="1"/>
       <c r="V308" s="1"/>
       <c r="W308" s="1"/>
@@ -22165,7 +22365,7 @@
       <c r="Q309" s="1"/>
       <c r="R309" s="1"/>
       <c r="S309" s="1"/>
-      <c r="T309" s="1"/>
+      <c r="T309" s="35"/>
       <c r="U309" s="1"/>
       <c r="V309" s="1"/>
       <c r="W309" s="1"/>
@@ -22219,7 +22419,7 @@
       <c r="Q310" s="1"/>
       <c r="R310" s="1"/>
       <c r="S310" s="1"/>
-      <c r="T310" s="1"/>
+      <c r="T310" s="35"/>
       <c r="U310" s="1"/>
       <c r="V310" s="1"/>
       <c r="W310" s="1"/>
@@ -22273,7 +22473,7 @@
       <c r="Q311" s="1"/>
       <c r="R311" s="1"/>
       <c r="S311" s="1"/>
-      <c r="T311" s="1"/>
+      <c r="T311" s="35"/>
       <c r="U311" s="1"/>
       <c r="V311" s="1"/>
       <c r="W311" s="1"/>
@@ -22327,7 +22527,7 @@
       <c r="Q312" s="1"/>
       <c r="R312" s="1"/>
       <c r="S312" s="1"/>
-      <c r="T312" s="1"/>
+      <c r="T312" s="35"/>
       <c r="U312" s="1"/>
       <c r="V312" s="1"/>
       <c r="W312" s="1"/>
@@ -22381,7 +22581,7 @@
       <c r="Q313" s="1"/>
       <c r="R313" s="1"/>
       <c r="S313" s="1"/>
-      <c r="T313" s="1"/>
+      <c r="T313" s="35"/>
       <c r="U313" s="1"/>
       <c r="V313" s="1"/>
       <c r="W313" s="1"/>
@@ -22435,7 +22635,7 @@
       <c r="Q314" s="1"/>
       <c r="R314" s="1"/>
       <c r="S314" s="1"/>
-      <c r="T314" s="1"/>
+      <c r="T314" s="35"/>
       <c r="U314" s="1"/>
       <c r="V314" s="1"/>
       <c r="W314" s="1"/>
@@ -22489,7 +22689,7 @@
       <c r="Q315" s="1"/>
       <c r="R315" s="1"/>
       <c r="S315" s="1"/>
-      <c r="T315" s="1"/>
+      <c r="T315" s="35"/>
       <c r="U315" s="1"/>
       <c r="V315" s="1"/>
       <c r="W315" s="1"/>
@@ -22543,7 +22743,7 @@
       <c r="Q316" s="1"/>
       <c r="R316" s="1"/>
       <c r="S316" s="1"/>
-      <c r="T316" s="1"/>
+      <c r="T316" s="35"/>
       <c r="U316" s="1"/>
       <c r="V316" s="1"/>
       <c r="W316" s="1"/>
@@ -22597,7 +22797,7 @@
       <c r="Q317" s="1"/>
       <c r="R317" s="1"/>
       <c r="S317" s="1"/>
-      <c r="T317" s="1"/>
+      <c r="T317" s="35"/>
       <c r="U317" s="1"/>
       <c r="V317" s="1"/>
       <c r="W317" s="1"/>
@@ -22651,7 +22851,7 @@
       <c r="Q318" s="1"/>
       <c r="R318" s="1"/>
       <c r="S318" s="1"/>
-      <c r="T318" s="1"/>
+      <c r="T318" s="35"/>
       <c r="U318" s="1"/>
       <c r="V318" s="1"/>
       <c r="W318" s="1"/>
@@ -22705,7 +22905,7 @@
       <c r="Q319" s="1"/>
       <c r="R319" s="1"/>
       <c r="S319" s="1"/>
-      <c r="T319" s="1"/>
+      <c r="T319" s="35"/>
       <c r="U319" s="1"/>
       <c r="V319" s="1"/>
       <c r="W319" s="1"/>
@@ -22759,7 +22959,7 @@
       <c r="Q320" s="1"/>
       <c r="R320" s="1"/>
       <c r="S320" s="1"/>
-      <c r="T320" s="1"/>
+      <c r="T320" s="35"/>
       <c r="U320" s="1"/>
       <c r="V320" s="1"/>
       <c r="W320" s="1"/>
@@ -22813,7 +23013,7 @@
       <c r="Q321" s="1"/>
       <c r="R321" s="1"/>
       <c r="S321" s="1"/>
-      <c r="T321" s="1"/>
+      <c r="T321" s="35"/>
       <c r="U321" s="1"/>
       <c r="V321" s="1"/>
       <c r="W321" s="1"/>
@@ -22867,7 +23067,7 @@
       <c r="Q322" s="1"/>
       <c r="R322" s="1"/>
       <c r="S322" s="1"/>
-      <c r="T322" s="1"/>
+      <c r="T322" s="35"/>
       <c r="U322" s="1"/>
       <c r="V322" s="1"/>
       <c r="W322" s="1"/>
@@ -22921,7 +23121,7 @@
       <c r="Q323" s="1"/>
       <c r="R323" s="1"/>
       <c r="S323" s="1"/>
-      <c r="T323" s="1"/>
+      <c r="T323" s="35"/>
       <c r="U323" s="1"/>
       <c r="V323" s="1"/>
       <c r="W323" s="1"/>
@@ -22975,7 +23175,7 @@
       <c r="Q324" s="1"/>
       <c r="R324" s="1"/>
       <c r="S324" s="1"/>
-      <c r="T324" s="1"/>
+      <c r="T324" s="35"/>
       <c r="U324" s="1"/>
       <c r="V324" s="1"/>
       <c r="W324" s="1"/>
@@ -23029,7 +23229,7 @@
       <c r="Q325" s="1"/>
       <c r="R325" s="1"/>
       <c r="S325" s="1"/>
-      <c r="T325" s="1"/>
+      <c r="T325" s="35"/>
       <c r="U325" s="1"/>
       <c r="V325" s="1"/>
       <c r="W325" s="1"/>
@@ -23083,7 +23283,7 @@
       <c r="Q326" s="1"/>
       <c r="R326" s="1"/>
       <c r="S326" s="1"/>
-      <c r="T326" s="1"/>
+      <c r="T326" s="35"/>
       <c r="U326" s="1"/>
       <c r="V326" s="1"/>
       <c r="W326" s="1"/>
@@ -23137,7 +23337,7 @@
       <c r="Q327" s="1"/>
       <c r="R327" s="1"/>
       <c r="S327" s="1"/>
-      <c r="T327" s="1"/>
+      <c r="T327" s="35"/>
       <c r="U327" s="1"/>
       <c r="V327" s="1"/>
       <c r="W327" s="1"/>
@@ -23191,7 +23391,7 @@
       <c r="Q328" s="1"/>
       <c r="R328" s="1"/>
       <c r="S328" s="1"/>
-      <c r="T328" s="1"/>
+      <c r="T328" s="35"/>
       <c r="U328" s="1"/>
       <c r="V328" s="1"/>
       <c r="W328" s="1"/>
@@ -23245,7 +23445,7 @@
       <c r="Q329" s="1"/>
       <c r="R329" s="1"/>
       <c r="S329" s="1"/>
-      <c r="T329" s="1"/>
+      <c r="T329" s="35"/>
       <c r="U329" s="1"/>
       <c r="V329" s="1"/>
       <c r="W329" s="1"/>
@@ -23299,7 +23499,7 @@
       <c r="Q330" s="1"/>
       <c r="R330" s="1"/>
       <c r="S330" s="1"/>
-      <c r="T330" s="1"/>
+      <c r="T330" s="35"/>
       <c r="U330" s="1"/>
       <c r="V330" s="1"/>
       <c r="W330" s="1"/>
@@ -23353,7 +23553,7 @@
       <c r="Q331" s="1"/>
       <c r="R331" s="1"/>
       <c r="S331" s="1"/>
-      <c r="T331" s="1"/>
+      <c r="T331" s="35"/>
       <c r="U331" s="1"/>
       <c r="V331" s="1"/>
       <c r="W331" s="1"/>
@@ -23407,7 +23607,7 @@
       <c r="Q332" s="1"/>
       <c r="R332" s="1"/>
       <c r="S332" s="1"/>
-      <c r="T332" s="1"/>
+      <c r="T332" s="35"/>
       <c r="U332" s="1"/>
       <c r="V332" s="1"/>
       <c r="W332" s="1"/>
@@ -23461,7 +23661,7 @@
       <c r="Q333" s="1"/>
       <c r="R333" s="1"/>
       <c r="S333" s="1"/>
-      <c r="T333" s="1"/>
+      <c r="T333" s="35"/>
       <c r="U333" s="1"/>
       <c r="V333" s="1"/>
       <c r="W333" s="1"/>
@@ -23515,7 +23715,7 @@
       <c r="Q334" s="1"/>
       <c r="R334" s="1"/>
       <c r="S334" s="1"/>
-      <c r="T334" s="1"/>
+      <c r="T334" s="35"/>
       <c r="U334" s="1"/>
       <c r="V334" s="1"/>
       <c r="W334" s="1"/>
@@ -23569,7 +23769,7 @@
       <c r="Q335" s="1"/>
       <c r="R335" s="1"/>
       <c r="S335" s="1"/>
-      <c r="T335" s="1"/>
+      <c r="T335" s="35"/>
       <c r="U335" s="1"/>
       <c r="V335" s="1"/>
       <c r="W335" s="1"/>
@@ -23623,7 +23823,7 @@
       <c r="Q336" s="1"/>
       <c r="R336" s="1"/>
       <c r="S336" s="1"/>
-      <c r="T336" s="1"/>
+      <c r="T336" s="35"/>
       <c r="U336" s="1"/>
       <c r="V336" s="1"/>
       <c r="W336" s="1"/>
@@ -23677,7 +23877,7 @@
       <c r="Q337" s="1"/>
       <c r="R337" s="1"/>
       <c r="S337" s="1"/>
-      <c r="T337" s="1"/>
+      <c r="T337" s="35"/>
       <c r="U337" s="1"/>
       <c r="V337" s="1"/>
       <c r="W337" s="1"/>
@@ -23731,7 +23931,7 @@
       <c r="Q338" s="1"/>
       <c r="R338" s="1"/>
       <c r="S338" s="1"/>
-      <c r="T338" s="1"/>
+      <c r="T338" s="35"/>
       <c r="U338" s="1"/>
       <c r="V338" s="1"/>
       <c r="W338" s="1"/>
@@ -23785,7 +23985,7 @@
       <c r="Q339" s="1"/>
       <c r="R339" s="1"/>
       <c r="S339" s="1"/>
-      <c r="T339" s="1"/>
+      <c r="T339" s="35"/>
       <c r="U339" s="1"/>
       <c r="V339" s="1"/>
       <c r="W339" s="1"/>
@@ -23839,7 +24039,7 @@
       <c r="Q340" s="1"/>
       <c r="R340" s="1"/>
       <c r="S340" s="1"/>
-      <c r="T340" s="1"/>
+      <c r="T340" s="35"/>
       <c r="U340" s="1"/>
       <c r="V340" s="1"/>
       <c r="W340" s="1"/>
@@ -23893,7 +24093,7 @@
       <c r="Q341" s="1"/>
       <c r="R341" s="1"/>
       <c r="S341" s="1"/>
-      <c r="T341" s="1"/>
+      <c r="T341" s="35"/>
       <c r="U341" s="1"/>
       <c r="V341" s="1"/>
       <c r="W341" s="1"/>
@@ -23947,7 +24147,7 @@
       <c r="Q342" s="1"/>
       <c r="R342" s="1"/>
       <c r="S342" s="1"/>
-      <c r="T342" s="1"/>
+      <c r="T342" s="35"/>
       <c r="U342" s="1"/>
       <c r="V342" s="1"/>
       <c r="W342" s="1"/>
@@ -24001,7 +24201,7 @@
       <c r="Q343" s="1"/>
       <c r="R343" s="1"/>
       <c r="S343" s="1"/>
-      <c r="T343" s="1"/>
+      <c r="T343" s="35"/>
       <c r="U343" s="1"/>
       <c r="V343" s="1"/>
       <c r="W343" s="1"/>
@@ -24055,7 +24255,7 @@
       <c r="Q344" s="1"/>
       <c r="R344" s="1"/>
       <c r="S344" s="1"/>
-      <c r="T344" s="1"/>
+      <c r="T344" s="35"/>
       <c r="U344" s="1"/>
       <c r="V344" s="1"/>
       <c r="W344" s="1"/>
@@ -24109,7 +24309,7 @@
       <c r="Q345" s="1"/>
       <c r="R345" s="1"/>
       <c r="S345" s="1"/>
-      <c r="T345" s="1"/>
+      <c r="T345" s="35"/>
       <c r="U345" s="1"/>
       <c r="V345" s="1"/>
       <c r="W345" s="1"/>
@@ -24163,7 +24363,7 @@
       <c r="Q346" s="1"/>
       <c r="R346" s="1"/>
       <c r="S346" s="1"/>
-      <c r="T346" s="1"/>
+      <c r="T346" s="35"/>
       <c r="U346" s="1"/>
       <c r="V346" s="1"/>
       <c r="W346" s="1"/>
@@ -24217,7 +24417,7 @@
       <c r="Q347" s="1"/>
       <c r="R347" s="1"/>
       <c r="S347" s="1"/>
-      <c r="T347" s="1"/>
+      <c r="T347" s="35"/>
       <c r="U347" s="1"/>
       <c r="V347" s="1"/>
       <c r="W347" s="1"/>
@@ -24271,7 +24471,7 @@
       <c r="Q348" s="1"/>
       <c r="R348" s="1"/>
       <c r="S348" s="1"/>
-      <c r="T348" s="1"/>
+      <c r="T348" s="35"/>
       <c r="U348" s="1"/>
       <c r="V348" s="1"/>
       <c r="W348" s="1"/>
@@ -24325,7 +24525,7 @@
       <c r="Q349" s="1"/>
       <c r="R349" s="1"/>
       <c r="S349" s="1"/>
-      <c r="T349" s="1"/>
+      <c r="T349" s="35"/>
       <c r="U349" s="1"/>
       <c r="V349" s="1"/>
       <c r="W349" s="1"/>
@@ -24379,7 +24579,7 @@
       <c r="Q350" s="1"/>
       <c r="R350" s="1"/>
       <c r="S350" s="1"/>
-      <c r="T350" s="1"/>
+      <c r="T350" s="35"/>
       <c r="U350" s="1"/>
       <c r="V350" s="1"/>
       <c r="W350" s="1"/>
@@ -24433,7 +24633,7 @@
       <c r="Q351" s="1"/>
       <c r="R351" s="1"/>
       <c r="S351" s="1"/>
-      <c r="T351" s="1"/>
+      <c r="T351" s="35"/>
       <c r="U351" s="1"/>
       <c r="V351" s="1"/>
       <c r="W351" s="1"/>
@@ -24487,7 +24687,7 @@
       <c r="Q352" s="1"/>
       <c r="R352" s="1"/>
       <c r="S352" s="1"/>
-      <c r="T352" s="1"/>
+      <c r="T352" s="35"/>
       <c r="U352" s="1"/>
       <c r="V352" s="1"/>
       <c r="W352" s="1"/>
@@ -24541,7 +24741,7 @@
       <c r="Q353" s="1"/>
       <c r="R353" s="1"/>
       <c r="S353" s="1"/>
-      <c r="T353" s="1"/>
+      <c r="T353" s="35"/>
       <c r="U353" s="1"/>
       <c r="V353" s="1"/>
       <c r="W353" s="1"/>
@@ -24595,7 +24795,7 @@
       <c r="Q354" s="1"/>
       <c r="R354" s="1"/>
       <c r="S354" s="1"/>
-      <c r="T354" s="1"/>
+      <c r="T354" s="35"/>
       <c r="U354" s="1"/>
       <c r="V354" s="1"/>
       <c r="W354" s="1"/>
@@ -24649,7 +24849,7 @@
       <c r="Q355" s="1"/>
       <c r="R355" s="1"/>
       <c r="S355" s="1"/>
-      <c r="T355" s="1"/>
+      <c r="T355" s="35"/>
       <c r="U355" s="1"/>
       <c r="V355" s="1"/>
       <c r="W355" s="1"/>
@@ -24703,7 +24903,7 @@
       <c r="Q356" s="1"/>
       <c r="R356" s="1"/>
       <c r="S356" s="1"/>
-      <c r="T356" s="1"/>
+      <c r="T356" s="35"/>
       <c r="U356" s="1"/>
       <c r="V356" s="1"/>
       <c r="W356" s="1"/>
@@ -24757,7 +24957,7 @@
       <c r="Q357" s="1"/>
       <c r="R357" s="1"/>
       <c r="S357" s="1"/>
-      <c r="T357" s="1"/>
+      <c r="T357" s="35"/>
       <c r="U357" s="1"/>
       <c r="V357" s="1"/>
       <c r="W357" s="1"/>
@@ -24811,7 +25011,7 @@
       <c r="Q358" s="1"/>
       <c r="R358" s="1"/>
       <c r="S358" s="1"/>
-      <c r="T358" s="1"/>
+      <c r="T358" s="35"/>
       <c r="U358" s="1"/>
       <c r="V358" s="1"/>
       <c r="W358" s="1"/>
@@ -24865,7 +25065,7 @@
       <c r="Q359" s="1"/>
       <c r="R359" s="1"/>
       <c r="S359" s="1"/>
-      <c r="T359" s="1"/>
+      <c r="T359" s="35"/>
       <c r="U359" s="1"/>
       <c r="V359" s="1"/>
       <c r="W359" s="1"/>
@@ -24919,7 +25119,7 @@
       <c r="Q360" s="1"/>
       <c r="R360" s="1"/>
       <c r="S360" s="1"/>
-      <c r="T360" s="1"/>
+      <c r="T360" s="35"/>
       <c r="U360" s="1"/>
       <c r="V360" s="1"/>
       <c r="W360" s="1"/>
@@ -24973,7 +25173,7 @@
       <c r="Q361" s="1"/>
       <c r="R361" s="1"/>
       <c r="S361" s="1"/>
-      <c r="T361" s="1"/>
+      <c r="T361" s="35"/>
       <c r="U361" s="1"/>
       <c r="V361" s="1"/>
       <c r="W361" s="1"/>
@@ -25027,7 +25227,7 @@
       <c r="Q362" s="1"/>
       <c r="R362" s="1"/>
       <c r="S362" s="1"/>
-      <c r="T362" s="1"/>
+      <c r="T362" s="35"/>
       <c r="U362" s="1"/>
       <c r="V362" s="1"/>
       <c r="W362" s="1"/>
@@ -25081,7 +25281,7 @@
       <c r="Q363" s="1"/>
       <c r="R363" s="1"/>
       <c r="S363" s="1"/>
-      <c r="T363" s="1"/>
+      <c r="T363" s="35"/>
       <c r="U363" s="1"/>
       <c r="V363" s="1"/>
       <c r="W363" s="1"/>
@@ -25135,7 +25335,7 @@
       <c r="Q364" s="1"/>
       <c r="R364" s="1"/>
       <c r="S364" s="1"/>
-      <c r="T364" s="1"/>
+      <c r="T364" s="35"/>
       <c r="U364" s="1"/>
       <c r="V364" s="1"/>
       <c r="W364" s="1"/>
@@ -25189,7 +25389,7 @@
       <c r="Q365" s="1"/>
       <c r="R365" s="1"/>
       <c r="S365" s="1"/>
-      <c r="T365" s="1"/>
+      <c r="T365" s="35"/>
       <c r="U365" s="1"/>
       <c r="V365" s="1"/>
       <c r="W365" s="1"/>
@@ -25243,7 +25443,7 @@
       <c r="Q366" s="1"/>
       <c r="R366" s="1"/>
       <c r="S366" s="1"/>
-      <c r="T366" s="1"/>
+      <c r="T366" s="35"/>
       <c r="U366" s="1"/>
       <c r="V366" s="1"/>
       <c r="W366" s="1"/>
@@ -25297,7 +25497,7 @@
       <c r="Q367" s="1"/>
       <c r="R367" s="1"/>
       <c r="S367" s="1"/>
-      <c r="T367" s="1"/>
+      <c r="T367" s="35"/>
       <c r="U367" s="1"/>
       <c r="V367" s="1"/>
       <c r="W367" s="1"/>
@@ -25351,7 +25551,7 @@
       <c r="Q368" s="1"/>
       <c r="R368" s="1"/>
       <c r="S368" s="1"/>
-      <c r="T368" s="1"/>
+      <c r="T368" s="35"/>
       <c r="U368" s="1"/>
       <c r="V368" s="1"/>
       <c r="W368" s="1"/>
@@ -25405,7 +25605,7 @@
       <c r="Q369" s="1"/>
       <c r="R369" s="1"/>
       <c r="S369" s="1"/>
-      <c r="T369" s="1"/>
+      <c r="T369" s="35"/>
       <c r="U369" s="1"/>
       <c r="V369" s="1"/>
       <c r="W369" s="1"/>
@@ -25459,7 +25659,7 @@
       <c r="Q370" s="1"/>
       <c r="R370" s="1"/>
       <c r="S370" s="1"/>
-      <c r="T370" s="1"/>
+      <c r="T370" s="35"/>
       <c r="U370" s="1"/>
       <c r="V370" s="1"/>
       <c r="W370" s="1"/>
@@ -25513,7 +25713,7 @@
       <c r="Q371" s="1"/>
       <c r="R371" s="1"/>
       <c r="S371" s="1"/>
-      <c r="T371" s="1"/>
+      <c r="T371" s="35"/>
       <c r="U371" s="1"/>
       <c r="V371" s="1"/>
       <c r="W371" s="1"/>
@@ -25567,7 +25767,7 @@
       <c r="Q372" s="1"/>
       <c r="R372" s="1"/>
       <c r="S372" s="1"/>
-      <c r="T372" s="1"/>
+      <c r="T372" s="35"/>
       <c r="U372" s="1"/>
       <c r="V372" s="1"/>
       <c r="W372" s="1"/>
@@ -25621,7 +25821,7 @@
       <c r="Q373" s="1"/>
       <c r="R373" s="1"/>
       <c r="S373" s="1"/>
-      <c r="T373" s="1"/>
+      <c r="T373" s="35"/>
       <c r="U373" s="1"/>
       <c r="V373" s="1"/>
       <c r="W373" s="1"/>
@@ -25675,7 +25875,7 @@
       <c r="Q374" s="1"/>
       <c r="R374" s="1"/>
       <c r="S374" s="1"/>
-      <c r="T374" s="1"/>
+      <c r="T374" s="35"/>
       <c r="U374" s="1"/>
       <c r="V374" s="1"/>
       <c r="W374" s="1"/>
@@ -25729,7 +25929,7 @@
       <c r="Q375" s="1"/>
       <c r="R375" s="1"/>
       <c r="S375" s="1"/>
-      <c r="T375" s="1"/>
+      <c r="T375" s="35"/>
       <c r="U375" s="1"/>
       <c r="V375" s="1"/>
       <c r="W375" s="1"/>
@@ -25783,7 +25983,7 @@
       <c r="Q376" s="1"/>
       <c r="R376" s="1"/>
       <c r="S376" s="1"/>
-      <c r="T376" s="1"/>
+      <c r="T376" s="35"/>
       <c r="U376" s="1"/>
       <c r="V376" s="1"/>
       <c r="W376" s="1"/>
@@ -25837,7 +26037,7 @@
       <c r="Q377" s="1"/>
       <c r="R377" s="1"/>
       <c r="S377" s="1"/>
-      <c r="T377" s="1"/>
+      <c r="T377" s="35"/>
       <c r="U377" s="1"/>
       <c r="V377" s="1"/>
       <c r="W377" s="1"/>
@@ -25891,7 +26091,7 @@
       <c r="Q378" s="1"/>
       <c r="R378" s="1"/>
       <c r="S378" s="1"/>
-      <c r="T378" s="1"/>
+      <c r="T378" s="35"/>
       <c r="U378" s="1"/>
       <c r="V378" s="1"/>
       <c r="W378" s="1"/>
@@ -25945,7 +26145,7 @@
       <c r="Q379" s="1"/>
       <c r="R379" s="1"/>
       <c r="S379" s="1"/>
-      <c r="T379" s="1"/>
+      <c r="T379" s="35"/>
       <c r="U379" s="1"/>
       <c r="V379" s="1"/>
       <c r="W379" s="1"/>
@@ -25999,7 +26199,7 @@
       <c r="Q380" s="1"/>
       <c r="R380" s="1"/>
       <c r="S380" s="1"/>
-      <c r="T380" s="1"/>
+      <c r="T380" s="35"/>
       <c r="U380" s="1"/>
       <c r="V380" s="1"/>
       <c r="W380" s="1"/>
@@ -26053,7 +26253,7 @@
       <c r="Q381" s="1"/>
       <c r="R381" s="1"/>
       <c r="S381" s="1"/>
-      <c r="T381" s="1"/>
+      <c r="T381" s="35"/>
       <c r="U381" s="1"/>
       <c r="V381" s="1"/>
       <c r="W381" s="1"/>
@@ -26107,7 +26307,7 @@
       <c r="Q382" s="1"/>
       <c r="R382" s="1"/>
       <c r="S382" s="1"/>
-      <c r="T382" s="1"/>
+      <c r="T382" s="35"/>
       <c r="U382" s="1"/>
       <c r="V382" s="1"/>
       <c r="W382" s="1"/>
@@ -26161,7 +26361,7 @@
       <c r="Q383" s="1"/>
       <c r="R383" s="1"/>
       <c r="S383" s="1"/>
-      <c r="T383" s="1"/>
+      <c r="T383" s="35"/>
       <c r="U383" s="1"/>
       <c r="V383" s="1"/>
       <c r="W383" s="1"/>
@@ -26215,7 +26415,7 @@
       <c r="Q384" s="1"/>
       <c r="R384" s="1"/>
       <c r="S384" s="1"/>
-      <c r="T384" s="1"/>
+      <c r="T384" s="35"/>
       <c r="U384" s="1"/>
       <c r="V384" s="1"/>
       <c r="W384" s="1"/>
@@ -26269,7 +26469,7 @@
       <c r="Q385" s="1"/>
       <c r="R385" s="1"/>
       <c r="S385" s="1"/>
-      <c r="T385" s="1"/>
+      <c r="T385" s="35"/>
       <c r="U385" s="1"/>
       <c r="V385" s="1"/>
       <c r="W385" s="1"/>
@@ -26323,7 +26523,7 @@
       <c r="Q386" s="1"/>
       <c r="R386" s="1"/>
       <c r="S386" s="1"/>
-      <c r="T386" s="1"/>
+      <c r="T386" s="35"/>
       <c r="U386" s="1"/>
       <c r="V386" s="1"/>
       <c r="W386" s="1"/>
@@ -26377,7 +26577,7 @@
       <c r="Q387" s="1"/>
       <c r="R387" s="1"/>
       <c r="S387" s="1"/>
-      <c r="T387" s="1"/>
+      <c r="T387" s="35"/>
       <c r="U387" s="1"/>
       <c r="V387" s="1"/>
       <c r="W387" s="1"/>
@@ -26431,7 +26631,7 @@
       <c r="Q388" s="1"/>
       <c r="R388" s="1"/>
       <c r="S388" s="1"/>
-      <c r="T388" s="1"/>
+      <c r="T388" s="35"/>
       <c r="U388" s="1"/>
       <c r="V388" s="1"/>
       <c r="W388" s="1"/>
@@ -26485,7 +26685,7 @@
       <c r="Q389" s="1"/>
       <c r="R389" s="1"/>
       <c r="S389" s="1"/>
-      <c r="T389" s="1"/>
+      <c r="T389" s="35"/>
       <c r="U389" s="1"/>
       <c r="V389" s="1"/>
       <c r="W389" s="1"/>
@@ -26539,7 +26739,7 @@
       <c r="Q390" s="1"/>
       <c r="R390" s="1"/>
       <c r="S390" s="1"/>
-      <c r="T390" s="1"/>
+      <c r="T390" s="35"/>
       <c r="U390" s="1"/>
       <c r="V390" s="1"/>
       <c r="W390" s="1"/>
@@ -26593,7 +26793,7 @@
       <c r="Q391" s="1"/>
       <c r="R391" s="1"/>
       <c r="S391" s="1"/>
-      <c r="T391" s="1"/>
+      <c r="T391" s="35"/>
       <c r="U391" s="1"/>
       <c r="V391" s="1"/>
       <c r="W391" s="1"/>
@@ -26647,7 +26847,7 @@
       <c r="Q392" s="1"/>
       <c r="R392" s="1"/>
       <c r="S392" s="1"/>
-      <c r="T392" s="1"/>
+      <c r="T392" s="35"/>
       <c r="U392" s="1"/>
       <c r="V392" s="1"/>
       <c r="W392" s="1"/>
@@ -26701,7 +26901,7 @@
       <c r="Q393" s="1"/>
       <c r="R393" s="1"/>
       <c r="S393" s="1"/>
-      <c r="T393" s="1"/>
+      <c r="T393" s="35"/>
       <c r="U393" s="1"/>
       <c r="V393" s="1"/>
       <c r="W393" s="1"/>
@@ -26755,7 +26955,7 @@
       <c r="Q394" s="1"/>
       <c r="R394" s="1"/>
       <c r="S394" s="1"/>
-      <c r="T394" s="1"/>
+      <c r="T394" s="35"/>
       <c r="U394" s="1"/>
       <c r="V394" s="1"/>
       <c r="W394" s="1"/>
@@ -26809,7 +27009,7 @@
       <c r="Q395" s="1"/>
       <c r="R395" s="1"/>
       <c r="S395" s="1"/>
-      <c r="T395" s="1"/>
+      <c r="T395" s="35"/>
       <c r="U395" s="1"/>
       <c r="V395" s="1"/>
       <c r="W395" s="1"/>
@@ -26863,7 +27063,7 @@
       <c r="Q396" s="1"/>
       <c r="R396" s="1"/>
       <c r="S396" s="1"/>
-      <c r="T396" s="1"/>
+      <c r="T396" s="35"/>
       <c r="U396" s="1"/>
       <c r="V396" s="1"/>
       <c r="W396" s="1"/>
@@ -26917,7 +27117,7 @@
       <c r="Q397" s="1"/>
       <c r="R397" s="1"/>
       <c r="S397" s="1"/>
-      <c r="T397" s="1"/>
+      <c r="T397" s="35"/>
       <c r="U397" s="1"/>
       <c r="V397" s="1"/>
       <c r="W397" s="1"/>
@@ -26971,7 +27171,7 @@
       <c r="Q398" s="1"/>
       <c r="R398" s="1"/>
       <c r="S398" s="1"/>
-      <c r="T398" s="1"/>
+      <c r="T398" s="35"/>
       <c r="U398" s="1"/>
       <c r="V398" s="1"/>
       <c r="W398" s="1"/>
@@ -27025,7 +27225,7 @@
       <c r="Q399" s="1"/>
       <c r="R399" s="1"/>
       <c r="S399" s="1"/>
-      <c r="T399" s="1"/>
+      <c r="T399" s="35"/>
       <c r="U399" s="1"/>
       <c r="V399" s="1"/>
       <c r="W399" s="1"/>
@@ -27079,7 +27279,7 @@
       <c r="Q400" s="1"/>
       <c r="R400" s="1"/>
       <c r="S400" s="1"/>
-      <c r="T400" s="1"/>
+      <c r="T400" s="35"/>
       <c r="U400" s="1"/>
       <c r="V400" s="1"/>
       <c r="W400" s="1"/>
@@ -27133,7 +27333,7 @@
       <c r="Q401" s="1"/>
       <c r="R401" s="1"/>
       <c r="S401" s="1"/>
-      <c r="T401" s="1"/>
+      <c r="T401" s="35"/>
       <c r="U401" s="1"/>
       <c r="V401" s="1"/>
       <c r="W401" s="1"/>
@@ -27187,7 +27387,7 @@
       <c r="Q402" s="1"/>
       <c r="R402" s="1"/>
       <c r="S402" s="1"/>
-      <c r="T402" s="1"/>
+      <c r="T402" s="35"/>
       <c r="U402" s="1"/>
       <c r="V402" s="1"/>
       <c r="W402" s="1"/>
@@ -27241,7 +27441,7 @@
       <c r="Q403" s="1"/>
       <c r="R403" s="1"/>
       <c r="S403" s="1"/>
-      <c r="T403" s="1"/>
+      <c r="T403" s="35"/>
       <c r="U403" s="1"/>
       <c r="V403" s="1"/>
       <c r="W403" s="1"/>
@@ -27295,7 +27495,7 @@
       <c r="Q404" s="1"/>
       <c r="R404" s="1"/>
       <c r="S404" s="1"/>
-      <c r="T404" s="1"/>
+      <c r="T404" s="35"/>
       <c r="U404" s="1"/>
       <c r="V404" s="1"/>
       <c r="W404" s="1"/>
@@ -27349,7 +27549,7 @@
       <c r="Q405" s="1"/>
       <c r="R405" s="1"/>
       <c r="S405" s="1"/>
-      <c r="T405" s="1"/>
+      <c r="T405" s="35"/>
       <c r="U405" s="1"/>
       <c r="V405" s="1"/>
       <c r="W405" s="1"/>
@@ -27403,7 +27603,7 @@
       <c r="Q406" s="1"/>
       <c r="R406" s="1"/>
       <c r="S406" s="1"/>
-      <c r="T406" s="1"/>
+      <c r="T406" s="35"/>
       <c r="U406" s="1"/>
       <c r="V406" s="1"/>
       <c r="W406" s="1"/>
@@ -27457,7 +27657,7 @@
       <c r="Q407" s="1"/>
       <c r="R407" s="1"/>
       <c r="S407" s="1"/>
-      <c r="T407" s="1"/>
+      <c r="T407" s="35"/>
       <c r="U407" s="1"/>
       <c r="V407" s="1"/>
       <c r="W407" s="1"/>
@@ -27511,7 +27711,7 @@
       <c r="Q408" s="1"/>
       <c r="R408" s="1"/>
       <c r="S408" s="1"/>
-      <c r="T408" s="1"/>
+      <c r="T408" s="35"/>
       <c r="U408" s="1"/>
       <c r="V408" s="1"/>
       <c r="W408" s="1"/>
@@ -27565,7 +27765,7 @@
       <c r="Q409" s="1"/>
       <c r="R409" s="1"/>
       <c r="S409" s="1"/>
-      <c r="T409" s="1"/>
+      <c r="T409" s="35"/>
       <c r="U409" s="1"/>
       <c r="V409" s="1"/>
       <c r="W409" s="1"/>
@@ -27619,7 +27819,7 @@
       <c r="Q410" s="1"/>
       <c r="R410" s="1"/>
       <c r="S410" s="1"/>
-      <c r="T410" s="1"/>
+      <c r="T410" s="35"/>
       <c r="U410" s="1"/>
       <c r="V410" s="1"/>
       <c r="W410" s="1"/>
@@ -27673,7 +27873,7 @@
       <c r="Q411" s="1"/>
       <c r="R411" s="1"/>
       <c r="S411" s="1"/>
-      <c r="T411" s="1"/>
+      <c r="T411" s="35"/>
       <c r="U411" s="1"/>
       <c r="V411" s="1"/>
       <c r="W411" s="1"/>
@@ -27727,7 +27927,7 @@
       <c r="Q412" s="1"/>
       <c r="R412" s="1"/>
       <c r="S412" s="1"/>
-      <c r="T412" s="1"/>
+      <c r="T412" s="35"/>
       <c r="U412" s="1"/>
       <c r="V412" s="1"/>
       <c r="W412" s="1"/>
@@ -27781,7 +27981,7 @@
       <c r="Q413" s="1"/>
       <c r="R413" s="1"/>
       <c r="S413" s="1"/>
-      <c r="T413" s="1"/>
+      <c r="T413" s="35"/>
       <c r="U413" s="1"/>
       <c r="V413" s="1"/>
       <c r="W413" s="1"/>
@@ -27835,7 +28035,7 @@
       <c r="Q414" s="1"/>
       <c r="R414" s="1"/>
       <c r="S414" s="1"/>
-      <c r="T414" s="1"/>
+      <c r="T414" s="35"/>
       <c r="U414" s="1"/>
       <c r="V414" s="1"/>
       <c r="W414" s="1"/>
@@ -27889,7 +28089,7 @@
       <c r="Q415" s="1"/>
       <c r="R415" s="1"/>
       <c r="S415" s="1"/>
-      <c r="T415" s="1"/>
+      <c r="T415" s="35"/>
       <c r="U415" s="1"/>
       <c r="V415" s="1"/>
       <c r="W415" s="1"/>
@@ -27943,7 +28143,7 @@
       <c r="Q416" s="1"/>
       <c r="R416" s="1"/>
       <c r="S416" s="1"/>
-      <c r="T416" s="1"/>
+      <c r="T416" s="35"/>
       <c r="U416" s="1"/>
       <c r="V416" s="1"/>
       <c r="W416" s="1"/>
@@ -27997,7 +28197,7 @@
       <c r="Q417" s="1"/>
       <c r="R417" s="1"/>
       <c r="S417" s="1"/>
-      <c r="T417" s="1"/>
+      <c r="T417" s="35"/>
       <c r="U417" s="1"/>
       <c r="V417" s="1"/>
       <c r="W417" s="1"/>
@@ -28051,7 +28251,7 @@
       <c r="Q418" s="1"/>
       <c r="R418" s="1"/>
       <c r="S418" s="1"/>
-      <c r="T418" s="1"/>
+      <c r="T418" s="35"/>
       <c r="U418" s="1"/>
       <c r="V418" s="1"/>
       <c r="W418" s="1"/>
@@ -28105,7 +28305,7 @@
       <c r="Q419" s="1"/>
       <c r="R419" s="1"/>
       <c r="S419" s="1"/>
-      <c r="T419" s="1"/>
+      <c r="T419" s="35"/>
       <c r="U419" s="1"/>
       <c r="V419" s="1"/>
       <c r="W419" s="1"/>
@@ -28159,7 +28359,7 @@
       <c r="Q420" s="1"/>
       <c r="R420" s="1"/>
       <c r="S420" s="1"/>
-      <c r="T420" s="1"/>
+      <c r="T420" s="35"/>
       <c r="U420" s="1"/>
       <c r="V420" s="1"/>
       <c r="W420" s="1"/>
@@ -28213,7 +28413,7 @@
       <c r="Q421" s="1"/>
       <c r="R421" s="1"/>
       <c r="S421" s="1"/>
-      <c r="T421" s="1"/>
+      <c r="T421" s="35"/>
       <c r="U421" s="1"/>
       <c r="V421" s="1"/>
       <c r="W421" s="1"/>
@@ -28267,7 +28467,7 @@
       <c r="Q422" s="1"/>
       <c r="R422" s="1"/>
       <c r="S422" s="1"/>
-      <c r="T422" s="1"/>
+      <c r="T422" s="35"/>
       <c r="U422" s="1"/>
       <c r="V422" s="1"/>
       <c r="W422" s="1"/>
@@ -28321,7 +28521,7 @@
       <c r="Q423" s="1"/>
       <c r="R423" s="1"/>
       <c r="S423" s="1"/>
-      <c r="T423" s="1"/>
+      <c r="T423" s="35"/>
       <c r="U423" s="1"/>
       <c r="V423" s="1"/>
       <c r="W423" s="1"/>
@@ -28375,7 +28575,7 @@
       <c r="Q424" s="1"/>
       <c r="R424" s="1"/>
       <c r="S424" s="1"/>
-      <c r="T424" s="1"/>
+      <c r="T424" s="35"/>
       <c r="U424" s="1"/>
       <c r="V424" s="1"/>
       <c r="W424" s="1"/>
@@ -28429,7 +28629,7 @@
       <c r="Q425" s="1"/>
       <c r="R425" s="1"/>
       <c r="S425" s="1"/>
-      <c r="T425" s="1"/>
+      <c r="T425" s="35"/>
       <c r="U425" s="1"/>
       <c r="V425" s="1"/>
       <c r="W425" s="1"/>
@@ -28483,7 +28683,7 @@
       <c r="Q426" s="1"/>
       <c r="R426" s="1"/>
       <c r="S426" s="1"/>
-      <c r="T426" s="1"/>
+      <c r="T426" s="35"/>
       <c r="U426" s="1"/>
       <c r="V426" s="1"/>
       <c r="W426" s="1"/>
@@ -28537,7 +28737,7 @@
       <c r="Q427" s="1"/>
       <c r="R427" s="1"/>
       <c r="S427" s="1"/>
-      <c r="T427" s="1"/>
+      <c r="T427" s="35"/>
       <c r="U427" s="1"/>
       <c r="V427" s="1"/>
       <c r="W427" s="1"/>
@@ -28591,7 +28791,7 @@
       <c r="Q428" s="1"/>
       <c r="R428" s="1"/>
       <c r="S428" s="1"/>
-      <c r="T428" s="1"/>
+      <c r="T428" s="35"/>
       <c r="U428" s="1"/>
       <c r="V428" s="1"/>
       <c r="W428" s="1"/>
@@ -28645,7 +28845,7 @@
       <c r="Q429" s="1"/>
       <c r="R429" s="1"/>
       <c r="S429" s="1"/>
-      <c r="T429" s="1"/>
+      <c r="T429" s="35"/>
       <c r="U429" s="1"/>
       <c r="V429" s="1"/>
       <c r="W429" s="1"/>
@@ -28699,7 +28899,7 @@
       <c r="Q430" s="1"/>
       <c r="R430" s="1"/>
       <c r="S430" s="1"/>
-      <c r="T430" s="1"/>
+      <c r="T430" s="35"/>
       <c r="U430" s="1"/>
       <c r="V430" s="1"/>
       <c r="W430" s="1"/>
@@ -28753,7 +28953,7 @@
       <c r="Q431" s="1"/>
       <c r="R431" s="1"/>
       <c r="S431" s="1"/>
-      <c r="T431" s="1"/>
+      <c r="T431" s="35"/>
       <c r="U431" s="1"/>
       <c r="V431" s="1"/>
       <c r="W431" s="1"/>
@@ -28807,7 +29007,7 @@
       <c r="Q432" s="1"/>
       <c r="R432" s="1"/>
       <c r="S432" s="1"/>
-      <c r="T432" s="1"/>
+      <c r="T432" s="35"/>
       <c r="U432" s="1"/>
       <c r="V432" s="1"/>
       <c r="W432" s="1"/>
@@ -28861,7 +29061,7 @@
       <c r="Q433" s="1"/>
       <c r="R433" s="1"/>
       <c r="S433" s="1"/>
-      <c r="T433" s="1"/>
+      <c r="T433" s="35"/>
       <c r="U433" s="1"/>
       <c r="V433" s="1"/>
       <c r="W433" s="1"/>
@@ -28915,7 +29115,7 @@
       <c r="Q434" s="1"/>
       <c r="R434" s="1"/>
       <c r="S434" s="1"/>
-      <c r="T434" s="1"/>
+      <c r="T434" s="35"/>
       <c r="U434" s="1"/>
       <c r="V434" s="1"/>
       <c r="W434" s="1"/>
@@ -28969,7 +29169,7 @@
       <c r="Q435" s="1"/>
       <c r="R435" s="1"/>
       <c r="S435" s="1"/>
-      <c r="T435" s="1"/>
+      <c r="T435" s="35"/>
       <c r="U435" s="1"/>
       <c r="V435" s="1"/>
       <c r="W435" s="1"/>
@@ -29023,7 +29223,7 @@
       <c r="Q436" s="1"/>
       <c r="R436" s="1"/>
       <c r="S436" s="1"/>
-      <c r="T436" s="1"/>
+      <c r="T436" s="35"/>
       <c r="U436" s="1"/>
       <c r="V436" s="1"/>
       <c r="W436" s="1"/>
@@ -29077,7 +29277,7 @@
       <c r="Q437" s="1"/>
       <c r="R437" s="1"/>
       <c r="S437" s="1"/>
-      <c r="T437" s="1"/>
+      <c r="T437" s="35"/>
       <c r="U437" s="1"/>
       <c r="V437" s="1"/>
       <c r="W437" s="1"/>
@@ -29131,7 +29331,7 @@
       <c r="Q438" s="1"/>
       <c r="R438" s="1"/>
       <c r="S438" s="1"/>
-      <c r="T438" s="1"/>
+      <c r="T438" s="35"/>
       <c r="U438" s="1"/>
       <c r="V438" s="1"/>
       <c r="W438" s="1"/>
@@ -29185,7 +29385,7 @@
       <c r="Q439" s="1"/>
       <c r="R439" s="1"/>
       <c r="S439" s="1"/>
-      <c r="T439" s="1"/>
+      <c r="T439" s="35"/>
       <c r="U439" s="1"/>
       <c r="V439" s="1"/>
       <c r="W439" s="1"/>
@@ -29239,7 +29439,7 @@
       <c r="Q440" s="1"/>
       <c r="R440" s="1"/>
       <c r="S440" s="1"/>
-      <c r="T440" s="1"/>
+      <c r="T440" s="35"/>
       <c r="U440" s="1"/>
       <c r="V440" s="1"/>
       <c r="W440" s="1"/>
@@ -29293,7 +29493,7 @@
       <c r="Q441" s="1"/>
       <c r="R441" s="1"/>
       <c r="S441" s="1"/>
-      <c r="T441" s="1"/>
+      <c r="T441" s="35"/>
       <c r="U441" s="1"/>
       <c r="V441" s="1"/>
       <c r="W441" s="1"/>
@@ -29347,7 +29547,7 @@
       <c r="Q442" s="1"/>
       <c r="R442" s="1"/>
       <c r="S442" s="1"/>
-      <c r="T442" s="1"/>
+      <c r="T442" s="35"/>
       <c r="U442" s="1"/>
       <c r="V442" s="1"/>
       <c r="W442" s="1"/>
@@ -29401,7 +29601,7 @@
       <c r="Q443" s="1"/>
       <c r="R443" s="1"/>
       <c r="S443" s="1"/>
-      <c r="T443" s="1"/>
+      <c r="T443" s="35"/>
       <c r="U443" s="1"/>
       <c r="V443" s="1"/>
       <c r="W443" s="1"/>
@@ -29455,7 +29655,7 @@
       <c r="Q444" s="1"/>
       <c r="R444" s="1"/>
       <c r="S444" s="1"/>
-      <c r="T444" s="1"/>
+      <c r="T444" s="35"/>
       <c r="U444" s="1"/>
       <c r="V444" s="1"/>
       <c r="W444" s="1"/>
@@ -29509,7 +29709,7 @@
       <c r="Q445" s="1"/>
       <c r="R445" s="1"/>
       <c r="S445" s="1"/>
-      <c r="T445" s="1"/>
+      <c r="T445" s="35"/>
       <c r="U445" s="1"/>
       <c r="V445" s="1"/>
       <c r="W445" s="1"/>
@@ -29563,7 +29763,7 @@
       <c r="Q446" s="1"/>
       <c r="R446" s="1"/>
       <c r="S446" s="1"/>
-      <c r="T446" s="1"/>
+      <c r="T446" s="35"/>
       <c r="U446" s="1"/>
       <c r="V446" s="1"/>
       <c r="W446" s="1"/>
@@ -29617,7 +29817,7 @@
       <c r="Q447" s="1"/>
       <c r="R447" s="1"/>
       <c r="S447" s="1"/>
-      <c r="T447" s="1"/>
+      <c r="T447" s="35"/>
       <c r="U447" s="1"/>
       <c r="V447" s="1"/>
       <c r="W447" s="1"/>
@@ -29671,7 +29871,7 @@
       <c r="Q448" s="1"/>
       <c r="R448" s="1"/>
       <c r="S448" s="1"/>
-      <c r="T448" s="1"/>
+      <c r="T448" s="35"/>
       <c r="U448" s="1"/>
       <c r="V448" s="1"/>
       <c r="W448" s="1"/>
@@ -29725,7 +29925,7 @@
       <c r="Q449" s="1"/>
       <c r="R449" s="1"/>
       <c r="S449" s="1"/>
-      <c r="T449" s="1"/>
+      <c r="T449" s="35"/>
       <c r="U449" s="1"/>
       <c r="V449" s="1"/>
       <c r="W449" s="1"/>
@@ -29779,7 +29979,7 @@
       <c r="Q450" s="1"/>
       <c r="R450" s="1"/>
       <c r="S450" s="1"/>
-      <c r="T450" s="1"/>
+      <c r="T450" s="35"/>
       <c r="U450" s="1"/>
       <c r="V450" s="1"/>
       <c r="W450" s="1"/>
@@ -29833,7 +30033,7 @@
       <c r="Q451" s="1"/>
       <c r="R451" s="1"/>
       <c r="S451" s="1"/>
-      <c r="T451" s="1"/>
+      <c r="T451" s="35"/>
       <c r="U451" s="1"/>
       <c r="V451" s="1"/>
       <c r="W451" s="1"/>
@@ -29887,7 +30087,7 @@
       <c r="Q452" s="1"/>
       <c r="R452" s="1"/>
       <c r="S452" s="1"/>
-      <c r="T452" s="1"/>
+      <c r="T452" s="35"/>
       <c r="U452" s="1"/>
       <c r="V452" s="1"/>
       <c r="W452" s="1"/>
@@ -29941,7 +30141,7 @@
       <c r="Q453" s="1"/>
       <c r="R453" s="1"/>
       <c r="S453" s="1"/>
-      <c r="T453" s="1"/>
+      <c r="T453" s="35"/>
       <c r="U453" s="1"/>
       <c r="V453" s="1"/>
       <c r="W453" s="1"/>
@@ -29995,7 +30195,7 @@
       <c r="Q454" s="1"/>
       <c r="R454" s="1"/>
       <c r="S454" s="1"/>
-      <c r="T454" s="1"/>
+      <c r="T454" s="35"/>
       <c r="U454" s="1"/>
       <c r="V454" s="1"/>
       <c r="W454" s="1"/>
@@ -30049,7 +30249,7 @@
       <c r="Q455" s="1"/>
       <c r="R455" s="1"/>
       <c r="S455" s="1"/>
-      <c r="T455" s="1"/>
+      <c r="T455" s="35"/>
       <c r="U455" s="1"/>
       <c r="V455" s="1"/>
       <c r="W455" s="1"/>
@@ -30103,7 +30303,7 @@
       <c r="Q456" s="1"/>
       <c r="R456" s="1"/>
       <c r="S456" s="1"/>
-      <c r="T456" s="1"/>
+      <c r="T456" s="35"/>
       <c r="U456" s="1"/>
       <c r="V456" s="1"/>
       <c r="W456" s="1"/>
@@ -30157,7 +30357,7 @@
       <c r="Q457" s="1"/>
       <c r="R457" s="1"/>
       <c r="S457" s="1"/>
-      <c r="T457" s="1"/>
+      <c r="T457" s="35"/>
       <c r="U457" s="1"/>
       <c r="V457" s="1"/>
       <c r="W457" s="1"/>
@@ -30211,7 +30411,7 @@
       <c r="Q458" s="1"/>
       <c r="R458" s="1"/>
       <c r="S458" s="1"/>
-      <c r="T458" s="1"/>
+      <c r="T458" s="35"/>
       <c r="U458" s="1"/>
       <c r="V458" s="1"/>
       <c r="W458" s="1"/>
@@ -30265,7 +30465,7 @@
       <c r="Q459" s="1"/>
       <c r="R459" s="1"/>
       <c r="S459" s="1"/>
-      <c r="T459" s="1"/>
+      <c r="T459" s="35"/>
       <c r="U459" s="1"/>
       <c r="V459" s="1"/>
       <c r="W459" s="1"/>
@@ -30319,7 +30519,7 @@
       <c r="Q460" s="1"/>
       <c r="R460" s="1"/>
       <c r="S460" s="1"/>
-      <c r="T460" s="1"/>
+      <c r="T460" s="35"/>
       <c r="U460" s="1"/>
       <c r="V460" s="1"/>
       <c r="W460" s="1"/>
@@ -30373,7 +30573,7 @@
       <c r="Q461" s="1"/>
       <c r="R461" s="1"/>
       <c r="S461" s="1"/>
-      <c r="T461" s="1"/>
+      <c r="T461" s="35"/>
       <c r="U461" s="1"/>
       <c r="V461" s="1"/>
       <c r="W461" s="1"/>
@@ -30427,7 +30627,7 @@
       <c r="Q462" s="1"/>
       <c r="R462" s="1"/>
       <c r="S462" s="1"/>
-      <c r="T462" s="1"/>
+      <c r="T462" s="35"/>
       <c r="U462" s="1"/>
       <c r="V462" s="1"/>
       <c r="W462" s="1"/>
@@ -30481,7 +30681,7 @@
       <c r="Q463" s="1"/>
       <c r="R463" s="1"/>
       <c r="S463" s="1"/>
-      <c r="T463" s="1"/>
+      <c r="T463" s="35"/>
       <c r="U463" s="1"/>
       <c r="V463" s="1"/>
       <c r="W463" s="1"/>
@@ -30535,7 +30735,7 @@
       <c r="Q464" s="1"/>
       <c r="R464" s="1"/>
       <c r="S464" s="1"/>
-      <c r="T464" s="1"/>
+      <c r="T464" s="35"/>
       <c r="U464" s="1"/>
       <c r="V464" s="1"/>
       <c r="W464" s="1"/>
@@ -30589,7 +30789,7 @@
       <c r="Q465" s="1"/>
       <c r="R465" s="1"/>
       <c r="S465" s="1"/>
-      <c r="T465" s="1"/>
+      <c r="T465" s="35"/>
       <c r="U465" s="1"/>
       <c r="V465" s="1"/>
       <c r="W465" s="1"/>
@@ -30643,7 +30843,7 @@
       <c r="Q466" s="1"/>
       <c r="R466" s="1"/>
       <c r="S466" s="1"/>
-      <c r="T466" s="1"/>
+      <c r="T466" s="35"/>
       <c r="U466" s="1"/>
       <c r="V466" s="1"/>
       <c r="W466" s="1"/>
@@ -30697,7 +30897,7 @@
       <c r="Q467" s="1"/>
       <c r="R467" s="1"/>
       <c r="S467" s="1"/>
-      <c r="T467" s="1"/>
+      <c r="T467" s="35"/>
       <c r="U467" s="1"/>
       <c r="V467" s="1"/>
       <c r="W467" s="1"/>
@@ -30751,7 +30951,7 @@
       <c r="Q468" s="1"/>
       <c r="R468" s="1"/>
       <c r="S468" s="1"/>
-      <c r="T468" s="1"/>
+      <c r="T468" s="35"/>
       <c r="U468" s="1"/>
       <c r="V468" s="1"/>
       <c r="W468" s="1"/>
@@ -30805,7 +31005,7 @@
       <c r="Q469" s="1"/>
       <c r="R469" s="1"/>
       <c r="S469" s="1"/>
-      <c r="T469" s="1"/>
+      <c r="T469" s="35"/>
       <c r="U469" s="1"/>
       <c r="V469" s="1"/>
       <c r="W469" s="1"/>
@@ -30859,7 +31059,7 @@
       <c r="Q470" s="1"/>
       <c r="R470" s="1"/>
       <c r="S470" s="1"/>
-      <c r="T470" s="1"/>
+      <c r="T470" s="35"/>
       <c r="U470" s="1"/>
       <c r="V470" s="1"/>
       <c r="W470" s="1"/>
@@ -30913,7 +31113,7 @@
       <c r="Q471" s="1"/>
       <c r="R471" s="1"/>
       <c r="S471" s="1"/>
-      <c r="T471" s="1"/>
+      <c r="T471" s="35"/>
       <c r="U471" s="1"/>
       <c r="V471" s="1"/>
       <c r="W471" s="1"/>
@@ -30967,7 +31167,7 @@
       <c r="Q472" s="1"/>
       <c r="R472" s="1"/>
       <c r="S472" s="1"/>
-      <c r="T472" s="1"/>
+      <c r="T472" s="35"/>
       <c r="U472" s="1"/>
       <c r="V472" s="1"/>
       <c r="W472" s="1"/>
@@ -31021,7 +31221,7 @@
       <c r="Q473" s="1"/>
       <c r="R473" s="1"/>
       <c r="S473" s="1"/>
-      <c r="T473" s="1"/>
+      <c r="T473" s="35"/>
       <c r="U473" s="1"/>
       <c r="V473" s="1"/>
       <c r="W473" s="1"/>
@@ -31075,7 +31275,7 @@
       <c r="Q474" s="1"/>
       <c r="R474" s="1"/>
       <c r="S474" s="1"/>
-      <c r="T474" s="1"/>
+      <c r="T474" s="35"/>
       <c r="U474" s="1"/>
       <c r="V474" s="1"/>
       <c r="W474" s="1"/>
@@ -31129,7 +31329,7 @@
       <c r="Q475" s="1"/>
       <c r="R475" s="1"/>
       <c r="S475" s="1"/>
-      <c r="T475" s="1"/>
+      <c r="T475" s="35"/>
       <c r="U475" s="1"/>
       <c r="V475" s="1"/>
       <c r="W475" s="1"/>
@@ -31183,7 +31383,7 @@
       <c r="Q476" s="1"/>
       <c r="R476" s="1"/>
       <c r="S476" s="1"/>
-      <c r="T476" s="1"/>
+      <c r="T476" s="35"/>
       <c r="U476" s="1"/>
       <c r="V476" s="1"/>
       <c r="W476" s="1"/>
@@ -31237,7 +31437,7 @@
       <c r="Q477" s="1"/>
       <c r="R477" s="1"/>
       <c r="S477" s="1"/>
-      <c r="T477" s="1"/>
+      <c r="T477" s="35"/>
       <c r="U477" s="1"/>
       <c r="V477" s="1"/>
       <c r="W477" s="1"/>
@@ -31291,7 +31491,7 @@
       <c r="Q478" s="1"/>
       <c r="R478" s="1"/>
       <c r="S478" s="1"/>
-      <c r="T478" s="1"/>
+      <c r="T478" s="35"/>
       <c r="U478" s="1"/>
       <c r="V478" s="1"/>
       <c r="W478" s="1"/>
@@ -31345,7 +31545,7 @@
       <c r="Q479" s="1"/>
       <c r="R479" s="1"/>
       <c r="S479" s="1"/>
-      <c r="T479" s="1"/>
+      <c r="T479" s="35"/>
       <c r="U479" s="1"/>
       <c r="V479" s="1"/>
       <c r="W479" s="1"/>
@@ -31399,7 +31599,7 @@
       <c r="Q480" s="1"/>
       <c r="R480" s="1"/>
       <c r="S480" s="1"/>
-      <c r="T480" s="1"/>
+      <c r="T480" s="35"/>
       <c r="U480" s="1"/>
       <c r="V480" s="1"/>
       <c r="W480" s="1"/>
@@ -31453,7 +31653,7 @@
       <c r="Q481" s="1"/>
       <c r="R481" s="1"/>
       <c r="S481" s="1"/>
-      <c r="T481" s="1"/>
+      <c r="T481" s="35"/>
       <c r="U481" s="1"/>
       <c r="V481" s="1"/>
       <c r="W481" s="1"/>
@@ -31507,7 +31707,7 @@
       <c r="Q482" s="1"/>
       <c r="R482" s="1"/>
       <c r="S482" s="1"/>
-      <c r="T482" s="1"/>
+      <c r="T482" s="35"/>
       <c r="U482" s="1"/>
       <c r="V482" s="1"/>
       <c r="W482" s="1"/>
@@ -31561,7 +31761,7 @@
       <c r="Q483" s="1"/>
       <c r="R483" s="1"/>
       <c r="S483" s="1"/>
-      <c r="T483" s="1"/>
+      <c r="T483" s="35"/>
       <c r="U483" s="1"/>
       <c r="V483" s="1"/>
       <c r="W483" s="1"/>
@@ -31615,7 +31815,7 @@
       <c r="Q484" s="1"/>
       <c r="R484" s="1"/>
       <c r="S484" s="1"/>
-      <c r="T484" s="1"/>
+      <c r="T484" s="35"/>
       <c r="U484" s="1"/>
       <c r="V484" s="1"/>
       <c r="W484" s="1"/>
@@ -31669,7 +31869,7 @@
       <c r="Q485" s="1"/>
       <c r="R485" s="1"/>
       <c r="S485" s="1"/>
-      <c r="T485" s="1"/>
+      <c r="T485" s="35"/>
       <c r="U485" s="1"/>
       <c r="V485" s="1"/>
       <c r="W485" s="1"/>
@@ -31723,7 +31923,7 @@
       <c r="Q486" s="1"/>
       <c r="R486" s="1"/>
       <c r="S486" s="1"/>
-      <c r="T486" s="1"/>
+      <c r="T486" s="35"/>
       <c r="U486" s="1"/>
       <c r="V486" s="1"/>
       <c r="W486" s="1"/>
@@ -31777,7 +31977,7 @@
       <c r="Q487" s="1"/>
       <c r="R487" s="1"/>
       <c r="S487" s="1"/>
-      <c r="T487" s="1"/>
+      <c r="T487" s="35"/>
       <c r="U487" s="1"/>
       <c r="V487" s="1"/>
       <c r="W487" s="1"/>
@@ -31831,7 +32031,7 @@
       <c r="Q488" s="1"/>
       <c r="R488" s="1"/>
       <c r="S488" s="1"/>
-      <c r="T488" s="1"/>
+      <c r="T488" s="35"/>
       <c r="U488" s="1"/>
       <c r="V488" s="1"/>
       <c r="W488" s="1"/>
@@ -31885,7 +32085,7 @@
       <c r="Q489" s="1"/>
       <c r="R489" s="1"/>
       <c r="S489" s="1"/>
-      <c r="T489" s="1"/>
+      <c r="T489" s="35"/>
       <c r="U489" s="1"/>
       <c r="V489" s="1"/>
       <c r="W489" s="1"/>
@@ -31939,7 +32139,7 @@
       <c r="Q490" s="1"/>
       <c r="R490" s="1"/>
       <c r="S490" s="1"/>
-      <c r="T490" s="1"/>
+      <c r="T490" s="35"/>
       <c r="U490" s="1"/>
       <c r="V490" s="1"/>
       <c r="W490" s="1"/>
@@ -31993,7 +32193,7 @@
       <c r="Q491" s="1"/>
       <c r="R491" s="1"/>
       <c r="S491" s="1"/>
-      <c r="T491" s="1"/>
+      <c r="T491" s="35"/>
       <c r="U491" s="1"/>
       <c r="V491" s="1"/>
       <c r="W491" s="1"/>
@@ -32047,7 +32247,7 @@
       <c r="Q492" s="1"/>
       <c r="R492" s="1"/>
       <c r="S492" s="1"/>
-      <c r="T492" s="1"/>
+      <c r="T492" s="35"/>
       <c r="U492" s="1"/>
       <c r="V492" s="1"/>
       <c r="W492" s="1"/>
@@ -32101,7 +32301,7 @@
       <c r="Q493" s="1"/>
       <c r="R493" s="1"/>
       <c r="S493" s="1"/>
-      <c r="T493" s="1"/>
+      <c r="T493" s="35"/>
       <c r="U493" s="1"/>
       <c r="V493" s="1"/>
       <c r="W493" s="1"/>
@@ -32155,7 +32355,7 @@
       <c r="Q494" s="1"/>
       <c r="R494" s="1"/>
       <c r="S494" s="1"/>
-      <c r="T494" s="1"/>
+      <c r="T494" s="35"/>
       <c r="U494" s="1"/>
       <c r="V494" s="1"/>
       <c r="W494" s="1"/>
@@ -32209,7 +32409,7 @@
       <c r="Q495" s="1"/>
       <c r="R495" s="1"/>
       <c r="S495" s="1"/>
-      <c r="T495" s="1"/>
+      <c r="T495" s="35"/>
       <c r="U495" s="1"/>
       <c r="V495" s="1"/>
       <c r="W495" s="1"/>
@@ -32263,7 +32463,7 @@
       <c r="Q496" s="1"/>
       <c r="R496" s="1"/>
       <c r="S496" s="1"/>
-      <c r="T496" s="1"/>
+      <c r="T496" s="35"/>
       <c r="U496" s="1"/>
       <c r="V496" s="1"/>
       <c r="W496" s="1"/>
@@ -32317,7 +32517,7 @@
       <c r="Q497" s="1"/>
       <c r="R497" s="1"/>
       <c r="S497" s="1"/>
-      <c r="T497" s="1"/>
+      <c r="T497" s="35"/>
       <c r="U497" s="1"/>
       <c r="V497" s="1"/>
       <c r="W497" s="1"/>
@@ -32371,7 +32571,7 @@
       <c r="Q498" s="1"/>
       <c r="R498" s="1"/>
       <c r="S498" s="1"/>
-      <c r="T498" s="1"/>
+      <c r="T498" s="35"/>
       <c r="U498" s="1"/>
       <c r="V498" s="1"/>
       <c r="W498" s="1"/>
@@ -32425,7 +32625,7 @@
       <c r="Q499" s="1"/>
       <c r="R499" s="1"/>
       <c r="S499" s="1"/>
-      <c r="T499" s="1"/>
+      <c r="T499" s="35"/>
       <c r="U499" s="1"/>
       <c r="V499" s="1"/>
       <c r="W499" s="1"/>
@@ -32479,7 +32679,7 @@
       <c r="Q500" s="1"/>
       <c r="R500" s="1"/>
       <c r="S500" s="1"/>
-      <c r="T500" s="1"/>
+      <c r="T500" s="35"/>
       <c r="U500" s="1"/>
       <c r="V500" s="1"/>
       <c r="W500" s="1"/>
